--- a/VerveStacks_CHN/SysSettings.xlsx
+++ b/VerveStacks_CHN/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF189E00-F12A-472A-B92A-2683A1A1781B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02F84926-5FC9-4842-970E-F66B19EF5DF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_CHN/SysSettings.xlsx
+++ b/VerveStacks_CHN/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02F84926-5FC9-4842-970E-F66B19EF5DF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A090746B-41EF-46A1-8166-A4E355C4498C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="570" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2256" uniqueCount="783">
   <si>
     <t>~BookRegions_Map</t>
   </si>
@@ -682,25 +682,1711 @@
     <t>set</t>
   </si>
   <si>
-    <t>elc_spv-CHN</t>
-  </si>
-  <si>
-    <t>solar electricity generation</t>
+    <t>elc_spv_001</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 1</t>
   </si>
   <si>
     <t>TWh</t>
   </si>
   <si>
-    <t>elc_wof-CHN</t>
-  </si>
-  <si>
-    <t>offshore wind electricity generation</t>
-  </si>
-  <si>
-    <t>elc_won-CHN</t>
-  </si>
-  <si>
-    <t>onshore wind electricity generation</t>
+    <t>elc_spv_002</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 2</t>
+  </si>
+  <si>
+    <t>elc_spv_003</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 3</t>
+  </si>
+  <si>
+    <t>elc_spv_004</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 4</t>
+  </si>
+  <si>
+    <t>elc_spv_005</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 5</t>
+  </si>
+  <si>
+    <t>elc_spv_006</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 6</t>
+  </si>
+  <si>
+    <t>elc_spv_007</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 7</t>
+  </si>
+  <si>
+    <t>elc_spv_008</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 8</t>
+  </si>
+  <si>
+    <t>elc_spv_009</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 9</t>
+  </si>
+  <si>
+    <t>elc_spv_010</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 10</t>
+  </si>
+  <si>
+    <t>elc_spv_011</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 11</t>
+  </si>
+  <si>
+    <t>elc_spv_012</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 12</t>
+  </si>
+  <si>
+    <t>elc_spv_013</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 13</t>
+  </si>
+  <si>
+    <t>elc_spv_014</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 14</t>
+  </si>
+  <si>
+    <t>elc_spv_015</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 15</t>
+  </si>
+  <si>
+    <t>elc_spv_016</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 16</t>
+  </si>
+  <si>
+    <t>elc_spv_017</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 17</t>
+  </si>
+  <si>
+    <t>elc_spv_018</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 18</t>
+  </si>
+  <si>
+    <t>elc_spv_019</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 19</t>
+  </si>
+  <si>
+    <t>elc_spv_020</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 20</t>
+  </si>
+  <si>
+    <t>elc_spv_021</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 21</t>
+  </si>
+  <si>
+    <t>elc_spv_022</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 22</t>
+  </si>
+  <si>
+    <t>elc_spv_023</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 23</t>
+  </si>
+  <si>
+    <t>elc_spv_024</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 24</t>
+  </si>
+  <si>
+    <t>elc_spv_025</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 25</t>
+  </si>
+  <si>
+    <t>elc_spv_026</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 26</t>
+  </si>
+  <si>
+    <t>elc_spv_027</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 27</t>
+  </si>
+  <si>
+    <t>elc_spv_028</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 28</t>
+  </si>
+  <si>
+    <t>elc_spv_029</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 29</t>
+  </si>
+  <si>
+    <t>elc_spv_030</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 30</t>
+  </si>
+  <si>
+    <t>elc_spv_031</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 31</t>
+  </si>
+  <si>
+    <t>elc_spv_032</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 32</t>
+  </si>
+  <si>
+    <t>elc_spv_033</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 33</t>
+  </si>
+  <si>
+    <t>elc_spv_034</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 34</t>
+  </si>
+  <si>
+    <t>elc_spv_035</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 35</t>
+  </si>
+  <si>
+    <t>elc_spv_036</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 36</t>
+  </si>
+  <si>
+    <t>elc_spv_037</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 37</t>
+  </si>
+  <si>
+    <t>elc_spv_038</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 38</t>
+  </si>
+  <si>
+    <t>elc_spv_039</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 39</t>
+  </si>
+  <si>
+    <t>elc_spv_040</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 40</t>
+  </si>
+  <si>
+    <t>elc_spv_041</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 41</t>
+  </si>
+  <si>
+    <t>elc_spv_042</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 42</t>
+  </si>
+  <si>
+    <t>elc_spv_043</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 43</t>
+  </si>
+  <si>
+    <t>elc_spv_044</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 44</t>
+  </si>
+  <si>
+    <t>elc_spv_045</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 45</t>
+  </si>
+  <si>
+    <t>elc_spv_046</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 46</t>
+  </si>
+  <si>
+    <t>elc_spv_047</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 47</t>
+  </si>
+  <si>
+    <t>elc_spv_048</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 48</t>
+  </si>
+  <si>
+    <t>elc_spv_049</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 49</t>
+  </si>
+  <si>
+    <t>elc_spv_050</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 50</t>
+  </si>
+  <si>
+    <t>elc_spv_051</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 51</t>
+  </si>
+  <si>
+    <t>elc_spv_052</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 52</t>
+  </si>
+  <si>
+    <t>elc_spv_053</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 53</t>
+  </si>
+  <si>
+    <t>elc_spv_054</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 54</t>
+  </si>
+  <si>
+    <t>elc_spv_055</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 55</t>
+  </si>
+  <si>
+    <t>elc_spv_056</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 56</t>
+  </si>
+  <si>
+    <t>elc_spv_057</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 57</t>
+  </si>
+  <si>
+    <t>elc_spv_058</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 58</t>
+  </si>
+  <si>
+    <t>elc_spv_059</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 59</t>
+  </si>
+  <si>
+    <t>elc_spv_060</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 60</t>
+  </si>
+  <si>
+    <t>elc_spv_061</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 61</t>
+  </si>
+  <si>
+    <t>elc_spv_062</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 62</t>
+  </si>
+  <si>
+    <t>elc_spv_063</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 63</t>
+  </si>
+  <si>
+    <t>elc_spv_064</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 64</t>
+  </si>
+  <si>
+    <t>elc_spv_065</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 65</t>
+  </si>
+  <si>
+    <t>elc_spv_066</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 66</t>
+  </si>
+  <si>
+    <t>elc_spv_067</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 67</t>
+  </si>
+  <si>
+    <t>elc_spv_068</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 68</t>
+  </si>
+  <si>
+    <t>elc_spv_069</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 69</t>
+  </si>
+  <si>
+    <t>elc_spv_070</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 70</t>
+  </si>
+  <si>
+    <t>elc_spv_071</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 71</t>
+  </si>
+  <si>
+    <t>elc_spv_072</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 72</t>
+  </si>
+  <si>
+    <t>elc_spv_073</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 73</t>
+  </si>
+  <si>
+    <t>elc_spv_074</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 74</t>
+  </si>
+  <si>
+    <t>elc_spv_075</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 75</t>
+  </si>
+  <si>
+    <t>elc_spv_076</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 76</t>
+  </si>
+  <si>
+    <t>elc_spv_077</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 77</t>
+  </si>
+  <si>
+    <t>elc_spv_078</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 78</t>
+  </si>
+  <si>
+    <t>elc_spv_079</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 79</t>
+  </si>
+  <si>
+    <t>elc_spv_080</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 80</t>
+  </si>
+  <si>
+    <t>elc_spv_081</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 81</t>
+  </si>
+  <si>
+    <t>elc_spv_082</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 82</t>
+  </si>
+  <si>
+    <t>elc_spv_083</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 83</t>
+  </si>
+  <si>
+    <t>elc_spv_084</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 84</t>
+  </si>
+  <si>
+    <t>elc_spv_085</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 85</t>
+  </si>
+  <si>
+    <t>elc_spv_086</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 86</t>
+  </si>
+  <si>
+    <t>elc_spv_087</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 87</t>
+  </si>
+  <si>
+    <t>elc_spv_088</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 88</t>
+  </si>
+  <si>
+    <t>elc_spv_089</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 89</t>
+  </si>
+  <si>
+    <t>elc_spv_090</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 90</t>
+  </si>
+  <si>
+    <t>elc_spv_091</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 91</t>
+  </si>
+  <si>
+    <t>elc_spv_092</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 92</t>
+  </si>
+  <si>
+    <t>elc_spv_093</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 93</t>
+  </si>
+  <si>
+    <t>elc_spv_094</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 94</t>
+  </si>
+  <si>
+    <t>elc_spv_095</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 95</t>
+  </si>
+  <si>
+    <t>elc_spv_096</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 96</t>
+  </si>
+  <si>
+    <t>elc_spv_097</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 97</t>
+  </si>
+  <si>
+    <t>elc_spv_098</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 98</t>
+  </si>
+  <si>
+    <t>elc_spv_099</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 99</t>
+  </si>
+  <si>
+    <t>elc_spv_100</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 100</t>
+  </si>
+  <si>
+    <t>elc_spv_101</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 101</t>
+  </si>
+  <si>
+    <t>elc_spv_102</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 102</t>
+  </si>
+  <si>
+    <t>elc_spv_103</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 103</t>
+  </si>
+  <si>
+    <t>elc_spv_104</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 104</t>
+  </si>
+  <si>
+    <t>elc_spv_105</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 105</t>
+  </si>
+  <si>
+    <t>elc_spv_106</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 106</t>
+  </si>
+  <si>
+    <t>elc_spv_107</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 107</t>
+  </si>
+  <si>
+    <t>elc_spv_108</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 108</t>
+  </si>
+  <si>
+    <t>elc_spv_109</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 109</t>
+  </si>
+  <si>
+    <t>elc_spv_110</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 110</t>
+  </si>
+  <si>
+    <t>elc_spv_111</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 111</t>
+  </si>
+  <si>
+    <t>elc_spv_112</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 112</t>
+  </si>
+  <si>
+    <t>elc_spv_113</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 113</t>
+  </si>
+  <si>
+    <t>elc_spv_114</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 114</t>
+  </si>
+  <si>
+    <t>elc_spv_115</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 115</t>
+  </si>
+  <si>
+    <t>elc_spv_116</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 116</t>
+  </si>
+  <si>
+    <t>elc_spv_117</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 117</t>
+  </si>
+  <si>
+    <t>elc_spv_118</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 118</t>
+  </si>
+  <si>
+    <t>elc_spv_119</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 119</t>
+  </si>
+  <si>
+    <t>elc_spv_120</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 120</t>
+  </si>
+  <si>
+    <t>elc_spv_121</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 121</t>
+  </si>
+  <si>
+    <t>elc_spv_122</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 122</t>
+  </si>
+  <si>
+    <t>elc_spv_123</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 123</t>
+  </si>
+  <si>
+    <t>elc_spv_124</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 124</t>
+  </si>
+  <si>
+    <t>elc_spv_125</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 125</t>
+  </si>
+  <si>
+    <t>elc_spv_126</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 126</t>
+  </si>
+  <si>
+    <t>elc_spv_127</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 127</t>
+  </si>
+  <si>
+    <t>elc_spv_128</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 128</t>
+  </si>
+  <si>
+    <t>elc_spv_129</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 129</t>
+  </si>
+  <si>
+    <t>elc_spv_130</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 130</t>
+  </si>
+  <si>
+    <t>elc_spv_131</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 131</t>
+  </si>
+  <si>
+    <t>elc_spv_132</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 132</t>
+  </si>
+  <si>
+    <t>elc_spv_133</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 133</t>
+  </si>
+  <si>
+    <t>elc_spv_134</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 134</t>
+  </si>
+  <si>
+    <t>elc_spv_135</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 135</t>
+  </si>
+  <si>
+    <t>elc_spv_136</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 136</t>
+  </si>
+  <si>
+    <t>elc_wof_001</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 1</t>
+  </si>
+  <si>
+    <t>elc_wof_002</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 2</t>
+  </si>
+  <si>
+    <t>elc_wof_003</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 3</t>
+  </si>
+  <si>
+    <t>elc_wof_004</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 4</t>
+  </si>
+  <si>
+    <t>elc_wof_005</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 5</t>
+  </si>
+  <si>
+    <t>elc_wof_006</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 6</t>
+  </si>
+  <si>
+    <t>elc_wof_007</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 7</t>
+  </si>
+  <si>
+    <t>elc_wof_008</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 8</t>
+  </si>
+  <si>
+    <t>elc_wof_009</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 9</t>
+  </si>
+  <si>
+    <t>elc_wof_010</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 10</t>
+  </si>
+  <si>
+    <t>elc_wof_011</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 11</t>
+  </si>
+  <si>
+    <t>elc_wof_012</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 12</t>
+  </si>
+  <si>
+    <t>elc_wof_013</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 13</t>
+  </si>
+  <si>
+    <t>elc_wof_014</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 14</t>
+  </si>
+  <si>
+    <t>elc_wof_015</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 15</t>
+  </si>
+  <si>
+    <t>elc_wof_016</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 16</t>
+  </si>
+  <si>
+    <t>elc_wof_017</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 17</t>
+  </si>
+  <si>
+    <t>elc_wof_018</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 18</t>
+  </si>
+  <si>
+    <t>elc_wof_019</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 19</t>
+  </si>
+  <si>
+    <t>elc_wof_020</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 20</t>
+  </si>
+  <si>
+    <t>elc_wof_021</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 21</t>
+  </si>
+  <si>
+    <t>elc_wof_022</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 22</t>
+  </si>
+  <si>
+    <t>elc_wof_023</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 23</t>
+  </si>
+  <si>
+    <t>elc_wof_024</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 24</t>
+  </si>
+  <si>
+    <t>elc_wof_025</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 25</t>
+  </si>
+  <si>
+    <t>elc_wof_026</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 26</t>
+  </si>
+  <si>
+    <t>elc_wof_027</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 27</t>
+  </si>
+  <si>
+    <t>elc_wof_028</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 28</t>
+  </si>
+  <si>
+    <t>elc_wof_029</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 29</t>
+  </si>
+  <si>
+    <t>elc_wof_030</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 30</t>
+  </si>
+  <si>
+    <t>elc_wof_031</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 31</t>
+  </si>
+  <si>
+    <t>elc_wof_032</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 32</t>
+  </si>
+  <si>
+    <t>elc_wof_033</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 33</t>
+  </si>
+  <si>
+    <t>elc_wof_034</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 34</t>
+  </si>
+  <si>
+    <t>elc_won_001</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 1</t>
+  </si>
+  <si>
+    <t>elc_won_002</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 2</t>
+  </si>
+  <si>
+    <t>elc_won_003</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 3</t>
+  </si>
+  <si>
+    <t>elc_won_004</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 4</t>
+  </si>
+  <si>
+    <t>elc_won_005</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 5</t>
+  </si>
+  <si>
+    <t>elc_won_006</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 6</t>
+  </si>
+  <si>
+    <t>elc_won_007</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 7</t>
+  </si>
+  <si>
+    <t>elc_won_008</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 8</t>
+  </si>
+  <si>
+    <t>elc_won_009</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 9</t>
+  </si>
+  <si>
+    <t>elc_won_010</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 10</t>
+  </si>
+  <si>
+    <t>elc_won_011</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 11</t>
+  </si>
+  <si>
+    <t>elc_won_012</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 12</t>
+  </si>
+  <si>
+    <t>elc_won_013</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 13</t>
+  </si>
+  <si>
+    <t>elc_won_014</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 14</t>
+  </si>
+  <si>
+    <t>elc_won_015</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 15</t>
+  </si>
+  <si>
+    <t>elc_won_016</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 16</t>
+  </si>
+  <si>
+    <t>elc_won_017</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 17</t>
+  </si>
+  <si>
+    <t>elc_won_018</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 18</t>
+  </si>
+  <si>
+    <t>elc_won_019</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 19</t>
+  </si>
+  <si>
+    <t>elc_won_020</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 20</t>
+  </si>
+  <si>
+    <t>elc_won_021</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 21</t>
+  </si>
+  <si>
+    <t>elc_won_022</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 22</t>
+  </si>
+  <si>
+    <t>elc_won_023</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 23</t>
+  </si>
+  <si>
+    <t>elc_won_024</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 24</t>
+  </si>
+  <si>
+    <t>elc_won_025</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 25</t>
+  </si>
+  <si>
+    <t>elc_won_026</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 26</t>
+  </si>
+  <si>
+    <t>elc_won_027</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 27</t>
+  </si>
+  <si>
+    <t>elc_won_028</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 28</t>
+  </si>
+  <si>
+    <t>elc_won_029</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 29</t>
+  </si>
+  <si>
+    <t>elc_won_030</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 30</t>
+  </si>
+  <si>
+    <t>elc_won_031</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 31</t>
+  </si>
+  <si>
+    <t>elc_won_032</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 32</t>
+  </si>
+  <si>
+    <t>elc_won_033</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 33</t>
+  </si>
+  <si>
+    <t>elc_won_034</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 34</t>
+  </si>
+  <si>
+    <t>elc_won_035</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 35</t>
+  </si>
+  <si>
+    <t>elc_won_036</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 36</t>
+  </si>
+  <si>
+    <t>elc_won_037</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 37</t>
+  </si>
+  <si>
+    <t>elc_won_038</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 38</t>
+  </si>
+  <si>
+    <t>elc_won_039</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 39</t>
+  </si>
+  <si>
+    <t>elc_won_040</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 40</t>
+  </si>
+  <si>
+    <t>elc_won_041</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 41</t>
+  </si>
+  <si>
+    <t>elc_won_042</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 42</t>
+  </si>
+  <si>
+    <t>elc_won_043</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 43</t>
+  </si>
+  <si>
+    <t>elc_won_044</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 44</t>
+  </si>
+  <si>
+    <t>elc_won_045</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 45</t>
+  </si>
+  <si>
+    <t>elc_won_046</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 46</t>
+  </si>
+  <si>
+    <t>elc_won_047</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 47</t>
+  </si>
+  <si>
+    <t>elc_won_048</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 48</t>
+  </si>
+  <si>
+    <t>elc_won_049</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 49</t>
+  </si>
+  <si>
+    <t>elc_won_050</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 50</t>
+  </si>
+  <si>
+    <t>elc_won_051</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 51</t>
+  </si>
+  <si>
+    <t>elc_won_052</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 52</t>
+  </si>
+  <si>
+    <t>elc_won_053</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 53</t>
+  </si>
+  <si>
+    <t>elc_won_054</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 54</t>
+  </si>
+  <si>
+    <t>elc_won_055</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 55</t>
+  </si>
+  <si>
+    <t>elc_won_056</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 56</t>
+  </si>
+  <si>
+    <t>elc_won_057</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 57</t>
+  </si>
+  <si>
+    <t>elc_won_058</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 58</t>
+  </si>
+  <si>
+    <t>elc_won_059</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 59</t>
+  </si>
+  <si>
+    <t>elc_won_060</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 60</t>
+  </si>
+  <si>
+    <t>elc_won_061</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 61</t>
+  </si>
+  <si>
+    <t>elc_won_062</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 62</t>
+  </si>
+  <si>
+    <t>elc_won_063</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 63</t>
+  </si>
+  <si>
+    <t>elc_won_064</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 64</t>
+  </si>
+  <si>
+    <t>elc_won_065</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 65</t>
+  </si>
+  <si>
+    <t>elc_won_066</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 66</t>
+  </si>
+  <si>
+    <t>elc_won_067</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 67</t>
+  </si>
+  <si>
+    <t>elc_won_068</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 68</t>
+  </si>
+  <si>
+    <t>elc_won_069</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 69</t>
+  </si>
+  <si>
+    <t>elc_won_070</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 70</t>
+  </si>
+  <si>
+    <t>elc_won_071</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 71</t>
+  </si>
+  <si>
+    <t>elc_won_072</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 72</t>
+  </si>
+  <si>
+    <t>elc_won_073</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 73</t>
+  </si>
+  <si>
+    <t>elc_won_074</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 74</t>
+  </si>
+  <si>
+    <t>elc_won_075</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 75</t>
+  </si>
+  <si>
+    <t>elc_won_076</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 76</t>
+  </si>
+  <si>
+    <t>elc_won_077</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 77</t>
+  </si>
+  <si>
+    <t>elc_won_078</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 78</t>
+  </si>
+  <si>
+    <t>elc_won_079</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 79</t>
+  </si>
+  <si>
+    <t>elc_won_080</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 80</t>
+  </si>
+  <si>
+    <t>elc_won_081</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 81</t>
+  </si>
+  <si>
+    <t>elc_won_082</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 82</t>
+  </si>
+  <si>
+    <t>elc_won_083</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 83</t>
+  </si>
+  <si>
+    <t>elc_won_084</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 84</t>
+  </si>
+  <si>
+    <t>elc_won_085</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 85</t>
+  </si>
+  <si>
+    <t>elc_won_086</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 86</t>
+  </si>
+  <si>
+    <t>elc_won_087</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 87</t>
+  </si>
+  <si>
+    <t>elc_won_088</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 88</t>
+  </si>
+  <si>
+    <t>elc_won_089</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 89</t>
+  </si>
+  <si>
+    <t>elc_won_090</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 90</t>
+  </si>
+  <si>
+    <t>elc_won_091</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 91</t>
+  </si>
+  <si>
+    <t>elc_won_092</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 92</t>
+  </si>
+  <si>
+    <t>elc_won_093</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 93</t>
+  </si>
+  <si>
+    <t>elc_won_094</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 94</t>
+  </si>
+  <si>
+    <t>elc_won_095</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 95</t>
+  </si>
+  <si>
+    <t>elc_won_096</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 96</t>
+  </si>
+  <si>
+    <t>elc_won_097</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 97</t>
+  </si>
+  <si>
+    <t>elc_won_098</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 98</t>
+  </si>
+  <si>
+    <t>elc_won_099</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 99</t>
+  </si>
+  <si>
+    <t>elc_won_100</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 100</t>
+  </si>
+  <si>
+    <t>elc_won_101</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 101</t>
+  </si>
+  <si>
+    <t>elc_won_102</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 102</t>
+  </si>
+  <si>
+    <t>elc_won_103</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 103</t>
+  </si>
+  <si>
+    <t>elc_won_104</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 104</t>
+  </si>
+  <si>
+    <t>elc_won_105</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 105</t>
+  </si>
+  <si>
+    <t>elc_won_106</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 106</t>
+  </si>
+  <si>
+    <t>elc_won_107</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 107</t>
+  </si>
+  <si>
+    <t>elc_won_108</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 108</t>
+  </si>
+  <si>
+    <t>elc_won_109</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 109</t>
+  </si>
+  <si>
+    <t>elc_won_110</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 110</t>
+  </si>
+  <si>
+    <t>elc_won_111</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 111</t>
+  </si>
+  <si>
+    <t>elc_won_112</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 112</t>
+  </si>
+  <si>
+    <t>elc_won_113</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 113</t>
+  </si>
+  <si>
+    <t>elc_won_114</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 114</t>
   </si>
 </sst>
 </file>
@@ -3116,7 +4802,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2F298A9-BCD9-4ABF-BE3B-9D1BDD3E7001}">
-  <dimension ref="B3:R24"/>
+  <dimension ref="B3:R288"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="11.19921875" bestFit="1" customWidth="1"/>
@@ -3289,6 +4975,24 @@
       <c r="E8" t="s">
         <v>18</v>
       </c>
+      <c r="M8" t="s">
+        <v>17</v>
+      </c>
+      <c r="N8" t="s">
+        <v>221</v>
+      </c>
+      <c r="O8" t="s">
+        <v>222</v>
+      </c>
+      <c r="P8" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>35</v>
+      </c>
+      <c r="R8" t="s">
+        <v>216</v>
+      </c>
     </row>
     <row r="9" spans="2:18">
       <c r="B9" t="s">
@@ -3300,6 +5004,24 @@
       <c r="E9" t="s">
         <v>18</v>
       </c>
+      <c r="M9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N9" t="s">
+        <v>223</v>
+      </c>
+      <c r="O9" t="s">
+        <v>224</v>
+      </c>
+      <c r="P9" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>35</v>
+      </c>
+      <c r="R9" t="s">
+        <v>216</v>
+      </c>
     </row>
     <row r="10" spans="2:18">
       <c r="B10" t="s">
@@ -3311,6 +5033,24 @@
       <c r="E10" t="s">
         <v>18</v>
       </c>
+      <c r="M10" t="s">
+        <v>17</v>
+      </c>
+      <c r="N10" t="s">
+        <v>225</v>
+      </c>
+      <c r="O10" t="s">
+        <v>226</v>
+      </c>
+      <c r="P10" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>35</v>
+      </c>
+      <c r="R10" t="s">
+        <v>216</v>
+      </c>
     </row>
     <row r="11" spans="2:18">
       <c r="B11" t="s">
@@ -3322,6 +5062,24 @@
       <c r="E11" t="s">
         <v>18</v>
       </c>
+      <c r="M11" t="s">
+        <v>17</v>
+      </c>
+      <c r="N11" t="s">
+        <v>227</v>
+      </c>
+      <c r="O11" t="s">
+        <v>228</v>
+      </c>
+      <c r="P11" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>35</v>
+      </c>
+      <c r="R11" t="s">
+        <v>216</v>
+      </c>
     </row>
     <row r="12" spans="2:18">
       <c r="B12" t="s">
@@ -3333,6 +5091,24 @@
       <c r="E12" t="s">
         <v>18</v>
       </c>
+      <c r="M12" t="s">
+        <v>17</v>
+      </c>
+      <c r="N12" t="s">
+        <v>229</v>
+      </c>
+      <c r="O12" t="s">
+        <v>230</v>
+      </c>
+      <c r="P12" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>35</v>
+      </c>
+      <c r="R12" t="s">
+        <v>216</v>
+      </c>
     </row>
     <row r="13" spans="2:18">
       <c r="B13" t="s">
@@ -3344,6 +5120,24 @@
       <c r="E13" t="s">
         <v>18</v>
       </c>
+      <c r="M13" t="s">
+        <v>17</v>
+      </c>
+      <c r="N13" t="s">
+        <v>231</v>
+      </c>
+      <c r="O13" t="s">
+        <v>232</v>
+      </c>
+      <c r="P13" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>35</v>
+      </c>
+      <c r="R13" t="s">
+        <v>216</v>
+      </c>
     </row>
     <row r="14" spans="2:18">
       <c r="B14" t="s">
@@ -3358,6 +5152,24 @@
       <c r="E14" t="s">
         <v>18</v>
       </c>
+      <c r="M14" t="s">
+        <v>17</v>
+      </c>
+      <c r="N14" t="s">
+        <v>233</v>
+      </c>
+      <c r="O14" t="s">
+        <v>234</v>
+      </c>
+      <c r="P14" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>35</v>
+      </c>
+      <c r="R14" t="s">
+        <v>216</v>
+      </c>
     </row>
     <row r="15" spans="2:18">
       <c r="B15" t="s">
@@ -3372,6 +5184,24 @@
       <c r="E15" t="s">
         <v>18</v>
       </c>
+      <c r="M15" t="s">
+        <v>17</v>
+      </c>
+      <c r="N15" t="s">
+        <v>235</v>
+      </c>
+      <c r="O15" t="s">
+        <v>236</v>
+      </c>
+      <c r="P15" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>35</v>
+      </c>
+      <c r="R15" t="s">
+        <v>216</v>
+      </c>
     </row>
     <row r="16" spans="2:18">
       <c r="B16" t="s">
@@ -3395,8 +5225,26 @@
       <c r="I16" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="17" spans="2:7">
+      <c r="M16" t="s">
+        <v>17</v>
+      </c>
+      <c r="N16" t="s">
+        <v>237</v>
+      </c>
+      <c r="O16" t="s">
+        <v>238</v>
+      </c>
+      <c r="P16" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>35</v>
+      </c>
+      <c r="R16" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="17" spans="2:18">
       <c r="B17" t="s">
         <v>34</v>
       </c>
@@ -3409,8 +5257,26 @@
       <c r="E17" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="18" spans="2:7">
+      <c r="M17" t="s">
+        <v>17</v>
+      </c>
+      <c r="N17" t="s">
+        <v>239</v>
+      </c>
+      <c r="O17" t="s">
+        <v>240</v>
+      </c>
+      <c r="P17" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>35</v>
+      </c>
+      <c r="R17" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="18" spans="2:18">
       <c r="B18" t="s">
         <v>34</v>
       </c>
@@ -3423,8 +5289,26 @@
       <c r="E18" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="19" spans="2:7">
+      <c r="M18" t="s">
+        <v>17</v>
+      </c>
+      <c r="N18" t="s">
+        <v>241</v>
+      </c>
+      <c r="O18" t="s">
+        <v>242</v>
+      </c>
+      <c r="P18" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>35</v>
+      </c>
+      <c r="R18" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="19" spans="2:18">
       <c r="B19" t="s">
         <v>34</v>
       </c>
@@ -3437,8 +5321,26 @@
       <c r="E19" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="20" spans="2:7">
+      <c r="M19" t="s">
+        <v>17</v>
+      </c>
+      <c r="N19" t="s">
+        <v>243</v>
+      </c>
+      <c r="O19" t="s">
+        <v>244</v>
+      </c>
+      <c r="P19" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>35</v>
+      </c>
+      <c r="R19" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="20" spans="2:18">
       <c r="B20" t="s">
         <v>34</v>
       </c>
@@ -3451,8 +5353,26 @@
       <c r="E20" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="21" spans="2:7">
+      <c r="M20" t="s">
+        <v>17</v>
+      </c>
+      <c r="N20" t="s">
+        <v>245</v>
+      </c>
+      <c r="O20" t="s">
+        <v>246</v>
+      </c>
+      <c r="P20" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>35</v>
+      </c>
+      <c r="R20" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="21" spans="2:18">
       <c r="B21" t="s">
         <v>17</v>
       </c>
@@ -3471,8 +5391,26 @@
       <c r="G21" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="22" spans="2:7">
+      <c r="M21" t="s">
+        <v>17</v>
+      </c>
+      <c r="N21" t="s">
+        <v>247</v>
+      </c>
+      <c r="O21" t="s">
+        <v>248</v>
+      </c>
+      <c r="P21" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>35</v>
+      </c>
+      <c r="R21" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="22" spans="2:18">
       <c r="B22" t="s">
         <v>193</v>
       </c>
@@ -3485,8 +5423,26 @@
       <c r="E22" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="23" spans="2:7">
+      <c r="M22" t="s">
+        <v>17</v>
+      </c>
+      <c r="N22" t="s">
+        <v>249</v>
+      </c>
+      <c r="O22" t="s">
+        <v>250</v>
+      </c>
+      <c r="P22" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>35</v>
+      </c>
+      <c r="R22" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="23" spans="2:18">
       <c r="B23" t="s">
         <v>193</v>
       </c>
@@ -3496,8 +5452,26 @@
       <c r="E23" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="24" spans="2:7">
+      <c r="M23" t="s">
+        <v>17</v>
+      </c>
+      <c r="N23" t="s">
+        <v>251</v>
+      </c>
+      <c r="O23" t="s">
+        <v>252</v>
+      </c>
+      <c r="P23" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>35</v>
+      </c>
+      <c r="R23" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="24" spans="2:18">
       <c r="B24" t="s">
         <v>193</v>
       </c>
@@ -3506,6 +5480,5304 @@
       </c>
       <c r="E24" t="s">
         <v>196</v>
+      </c>
+      <c r="M24" t="s">
+        <v>17</v>
+      </c>
+      <c r="N24" t="s">
+        <v>253</v>
+      </c>
+      <c r="O24" t="s">
+        <v>254</v>
+      </c>
+      <c r="P24" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>35</v>
+      </c>
+      <c r="R24" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="25" spans="2:18">
+      <c r="M25" t="s">
+        <v>17</v>
+      </c>
+      <c r="N25" t="s">
+        <v>255</v>
+      </c>
+      <c r="O25" t="s">
+        <v>256</v>
+      </c>
+      <c r="P25" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>35</v>
+      </c>
+      <c r="R25" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="26" spans="2:18">
+      <c r="M26" t="s">
+        <v>17</v>
+      </c>
+      <c r="N26" t="s">
+        <v>257</v>
+      </c>
+      <c r="O26" t="s">
+        <v>258</v>
+      </c>
+      <c r="P26" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>35</v>
+      </c>
+      <c r="R26" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="27" spans="2:18">
+      <c r="M27" t="s">
+        <v>17</v>
+      </c>
+      <c r="N27" t="s">
+        <v>259</v>
+      </c>
+      <c r="O27" t="s">
+        <v>260</v>
+      </c>
+      <c r="P27" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>35</v>
+      </c>
+      <c r="R27" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="28" spans="2:18">
+      <c r="M28" t="s">
+        <v>17</v>
+      </c>
+      <c r="N28" t="s">
+        <v>261</v>
+      </c>
+      <c r="O28" t="s">
+        <v>262</v>
+      </c>
+      <c r="P28" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>35</v>
+      </c>
+      <c r="R28" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="29" spans="2:18">
+      <c r="M29" t="s">
+        <v>17</v>
+      </c>
+      <c r="N29" t="s">
+        <v>263</v>
+      </c>
+      <c r="O29" t="s">
+        <v>264</v>
+      </c>
+      <c r="P29" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>35</v>
+      </c>
+      <c r="R29" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="30" spans="2:18">
+      <c r="M30" t="s">
+        <v>17</v>
+      </c>
+      <c r="N30" t="s">
+        <v>265</v>
+      </c>
+      <c r="O30" t="s">
+        <v>266</v>
+      </c>
+      <c r="P30" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>35</v>
+      </c>
+      <c r="R30" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="31" spans="2:18">
+      <c r="M31" t="s">
+        <v>17</v>
+      </c>
+      <c r="N31" t="s">
+        <v>267</v>
+      </c>
+      <c r="O31" t="s">
+        <v>268</v>
+      </c>
+      <c r="P31" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>35</v>
+      </c>
+      <c r="R31" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="32" spans="2:18">
+      <c r="M32" t="s">
+        <v>17</v>
+      </c>
+      <c r="N32" t="s">
+        <v>269</v>
+      </c>
+      <c r="O32" t="s">
+        <v>270</v>
+      </c>
+      <c r="P32" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>35</v>
+      </c>
+      <c r="R32" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="33" spans="13:18">
+      <c r="M33" t="s">
+        <v>17</v>
+      </c>
+      <c r="N33" t="s">
+        <v>271</v>
+      </c>
+      <c r="O33" t="s">
+        <v>272</v>
+      </c>
+      <c r="P33" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>35</v>
+      </c>
+      <c r="R33" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="34" spans="13:18">
+      <c r="M34" t="s">
+        <v>17</v>
+      </c>
+      <c r="N34" t="s">
+        <v>273</v>
+      </c>
+      <c r="O34" t="s">
+        <v>274</v>
+      </c>
+      <c r="P34" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>35</v>
+      </c>
+      <c r="R34" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="35" spans="13:18">
+      <c r="M35" t="s">
+        <v>17</v>
+      </c>
+      <c r="N35" t="s">
+        <v>275</v>
+      </c>
+      <c r="O35" t="s">
+        <v>276</v>
+      </c>
+      <c r="P35" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q35" t="s">
+        <v>35</v>
+      </c>
+      <c r="R35" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="36" spans="13:18">
+      <c r="M36" t="s">
+        <v>17</v>
+      </c>
+      <c r="N36" t="s">
+        <v>277</v>
+      </c>
+      <c r="O36" t="s">
+        <v>278</v>
+      </c>
+      <c r="P36" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>35</v>
+      </c>
+      <c r="R36" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="37" spans="13:18">
+      <c r="M37" t="s">
+        <v>17</v>
+      </c>
+      <c r="N37" t="s">
+        <v>279</v>
+      </c>
+      <c r="O37" t="s">
+        <v>280</v>
+      </c>
+      <c r="P37" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q37" t="s">
+        <v>35</v>
+      </c>
+      <c r="R37" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="38" spans="13:18">
+      <c r="M38" t="s">
+        <v>17</v>
+      </c>
+      <c r="N38" t="s">
+        <v>281</v>
+      </c>
+      <c r="O38" t="s">
+        <v>282</v>
+      </c>
+      <c r="P38" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q38" t="s">
+        <v>35</v>
+      </c>
+      <c r="R38" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="39" spans="13:18">
+      <c r="M39" t="s">
+        <v>17</v>
+      </c>
+      <c r="N39" t="s">
+        <v>283</v>
+      </c>
+      <c r="O39" t="s">
+        <v>284</v>
+      </c>
+      <c r="P39" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>35</v>
+      </c>
+      <c r="R39" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="40" spans="13:18">
+      <c r="M40" t="s">
+        <v>17</v>
+      </c>
+      <c r="N40" t="s">
+        <v>285</v>
+      </c>
+      <c r="O40" t="s">
+        <v>286</v>
+      </c>
+      <c r="P40" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>35</v>
+      </c>
+      <c r="R40" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="41" spans="13:18">
+      <c r="M41" t="s">
+        <v>17</v>
+      </c>
+      <c r="N41" t="s">
+        <v>287</v>
+      </c>
+      <c r="O41" t="s">
+        <v>288</v>
+      </c>
+      <c r="P41" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q41" t="s">
+        <v>35</v>
+      </c>
+      <c r="R41" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="42" spans="13:18">
+      <c r="M42" t="s">
+        <v>17</v>
+      </c>
+      <c r="N42" t="s">
+        <v>289</v>
+      </c>
+      <c r="O42" t="s">
+        <v>290</v>
+      </c>
+      <c r="P42" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q42" t="s">
+        <v>35</v>
+      </c>
+      <c r="R42" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="43" spans="13:18">
+      <c r="M43" t="s">
+        <v>17</v>
+      </c>
+      <c r="N43" t="s">
+        <v>291</v>
+      </c>
+      <c r="O43" t="s">
+        <v>292</v>
+      </c>
+      <c r="P43" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q43" t="s">
+        <v>35</v>
+      </c>
+      <c r="R43" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="44" spans="13:18">
+      <c r="M44" t="s">
+        <v>17</v>
+      </c>
+      <c r="N44" t="s">
+        <v>293</v>
+      </c>
+      <c r="O44" t="s">
+        <v>294</v>
+      </c>
+      <c r="P44" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q44" t="s">
+        <v>35</v>
+      </c>
+      <c r="R44" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="45" spans="13:18">
+      <c r="M45" t="s">
+        <v>17</v>
+      </c>
+      <c r="N45" t="s">
+        <v>295</v>
+      </c>
+      <c r="O45" t="s">
+        <v>296</v>
+      </c>
+      <c r="P45" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q45" t="s">
+        <v>35</v>
+      </c>
+      <c r="R45" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="46" spans="13:18">
+      <c r="M46" t="s">
+        <v>17</v>
+      </c>
+      <c r="N46" t="s">
+        <v>297</v>
+      </c>
+      <c r="O46" t="s">
+        <v>298</v>
+      </c>
+      <c r="P46" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q46" t="s">
+        <v>35</v>
+      </c>
+      <c r="R46" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="47" spans="13:18">
+      <c r="M47" t="s">
+        <v>17</v>
+      </c>
+      <c r="N47" t="s">
+        <v>299</v>
+      </c>
+      <c r="O47" t="s">
+        <v>300</v>
+      </c>
+      <c r="P47" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q47" t="s">
+        <v>35</v>
+      </c>
+      <c r="R47" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="48" spans="13:18">
+      <c r="M48" t="s">
+        <v>17</v>
+      </c>
+      <c r="N48" t="s">
+        <v>301</v>
+      </c>
+      <c r="O48" t="s">
+        <v>302</v>
+      </c>
+      <c r="P48" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q48" t="s">
+        <v>35</v>
+      </c>
+      <c r="R48" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="49" spans="13:18">
+      <c r="M49" t="s">
+        <v>17</v>
+      </c>
+      <c r="N49" t="s">
+        <v>303</v>
+      </c>
+      <c r="O49" t="s">
+        <v>304</v>
+      </c>
+      <c r="P49" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q49" t="s">
+        <v>35</v>
+      </c>
+      <c r="R49" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="50" spans="13:18">
+      <c r="M50" t="s">
+        <v>17</v>
+      </c>
+      <c r="N50" t="s">
+        <v>305</v>
+      </c>
+      <c r="O50" t="s">
+        <v>306</v>
+      </c>
+      <c r="P50" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q50" t="s">
+        <v>35</v>
+      </c>
+      <c r="R50" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="51" spans="13:18">
+      <c r="M51" t="s">
+        <v>17</v>
+      </c>
+      <c r="N51" t="s">
+        <v>307</v>
+      </c>
+      <c r="O51" t="s">
+        <v>308</v>
+      </c>
+      <c r="P51" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q51" t="s">
+        <v>35</v>
+      </c>
+      <c r="R51" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="52" spans="13:18">
+      <c r="M52" t="s">
+        <v>17</v>
+      </c>
+      <c r="N52" t="s">
+        <v>309</v>
+      </c>
+      <c r="O52" t="s">
+        <v>310</v>
+      </c>
+      <c r="P52" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q52" t="s">
+        <v>35</v>
+      </c>
+      <c r="R52" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="53" spans="13:18">
+      <c r="M53" t="s">
+        <v>17</v>
+      </c>
+      <c r="N53" t="s">
+        <v>311</v>
+      </c>
+      <c r="O53" t="s">
+        <v>312</v>
+      </c>
+      <c r="P53" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q53" t="s">
+        <v>35</v>
+      </c>
+      <c r="R53" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="54" spans="13:18">
+      <c r="M54" t="s">
+        <v>17</v>
+      </c>
+      <c r="N54" t="s">
+        <v>313</v>
+      </c>
+      <c r="O54" t="s">
+        <v>314</v>
+      </c>
+      <c r="P54" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q54" t="s">
+        <v>35</v>
+      </c>
+      <c r="R54" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="55" spans="13:18">
+      <c r="M55" t="s">
+        <v>17</v>
+      </c>
+      <c r="N55" t="s">
+        <v>315</v>
+      </c>
+      <c r="O55" t="s">
+        <v>316</v>
+      </c>
+      <c r="P55" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q55" t="s">
+        <v>35</v>
+      </c>
+      <c r="R55" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="56" spans="13:18">
+      <c r="M56" t="s">
+        <v>17</v>
+      </c>
+      <c r="N56" t="s">
+        <v>317</v>
+      </c>
+      <c r="O56" t="s">
+        <v>318</v>
+      </c>
+      <c r="P56" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q56" t="s">
+        <v>35</v>
+      </c>
+      <c r="R56" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="57" spans="13:18">
+      <c r="M57" t="s">
+        <v>17</v>
+      </c>
+      <c r="N57" t="s">
+        <v>319</v>
+      </c>
+      <c r="O57" t="s">
+        <v>320</v>
+      </c>
+      <c r="P57" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q57" t="s">
+        <v>35</v>
+      </c>
+      <c r="R57" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="58" spans="13:18">
+      <c r="M58" t="s">
+        <v>17</v>
+      </c>
+      <c r="N58" t="s">
+        <v>321</v>
+      </c>
+      <c r="O58" t="s">
+        <v>322</v>
+      </c>
+      <c r="P58" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q58" t="s">
+        <v>35</v>
+      </c>
+      <c r="R58" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="59" spans="13:18">
+      <c r="M59" t="s">
+        <v>17</v>
+      </c>
+      <c r="N59" t="s">
+        <v>323</v>
+      </c>
+      <c r="O59" t="s">
+        <v>324</v>
+      </c>
+      <c r="P59" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q59" t="s">
+        <v>35</v>
+      </c>
+      <c r="R59" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="60" spans="13:18">
+      <c r="M60" t="s">
+        <v>17</v>
+      </c>
+      <c r="N60" t="s">
+        <v>325</v>
+      </c>
+      <c r="O60" t="s">
+        <v>326</v>
+      </c>
+      <c r="P60" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q60" t="s">
+        <v>35</v>
+      </c>
+      <c r="R60" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="61" spans="13:18">
+      <c r="M61" t="s">
+        <v>17</v>
+      </c>
+      <c r="N61" t="s">
+        <v>327</v>
+      </c>
+      <c r="O61" t="s">
+        <v>328</v>
+      </c>
+      <c r="P61" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q61" t="s">
+        <v>35</v>
+      </c>
+      <c r="R61" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="62" spans="13:18">
+      <c r="M62" t="s">
+        <v>17</v>
+      </c>
+      <c r="N62" t="s">
+        <v>329</v>
+      </c>
+      <c r="O62" t="s">
+        <v>330</v>
+      </c>
+      <c r="P62" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q62" t="s">
+        <v>35</v>
+      </c>
+      <c r="R62" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="63" spans="13:18">
+      <c r="M63" t="s">
+        <v>17</v>
+      </c>
+      <c r="N63" t="s">
+        <v>331</v>
+      </c>
+      <c r="O63" t="s">
+        <v>332</v>
+      </c>
+      <c r="P63" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q63" t="s">
+        <v>35</v>
+      </c>
+      <c r="R63" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="64" spans="13:18">
+      <c r="M64" t="s">
+        <v>17</v>
+      </c>
+      <c r="N64" t="s">
+        <v>333</v>
+      </c>
+      <c r="O64" t="s">
+        <v>334</v>
+      </c>
+      <c r="P64" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q64" t="s">
+        <v>35</v>
+      </c>
+      <c r="R64" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="65" spans="13:18">
+      <c r="M65" t="s">
+        <v>17</v>
+      </c>
+      <c r="N65" t="s">
+        <v>335</v>
+      </c>
+      <c r="O65" t="s">
+        <v>336</v>
+      </c>
+      <c r="P65" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q65" t="s">
+        <v>35</v>
+      </c>
+      <c r="R65" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="66" spans="13:18">
+      <c r="M66" t="s">
+        <v>17</v>
+      </c>
+      <c r="N66" t="s">
+        <v>337</v>
+      </c>
+      <c r="O66" t="s">
+        <v>338</v>
+      </c>
+      <c r="P66" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q66" t="s">
+        <v>35</v>
+      </c>
+      <c r="R66" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="67" spans="13:18">
+      <c r="M67" t="s">
+        <v>17</v>
+      </c>
+      <c r="N67" t="s">
+        <v>339</v>
+      </c>
+      <c r="O67" t="s">
+        <v>340</v>
+      </c>
+      <c r="P67" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q67" t="s">
+        <v>35</v>
+      </c>
+      <c r="R67" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="68" spans="13:18">
+      <c r="M68" t="s">
+        <v>17</v>
+      </c>
+      <c r="N68" t="s">
+        <v>341</v>
+      </c>
+      <c r="O68" t="s">
+        <v>342</v>
+      </c>
+      <c r="P68" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q68" t="s">
+        <v>35</v>
+      </c>
+      <c r="R68" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="69" spans="13:18">
+      <c r="M69" t="s">
+        <v>17</v>
+      </c>
+      <c r="N69" t="s">
+        <v>343</v>
+      </c>
+      <c r="O69" t="s">
+        <v>344</v>
+      </c>
+      <c r="P69" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q69" t="s">
+        <v>35</v>
+      </c>
+      <c r="R69" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="70" spans="13:18">
+      <c r="M70" t="s">
+        <v>17</v>
+      </c>
+      <c r="N70" t="s">
+        <v>345</v>
+      </c>
+      <c r="O70" t="s">
+        <v>346</v>
+      </c>
+      <c r="P70" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q70" t="s">
+        <v>35</v>
+      </c>
+      <c r="R70" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="71" spans="13:18">
+      <c r="M71" t="s">
+        <v>17</v>
+      </c>
+      <c r="N71" t="s">
+        <v>347</v>
+      </c>
+      <c r="O71" t="s">
+        <v>348</v>
+      </c>
+      <c r="P71" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q71" t="s">
+        <v>35</v>
+      </c>
+      <c r="R71" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="72" spans="13:18">
+      <c r="M72" t="s">
+        <v>17</v>
+      </c>
+      <c r="N72" t="s">
+        <v>349</v>
+      </c>
+      <c r="O72" t="s">
+        <v>350</v>
+      </c>
+      <c r="P72" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q72" t="s">
+        <v>35</v>
+      </c>
+      <c r="R72" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="73" spans="13:18">
+      <c r="M73" t="s">
+        <v>17</v>
+      </c>
+      <c r="N73" t="s">
+        <v>351</v>
+      </c>
+      <c r="O73" t="s">
+        <v>352</v>
+      </c>
+      <c r="P73" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q73" t="s">
+        <v>35</v>
+      </c>
+      <c r="R73" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="74" spans="13:18">
+      <c r="M74" t="s">
+        <v>17</v>
+      </c>
+      <c r="N74" t="s">
+        <v>353</v>
+      </c>
+      <c r="O74" t="s">
+        <v>354</v>
+      </c>
+      <c r="P74" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q74" t="s">
+        <v>35</v>
+      </c>
+      <c r="R74" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="75" spans="13:18">
+      <c r="M75" t="s">
+        <v>17</v>
+      </c>
+      <c r="N75" t="s">
+        <v>355</v>
+      </c>
+      <c r="O75" t="s">
+        <v>356</v>
+      </c>
+      <c r="P75" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q75" t="s">
+        <v>35</v>
+      </c>
+      <c r="R75" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="76" spans="13:18">
+      <c r="M76" t="s">
+        <v>17</v>
+      </c>
+      <c r="N76" t="s">
+        <v>357</v>
+      </c>
+      <c r="O76" t="s">
+        <v>358</v>
+      </c>
+      <c r="P76" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q76" t="s">
+        <v>35</v>
+      </c>
+      <c r="R76" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="77" spans="13:18">
+      <c r="M77" t="s">
+        <v>17</v>
+      </c>
+      <c r="N77" t="s">
+        <v>359</v>
+      </c>
+      <c r="O77" t="s">
+        <v>360</v>
+      </c>
+      <c r="P77" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q77" t="s">
+        <v>35</v>
+      </c>
+      <c r="R77" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="78" spans="13:18">
+      <c r="M78" t="s">
+        <v>17</v>
+      </c>
+      <c r="N78" t="s">
+        <v>361</v>
+      </c>
+      <c r="O78" t="s">
+        <v>362</v>
+      </c>
+      <c r="P78" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q78" t="s">
+        <v>35</v>
+      </c>
+      <c r="R78" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="79" spans="13:18">
+      <c r="M79" t="s">
+        <v>17</v>
+      </c>
+      <c r="N79" t="s">
+        <v>363</v>
+      </c>
+      <c r="O79" t="s">
+        <v>364</v>
+      </c>
+      <c r="P79" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q79" t="s">
+        <v>35</v>
+      </c>
+      <c r="R79" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="80" spans="13:18">
+      <c r="M80" t="s">
+        <v>17</v>
+      </c>
+      <c r="N80" t="s">
+        <v>365</v>
+      </c>
+      <c r="O80" t="s">
+        <v>366</v>
+      </c>
+      <c r="P80" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q80" t="s">
+        <v>35</v>
+      </c>
+      <c r="R80" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="81" spans="13:18">
+      <c r="M81" t="s">
+        <v>17</v>
+      </c>
+      <c r="N81" t="s">
+        <v>367</v>
+      </c>
+      <c r="O81" t="s">
+        <v>368</v>
+      </c>
+      <c r="P81" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q81" t="s">
+        <v>35</v>
+      </c>
+      <c r="R81" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="82" spans="13:18">
+      <c r="M82" t="s">
+        <v>17</v>
+      </c>
+      <c r="N82" t="s">
+        <v>369</v>
+      </c>
+      <c r="O82" t="s">
+        <v>370</v>
+      </c>
+      <c r="P82" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q82" t="s">
+        <v>35</v>
+      </c>
+      <c r="R82" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="83" spans="13:18">
+      <c r="M83" t="s">
+        <v>17</v>
+      </c>
+      <c r="N83" t="s">
+        <v>371</v>
+      </c>
+      <c r="O83" t="s">
+        <v>372</v>
+      </c>
+      <c r="P83" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q83" t="s">
+        <v>35</v>
+      </c>
+      <c r="R83" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="84" spans="13:18">
+      <c r="M84" t="s">
+        <v>17</v>
+      </c>
+      <c r="N84" t="s">
+        <v>373</v>
+      </c>
+      <c r="O84" t="s">
+        <v>374</v>
+      </c>
+      <c r="P84" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q84" t="s">
+        <v>35</v>
+      </c>
+      <c r="R84" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="85" spans="13:18">
+      <c r="M85" t="s">
+        <v>17</v>
+      </c>
+      <c r="N85" t="s">
+        <v>375</v>
+      </c>
+      <c r="O85" t="s">
+        <v>376</v>
+      </c>
+      <c r="P85" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q85" t="s">
+        <v>35</v>
+      </c>
+      <c r="R85" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="86" spans="13:18">
+      <c r="M86" t="s">
+        <v>17</v>
+      </c>
+      <c r="N86" t="s">
+        <v>377</v>
+      </c>
+      <c r="O86" t="s">
+        <v>378</v>
+      </c>
+      <c r="P86" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q86" t="s">
+        <v>35</v>
+      </c>
+      <c r="R86" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="87" spans="13:18">
+      <c r="M87" t="s">
+        <v>17</v>
+      </c>
+      <c r="N87" t="s">
+        <v>379</v>
+      </c>
+      <c r="O87" t="s">
+        <v>380</v>
+      </c>
+      <c r="P87" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q87" t="s">
+        <v>35</v>
+      </c>
+      <c r="R87" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="88" spans="13:18">
+      <c r="M88" t="s">
+        <v>17</v>
+      </c>
+      <c r="N88" t="s">
+        <v>381</v>
+      </c>
+      <c r="O88" t="s">
+        <v>382</v>
+      </c>
+      <c r="P88" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q88" t="s">
+        <v>35</v>
+      </c>
+      <c r="R88" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="89" spans="13:18">
+      <c r="M89" t="s">
+        <v>17</v>
+      </c>
+      <c r="N89" t="s">
+        <v>383</v>
+      </c>
+      <c r="O89" t="s">
+        <v>384</v>
+      </c>
+      <c r="P89" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q89" t="s">
+        <v>35</v>
+      </c>
+      <c r="R89" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="90" spans="13:18">
+      <c r="M90" t="s">
+        <v>17</v>
+      </c>
+      <c r="N90" t="s">
+        <v>385</v>
+      </c>
+      <c r="O90" t="s">
+        <v>386</v>
+      </c>
+      <c r="P90" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q90" t="s">
+        <v>35</v>
+      </c>
+      <c r="R90" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="91" spans="13:18">
+      <c r="M91" t="s">
+        <v>17</v>
+      </c>
+      <c r="N91" t="s">
+        <v>387</v>
+      </c>
+      <c r="O91" t="s">
+        <v>388</v>
+      </c>
+      <c r="P91" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q91" t="s">
+        <v>35</v>
+      </c>
+      <c r="R91" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="92" spans="13:18">
+      <c r="M92" t="s">
+        <v>17</v>
+      </c>
+      <c r="N92" t="s">
+        <v>389</v>
+      </c>
+      <c r="O92" t="s">
+        <v>390</v>
+      </c>
+      <c r="P92" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q92" t="s">
+        <v>35</v>
+      </c>
+      <c r="R92" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="93" spans="13:18">
+      <c r="M93" t="s">
+        <v>17</v>
+      </c>
+      <c r="N93" t="s">
+        <v>391</v>
+      </c>
+      <c r="O93" t="s">
+        <v>392</v>
+      </c>
+      <c r="P93" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q93" t="s">
+        <v>35</v>
+      </c>
+      <c r="R93" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="94" spans="13:18">
+      <c r="M94" t="s">
+        <v>17</v>
+      </c>
+      <c r="N94" t="s">
+        <v>393</v>
+      </c>
+      <c r="O94" t="s">
+        <v>394</v>
+      </c>
+      <c r="P94" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q94" t="s">
+        <v>35</v>
+      </c>
+      <c r="R94" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="95" spans="13:18">
+      <c r="M95" t="s">
+        <v>17</v>
+      </c>
+      <c r="N95" t="s">
+        <v>395</v>
+      </c>
+      <c r="O95" t="s">
+        <v>396</v>
+      </c>
+      <c r="P95" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q95" t="s">
+        <v>35</v>
+      </c>
+      <c r="R95" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="96" spans="13:18">
+      <c r="M96" t="s">
+        <v>17</v>
+      </c>
+      <c r="N96" t="s">
+        <v>397</v>
+      </c>
+      <c r="O96" t="s">
+        <v>398</v>
+      </c>
+      <c r="P96" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q96" t="s">
+        <v>35</v>
+      </c>
+      <c r="R96" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="97" spans="13:18">
+      <c r="M97" t="s">
+        <v>17</v>
+      </c>
+      <c r="N97" t="s">
+        <v>399</v>
+      </c>
+      <c r="O97" t="s">
+        <v>400</v>
+      </c>
+      <c r="P97" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q97" t="s">
+        <v>35</v>
+      </c>
+      <c r="R97" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="98" spans="13:18">
+      <c r="M98" t="s">
+        <v>17</v>
+      </c>
+      <c r="N98" t="s">
+        <v>401</v>
+      </c>
+      <c r="O98" t="s">
+        <v>402</v>
+      </c>
+      <c r="P98" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q98" t="s">
+        <v>35</v>
+      </c>
+      <c r="R98" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="99" spans="13:18">
+      <c r="M99" t="s">
+        <v>17</v>
+      </c>
+      <c r="N99" t="s">
+        <v>403</v>
+      </c>
+      <c r="O99" t="s">
+        <v>404</v>
+      </c>
+      <c r="P99" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q99" t="s">
+        <v>35</v>
+      </c>
+      <c r="R99" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="100" spans="13:18">
+      <c r="M100" t="s">
+        <v>17</v>
+      </c>
+      <c r="N100" t="s">
+        <v>405</v>
+      </c>
+      <c r="O100" t="s">
+        <v>406</v>
+      </c>
+      <c r="P100" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q100" t="s">
+        <v>35</v>
+      </c>
+      <c r="R100" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="101" spans="13:18">
+      <c r="M101" t="s">
+        <v>17</v>
+      </c>
+      <c r="N101" t="s">
+        <v>407</v>
+      </c>
+      <c r="O101" t="s">
+        <v>408</v>
+      </c>
+      <c r="P101" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q101" t="s">
+        <v>35</v>
+      </c>
+      <c r="R101" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="102" spans="13:18">
+      <c r="M102" t="s">
+        <v>17</v>
+      </c>
+      <c r="N102" t="s">
+        <v>409</v>
+      </c>
+      <c r="O102" t="s">
+        <v>410</v>
+      </c>
+      <c r="P102" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q102" t="s">
+        <v>35</v>
+      </c>
+      <c r="R102" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="103" spans="13:18">
+      <c r="M103" t="s">
+        <v>17</v>
+      </c>
+      <c r="N103" t="s">
+        <v>411</v>
+      </c>
+      <c r="O103" t="s">
+        <v>412</v>
+      </c>
+      <c r="P103" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q103" t="s">
+        <v>35</v>
+      </c>
+      <c r="R103" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="104" spans="13:18">
+      <c r="M104" t="s">
+        <v>17</v>
+      </c>
+      <c r="N104" t="s">
+        <v>413</v>
+      </c>
+      <c r="O104" t="s">
+        <v>414</v>
+      </c>
+      <c r="P104" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q104" t="s">
+        <v>35</v>
+      </c>
+      <c r="R104" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="105" spans="13:18">
+      <c r="M105" t="s">
+        <v>17</v>
+      </c>
+      <c r="N105" t="s">
+        <v>415</v>
+      </c>
+      <c r="O105" t="s">
+        <v>416</v>
+      </c>
+      <c r="P105" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q105" t="s">
+        <v>35</v>
+      </c>
+      <c r="R105" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="106" spans="13:18">
+      <c r="M106" t="s">
+        <v>17</v>
+      </c>
+      <c r="N106" t="s">
+        <v>417</v>
+      </c>
+      <c r="O106" t="s">
+        <v>418</v>
+      </c>
+      <c r="P106" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q106" t="s">
+        <v>35</v>
+      </c>
+      <c r="R106" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="107" spans="13:18">
+      <c r="M107" t="s">
+        <v>17</v>
+      </c>
+      <c r="N107" t="s">
+        <v>419</v>
+      </c>
+      <c r="O107" t="s">
+        <v>420</v>
+      </c>
+      <c r="P107" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q107" t="s">
+        <v>35</v>
+      </c>
+      <c r="R107" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="108" spans="13:18">
+      <c r="M108" t="s">
+        <v>17</v>
+      </c>
+      <c r="N108" t="s">
+        <v>421</v>
+      </c>
+      <c r="O108" t="s">
+        <v>422</v>
+      </c>
+      <c r="P108" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q108" t="s">
+        <v>35</v>
+      </c>
+      <c r="R108" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="109" spans="13:18">
+      <c r="M109" t="s">
+        <v>17</v>
+      </c>
+      <c r="N109" t="s">
+        <v>423</v>
+      </c>
+      <c r="O109" t="s">
+        <v>424</v>
+      </c>
+      <c r="P109" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q109" t="s">
+        <v>35</v>
+      </c>
+      <c r="R109" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="110" spans="13:18">
+      <c r="M110" t="s">
+        <v>17</v>
+      </c>
+      <c r="N110" t="s">
+        <v>425</v>
+      </c>
+      <c r="O110" t="s">
+        <v>426</v>
+      </c>
+      <c r="P110" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q110" t="s">
+        <v>35</v>
+      </c>
+      <c r="R110" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="111" spans="13:18">
+      <c r="M111" t="s">
+        <v>17</v>
+      </c>
+      <c r="N111" t="s">
+        <v>427</v>
+      </c>
+      <c r="O111" t="s">
+        <v>428</v>
+      </c>
+      <c r="P111" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q111" t="s">
+        <v>35</v>
+      </c>
+      <c r="R111" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="112" spans="13:18">
+      <c r="M112" t="s">
+        <v>17</v>
+      </c>
+      <c r="N112" t="s">
+        <v>429</v>
+      </c>
+      <c r="O112" t="s">
+        <v>430</v>
+      </c>
+      <c r="P112" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q112" t="s">
+        <v>35</v>
+      </c>
+      <c r="R112" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="113" spans="13:18">
+      <c r="M113" t="s">
+        <v>17</v>
+      </c>
+      <c r="N113" t="s">
+        <v>431</v>
+      </c>
+      <c r="O113" t="s">
+        <v>432</v>
+      </c>
+      <c r="P113" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q113" t="s">
+        <v>35</v>
+      </c>
+      <c r="R113" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="114" spans="13:18">
+      <c r="M114" t="s">
+        <v>17</v>
+      </c>
+      <c r="N114" t="s">
+        <v>433</v>
+      </c>
+      <c r="O114" t="s">
+        <v>434</v>
+      </c>
+      <c r="P114" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q114" t="s">
+        <v>35</v>
+      </c>
+      <c r="R114" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="115" spans="13:18">
+      <c r="M115" t="s">
+        <v>17</v>
+      </c>
+      <c r="N115" t="s">
+        <v>435</v>
+      </c>
+      <c r="O115" t="s">
+        <v>436</v>
+      </c>
+      <c r="P115" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q115" t="s">
+        <v>35</v>
+      </c>
+      <c r="R115" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="116" spans="13:18">
+      <c r="M116" t="s">
+        <v>17</v>
+      </c>
+      <c r="N116" t="s">
+        <v>437</v>
+      </c>
+      <c r="O116" t="s">
+        <v>438</v>
+      </c>
+      <c r="P116" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q116" t="s">
+        <v>35</v>
+      </c>
+      <c r="R116" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="117" spans="13:18">
+      <c r="M117" t="s">
+        <v>17</v>
+      </c>
+      <c r="N117" t="s">
+        <v>439</v>
+      </c>
+      <c r="O117" t="s">
+        <v>440</v>
+      </c>
+      <c r="P117" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q117" t="s">
+        <v>35</v>
+      </c>
+      <c r="R117" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="118" spans="13:18">
+      <c r="M118" t="s">
+        <v>17</v>
+      </c>
+      <c r="N118" t="s">
+        <v>441</v>
+      </c>
+      <c r="O118" t="s">
+        <v>442</v>
+      </c>
+      <c r="P118" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q118" t="s">
+        <v>35</v>
+      </c>
+      <c r="R118" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="119" spans="13:18">
+      <c r="M119" t="s">
+        <v>17</v>
+      </c>
+      <c r="N119" t="s">
+        <v>443</v>
+      </c>
+      <c r="O119" t="s">
+        <v>444</v>
+      </c>
+      <c r="P119" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q119" t="s">
+        <v>35</v>
+      </c>
+      <c r="R119" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="120" spans="13:18">
+      <c r="M120" t="s">
+        <v>17</v>
+      </c>
+      <c r="N120" t="s">
+        <v>445</v>
+      </c>
+      <c r="O120" t="s">
+        <v>446</v>
+      </c>
+      <c r="P120" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q120" t="s">
+        <v>35</v>
+      </c>
+      <c r="R120" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="121" spans="13:18">
+      <c r="M121" t="s">
+        <v>17</v>
+      </c>
+      <c r="N121" t="s">
+        <v>447</v>
+      </c>
+      <c r="O121" t="s">
+        <v>448</v>
+      </c>
+      <c r="P121" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q121" t="s">
+        <v>35</v>
+      </c>
+      <c r="R121" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="122" spans="13:18">
+      <c r="M122" t="s">
+        <v>17</v>
+      </c>
+      <c r="N122" t="s">
+        <v>449</v>
+      </c>
+      <c r="O122" t="s">
+        <v>450</v>
+      </c>
+      <c r="P122" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q122" t="s">
+        <v>35</v>
+      </c>
+      <c r="R122" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="123" spans="13:18">
+      <c r="M123" t="s">
+        <v>17</v>
+      </c>
+      <c r="N123" t="s">
+        <v>451</v>
+      </c>
+      <c r="O123" t="s">
+        <v>452</v>
+      </c>
+      <c r="P123" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q123" t="s">
+        <v>35</v>
+      </c>
+      <c r="R123" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="124" spans="13:18">
+      <c r="M124" t="s">
+        <v>17</v>
+      </c>
+      <c r="N124" t="s">
+        <v>453</v>
+      </c>
+      <c r="O124" t="s">
+        <v>454</v>
+      </c>
+      <c r="P124" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q124" t="s">
+        <v>35</v>
+      </c>
+      <c r="R124" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="125" spans="13:18">
+      <c r="M125" t="s">
+        <v>17</v>
+      </c>
+      <c r="N125" t="s">
+        <v>455</v>
+      </c>
+      <c r="O125" t="s">
+        <v>456</v>
+      </c>
+      <c r="P125" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q125" t="s">
+        <v>35</v>
+      </c>
+      <c r="R125" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="126" spans="13:18">
+      <c r="M126" t="s">
+        <v>17</v>
+      </c>
+      <c r="N126" t="s">
+        <v>457</v>
+      </c>
+      <c r="O126" t="s">
+        <v>458</v>
+      </c>
+      <c r="P126" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q126" t="s">
+        <v>35</v>
+      </c>
+      <c r="R126" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="127" spans="13:18">
+      <c r="M127" t="s">
+        <v>17</v>
+      </c>
+      <c r="N127" t="s">
+        <v>459</v>
+      </c>
+      <c r="O127" t="s">
+        <v>460</v>
+      </c>
+      <c r="P127" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q127" t="s">
+        <v>35</v>
+      </c>
+      <c r="R127" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="128" spans="13:18">
+      <c r="M128" t="s">
+        <v>17</v>
+      </c>
+      <c r="N128" t="s">
+        <v>461</v>
+      </c>
+      <c r="O128" t="s">
+        <v>462</v>
+      </c>
+      <c r="P128" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q128" t="s">
+        <v>35</v>
+      </c>
+      <c r="R128" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="129" spans="13:18">
+      <c r="M129" t="s">
+        <v>17</v>
+      </c>
+      <c r="N129" t="s">
+        <v>463</v>
+      </c>
+      <c r="O129" t="s">
+        <v>464</v>
+      </c>
+      <c r="P129" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q129" t="s">
+        <v>35</v>
+      </c>
+      <c r="R129" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="130" spans="13:18">
+      <c r="M130" t="s">
+        <v>17</v>
+      </c>
+      <c r="N130" t="s">
+        <v>465</v>
+      </c>
+      <c r="O130" t="s">
+        <v>466</v>
+      </c>
+      <c r="P130" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q130" t="s">
+        <v>35</v>
+      </c>
+      <c r="R130" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="131" spans="13:18">
+      <c r="M131" t="s">
+        <v>17</v>
+      </c>
+      <c r="N131" t="s">
+        <v>467</v>
+      </c>
+      <c r="O131" t="s">
+        <v>468</v>
+      </c>
+      <c r="P131" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q131" t="s">
+        <v>35</v>
+      </c>
+      <c r="R131" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="132" spans="13:18">
+      <c r="M132" t="s">
+        <v>17</v>
+      </c>
+      <c r="N132" t="s">
+        <v>469</v>
+      </c>
+      <c r="O132" t="s">
+        <v>470</v>
+      </c>
+      <c r="P132" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q132" t="s">
+        <v>35</v>
+      </c>
+      <c r="R132" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="133" spans="13:18">
+      <c r="M133" t="s">
+        <v>17</v>
+      </c>
+      <c r="N133" t="s">
+        <v>471</v>
+      </c>
+      <c r="O133" t="s">
+        <v>472</v>
+      </c>
+      <c r="P133" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q133" t="s">
+        <v>35</v>
+      </c>
+      <c r="R133" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="134" spans="13:18">
+      <c r="M134" t="s">
+        <v>17</v>
+      </c>
+      <c r="N134" t="s">
+        <v>473</v>
+      </c>
+      <c r="O134" t="s">
+        <v>474</v>
+      </c>
+      <c r="P134" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q134" t="s">
+        <v>35</v>
+      </c>
+      <c r="R134" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="135" spans="13:18">
+      <c r="M135" t="s">
+        <v>17</v>
+      </c>
+      <c r="N135" t="s">
+        <v>475</v>
+      </c>
+      <c r="O135" t="s">
+        <v>476</v>
+      </c>
+      <c r="P135" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q135" t="s">
+        <v>35</v>
+      </c>
+      <c r="R135" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="136" spans="13:18">
+      <c r="M136" t="s">
+        <v>17</v>
+      </c>
+      <c r="N136" t="s">
+        <v>477</v>
+      </c>
+      <c r="O136" t="s">
+        <v>478</v>
+      </c>
+      <c r="P136" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q136" t="s">
+        <v>35</v>
+      </c>
+      <c r="R136" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="137" spans="13:18">
+      <c r="M137" t="s">
+        <v>17</v>
+      </c>
+      <c r="N137" t="s">
+        <v>479</v>
+      </c>
+      <c r="O137" t="s">
+        <v>480</v>
+      </c>
+      <c r="P137" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q137" t="s">
+        <v>35</v>
+      </c>
+      <c r="R137" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="138" spans="13:18">
+      <c r="M138" t="s">
+        <v>17</v>
+      </c>
+      <c r="N138" t="s">
+        <v>481</v>
+      </c>
+      <c r="O138" t="s">
+        <v>482</v>
+      </c>
+      <c r="P138" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q138" t="s">
+        <v>35</v>
+      </c>
+      <c r="R138" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="139" spans="13:18">
+      <c r="M139" t="s">
+        <v>17</v>
+      </c>
+      <c r="N139" t="s">
+        <v>483</v>
+      </c>
+      <c r="O139" t="s">
+        <v>484</v>
+      </c>
+      <c r="P139" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q139" t="s">
+        <v>35</v>
+      </c>
+      <c r="R139" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="140" spans="13:18">
+      <c r="M140" t="s">
+        <v>17</v>
+      </c>
+      <c r="N140" t="s">
+        <v>485</v>
+      </c>
+      <c r="O140" t="s">
+        <v>486</v>
+      </c>
+      <c r="P140" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q140" t="s">
+        <v>35</v>
+      </c>
+      <c r="R140" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="141" spans="13:18">
+      <c r="M141" t="s">
+        <v>17</v>
+      </c>
+      <c r="N141" t="s">
+        <v>487</v>
+      </c>
+      <c r="O141" t="s">
+        <v>488</v>
+      </c>
+      <c r="P141" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q141" t="s">
+        <v>35</v>
+      </c>
+      <c r="R141" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="142" spans="13:18">
+      <c r="M142" t="s">
+        <v>17</v>
+      </c>
+      <c r="N142" t="s">
+        <v>489</v>
+      </c>
+      <c r="O142" t="s">
+        <v>490</v>
+      </c>
+      <c r="P142" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q142" t="s">
+        <v>35</v>
+      </c>
+      <c r="R142" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="143" spans="13:18">
+      <c r="M143" t="s">
+        <v>17</v>
+      </c>
+      <c r="N143" t="s">
+        <v>491</v>
+      </c>
+      <c r="O143" t="s">
+        <v>492</v>
+      </c>
+      <c r="P143" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q143" t="s">
+        <v>35</v>
+      </c>
+      <c r="R143" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="144" spans="13:18">
+      <c r="M144" t="s">
+        <v>17</v>
+      </c>
+      <c r="N144" t="s">
+        <v>493</v>
+      </c>
+      <c r="O144" t="s">
+        <v>494</v>
+      </c>
+      <c r="P144" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q144" t="s">
+        <v>35</v>
+      </c>
+      <c r="R144" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="145" spans="13:18">
+      <c r="M145" t="s">
+        <v>17</v>
+      </c>
+      <c r="N145" t="s">
+        <v>495</v>
+      </c>
+      <c r="O145" t="s">
+        <v>496</v>
+      </c>
+      <c r="P145" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q145" t="s">
+        <v>35</v>
+      </c>
+      <c r="R145" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="146" spans="13:18">
+      <c r="M146" t="s">
+        <v>17</v>
+      </c>
+      <c r="N146" t="s">
+        <v>497</v>
+      </c>
+      <c r="O146" t="s">
+        <v>498</v>
+      </c>
+      <c r="P146" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q146" t="s">
+        <v>35</v>
+      </c>
+      <c r="R146" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="147" spans="13:18">
+      <c r="M147" t="s">
+        <v>17</v>
+      </c>
+      <c r="N147" t="s">
+        <v>499</v>
+      </c>
+      <c r="O147" t="s">
+        <v>500</v>
+      </c>
+      <c r="P147" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q147" t="s">
+        <v>35</v>
+      </c>
+      <c r="R147" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="148" spans="13:18">
+      <c r="M148" t="s">
+        <v>17</v>
+      </c>
+      <c r="N148" t="s">
+        <v>501</v>
+      </c>
+      <c r="O148" t="s">
+        <v>502</v>
+      </c>
+      <c r="P148" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q148" t="s">
+        <v>35</v>
+      </c>
+      <c r="R148" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="149" spans="13:18">
+      <c r="M149" t="s">
+        <v>17</v>
+      </c>
+      <c r="N149" t="s">
+        <v>503</v>
+      </c>
+      <c r="O149" t="s">
+        <v>504</v>
+      </c>
+      <c r="P149" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q149" t="s">
+        <v>35</v>
+      </c>
+      <c r="R149" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="150" spans="13:18">
+      <c r="M150" t="s">
+        <v>17</v>
+      </c>
+      <c r="N150" t="s">
+        <v>505</v>
+      </c>
+      <c r="O150" t="s">
+        <v>506</v>
+      </c>
+      <c r="P150" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q150" t="s">
+        <v>35</v>
+      </c>
+      <c r="R150" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="151" spans="13:18">
+      <c r="M151" t="s">
+        <v>17</v>
+      </c>
+      <c r="N151" t="s">
+        <v>507</v>
+      </c>
+      <c r="O151" t="s">
+        <v>508</v>
+      </c>
+      <c r="P151" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q151" t="s">
+        <v>35</v>
+      </c>
+      <c r="R151" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="152" spans="13:18">
+      <c r="M152" t="s">
+        <v>17</v>
+      </c>
+      <c r="N152" t="s">
+        <v>509</v>
+      </c>
+      <c r="O152" t="s">
+        <v>510</v>
+      </c>
+      <c r="P152" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q152" t="s">
+        <v>35</v>
+      </c>
+      <c r="R152" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="153" spans="13:18">
+      <c r="M153" t="s">
+        <v>17</v>
+      </c>
+      <c r="N153" t="s">
+        <v>511</v>
+      </c>
+      <c r="O153" t="s">
+        <v>512</v>
+      </c>
+      <c r="P153" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q153" t="s">
+        <v>35</v>
+      </c>
+      <c r="R153" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="154" spans="13:18">
+      <c r="M154" t="s">
+        <v>17</v>
+      </c>
+      <c r="N154" t="s">
+        <v>513</v>
+      </c>
+      <c r="O154" t="s">
+        <v>514</v>
+      </c>
+      <c r="P154" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q154" t="s">
+        <v>35</v>
+      </c>
+      <c r="R154" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="155" spans="13:18">
+      <c r="M155" t="s">
+        <v>17</v>
+      </c>
+      <c r="N155" t="s">
+        <v>515</v>
+      </c>
+      <c r="O155" t="s">
+        <v>516</v>
+      </c>
+      <c r="P155" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q155" t="s">
+        <v>35</v>
+      </c>
+      <c r="R155" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="156" spans="13:18">
+      <c r="M156" t="s">
+        <v>17</v>
+      </c>
+      <c r="N156" t="s">
+        <v>517</v>
+      </c>
+      <c r="O156" t="s">
+        <v>518</v>
+      </c>
+      <c r="P156" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q156" t="s">
+        <v>35</v>
+      </c>
+      <c r="R156" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="157" spans="13:18">
+      <c r="M157" t="s">
+        <v>17</v>
+      </c>
+      <c r="N157" t="s">
+        <v>519</v>
+      </c>
+      <c r="O157" t="s">
+        <v>520</v>
+      </c>
+      <c r="P157" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q157" t="s">
+        <v>35</v>
+      </c>
+      <c r="R157" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="158" spans="13:18">
+      <c r="M158" t="s">
+        <v>17</v>
+      </c>
+      <c r="N158" t="s">
+        <v>521</v>
+      </c>
+      <c r="O158" t="s">
+        <v>522</v>
+      </c>
+      <c r="P158" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q158" t="s">
+        <v>35</v>
+      </c>
+      <c r="R158" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="159" spans="13:18">
+      <c r="M159" t="s">
+        <v>17</v>
+      </c>
+      <c r="N159" t="s">
+        <v>523</v>
+      </c>
+      <c r="O159" t="s">
+        <v>524</v>
+      </c>
+      <c r="P159" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q159" t="s">
+        <v>35</v>
+      </c>
+      <c r="R159" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="160" spans="13:18">
+      <c r="M160" t="s">
+        <v>17</v>
+      </c>
+      <c r="N160" t="s">
+        <v>525</v>
+      </c>
+      <c r="O160" t="s">
+        <v>526</v>
+      </c>
+      <c r="P160" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q160" t="s">
+        <v>35</v>
+      </c>
+      <c r="R160" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="161" spans="13:18">
+      <c r="M161" t="s">
+        <v>17</v>
+      </c>
+      <c r="N161" t="s">
+        <v>527</v>
+      </c>
+      <c r="O161" t="s">
+        <v>528</v>
+      </c>
+      <c r="P161" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q161" t="s">
+        <v>35</v>
+      </c>
+      <c r="R161" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="162" spans="13:18">
+      <c r="M162" t="s">
+        <v>17</v>
+      </c>
+      <c r="N162" t="s">
+        <v>529</v>
+      </c>
+      <c r="O162" t="s">
+        <v>530</v>
+      </c>
+      <c r="P162" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q162" t="s">
+        <v>35</v>
+      </c>
+      <c r="R162" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="163" spans="13:18">
+      <c r="M163" t="s">
+        <v>17</v>
+      </c>
+      <c r="N163" t="s">
+        <v>531</v>
+      </c>
+      <c r="O163" t="s">
+        <v>532</v>
+      </c>
+      <c r="P163" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q163" t="s">
+        <v>35</v>
+      </c>
+      <c r="R163" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="164" spans="13:18">
+      <c r="M164" t="s">
+        <v>17</v>
+      </c>
+      <c r="N164" t="s">
+        <v>533</v>
+      </c>
+      <c r="O164" t="s">
+        <v>534</v>
+      </c>
+      <c r="P164" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q164" t="s">
+        <v>35</v>
+      </c>
+      <c r="R164" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="165" spans="13:18">
+      <c r="M165" t="s">
+        <v>17</v>
+      </c>
+      <c r="N165" t="s">
+        <v>535</v>
+      </c>
+      <c r="O165" t="s">
+        <v>536</v>
+      </c>
+      <c r="P165" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q165" t="s">
+        <v>35</v>
+      </c>
+      <c r="R165" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="166" spans="13:18">
+      <c r="M166" t="s">
+        <v>17</v>
+      </c>
+      <c r="N166" t="s">
+        <v>537</v>
+      </c>
+      <c r="O166" t="s">
+        <v>538</v>
+      </c>
+      <c r="P166" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q166" t="s">
+        <v>35</v>
+      </c>
+      <c r="R166" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="167" spans="13:18">
+      <c r="M167" t="s">
+        <v>17</v>
+      </c>
+      <c r="N167" t="s">
+        <v>539</v>
+      </c>
+      <c r="O167" t="s">
+        <v>540</v>
+      </c>
+      <c r="P167" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q167" t="s">
+        <v>35</v>
+      </c>
+      <c r="R167" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="168" spans="13:18">
+      <c r="M168" t="s">
+        <v>17</v>
+      </c>
+      <c r="N168" t="s">
+        <v>541</v>
+      </c>
+      <c r="O168" t="s">
+        <v>542</v>
+      </c>
+      <c r="P168" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q168" t="s">
+        <v>35</v>
+      </c>
+      <c r="R168" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="169" spans="13:18">
+      <c r="M169" t="s">
+        <v>17</v>
+      </c>
+      <c r="N169" t="s">
+        <v>543</v>
+      </c>
+      <c r="O169" t="s">
+        <v>544</v>
+      </c>
+      <c r="P169" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q169" t="s">
+        <v>35</v>
+      </c>
+      <c r="R169" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="170" spans="13:18">
+      <c r="M170" t="s">
+        <v>17</v>
+      </c>
+      <c r="N170" t="s">
+        <v>545</v>
+      </c>
+      <c r="O170" t="s">
+        <v>546</v>
+      </c>
+      <c r="P170" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q170" t="s">
+        <v>35</v>
+      </c>
+      <c r="R170" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="171" spans="13:18">
+      <c r="M171" t="s">
+        <v>17</v>
+      </c>
+      <c r="N171" t="s">
+        <v>547</v>
+      </c>
+      <c r="O171" t="s">
+        <v>548</v>
+      </c>
+      <c r="P171" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q171" t="s">
+        <v>35</v>
+      </c>
+      <c r="R171" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="172" spans="13:18">
+      <c r="M172" t="s">
+        <v>17</v>
+      </c>
+      <c r="N172" t="s">
+        <v>549</v>
+      </c>
+      <c r="O172" t="s">
+        <v>550</v>
+      </c>
+      <c r="P172" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q172" t="s">
+        <v>35</v>
+      </c>
+      <c r="R172" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="173" spans="13:18">
+      <c r="M173" t="s">
+        <v>17</v>
+      </c>
+      <c r="N173" t="s">
+        <v>551</v>
+      </c>
+      <c r="O173" t="s">
+        <v>552</v>
+      </c>
+      <c r="P173" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q173" t="s">
+        <v>35</v>
+      </c>
+      <c r="R173" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="174" spans="13:18">
+      <c r="M174" t="s">
+        <v>17</v>
+      </c>
+      <c r="N174" t="s">
+        <v>553</v>
+      </c>
+      <c r="O174" t="s">
+        <v>554</v>
+      </c>
+      <c r="P174" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q174" t="s">
+        <v>35</v>
+      </c>
+      <c r="R174" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="175" spans="13:18">
+      <c r="M175" t="s">
+        <v>17</v>
+      </c>
+      <c r="N175" t="s">
+        <v>555</v>
+      </c>
+      <c r="O175" t="s">
+        <v>556</v>
+      </c>
+      <c r="P175" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q175" t="s">
+        <v>35</v>
+      </c>
+      <c r="R175" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="176" spans="13:18">
+      <c r="M176" t="s">
+        <v>17</v>
+      </c>
+      <c r="N176" t="s">
+        <v>557</v>
+      </c>
+      <c r="O176" t="s">
+        <v>558</v>
+      </c>
+      <c r="P176" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q176" t="s">
+        <v>35</v>
+      </c>
+      <c r="R176" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="177" spans="13:18">
+      <c r="M177" t="s">
+        <v>17</v>
+      </c>
+      <c r="N177" t="s">
+        <v>559</v>
+      </c>
+      <c r="O177" t="s">
+        <v>560</v>
+      </c>
+      <c r="P177" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q177" t="s">
+        <v>35</v>
+      </c>
+      <c r="R177" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="178" spans="13:18">
+      <c r="M178" t="s">
+        <v>17</v>
+      </c>
+      <c r="N178" t="s">
+        <v>561</v>
+      </c>
+      <c r="O178" t="s">
+        <v>562</v>
+      </c>
+      <c r="P178" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q178" t="s">
+        <v>35</v>
+      </c>
+      <c r="R178" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="179" spans="13:18">
+      <c r="M179" t="s">
+        <v>17</v>
+      </c>
+      <c r="N179" t="s">
+        <v>563</v>
+      </c>
+      <c r="O179" t="s">
+        <v>564</v>
+      </c>
+      <c r="P179" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q179" t="s">
+        <v>35</v>
+      </c>
+      <c r="R179" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="180" spans="13:18">
+      <c r="M180" t="s">
+        <v>17</v>
+      </c>
+      <c r="N180" t="s">
+        <v>565</v>
+      </c>
+      <c r="O180" t="s">
+        <v>566</v>
+      </c>
+      <c r="P180" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q180" t="s">
+        <v>35</v>
+      </c>
+      <c r="R180" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="181" spans="13:18">
+      <c r="M181" t="s">
+        <v>17</v>
+      </c>
+      <c r="N181" t="s">
+        <v>567</v>
+      </c>
+      <c r="O181" t="s">
+        <v>568</v>
+      </c>
+      <c r="P181" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q181" t="s">
+        <v>35</v>
+      </c>
+      <c r="R181" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="182" spans="13:18">
+      <c r="M182" t="s">
+        <v>17</v>
+      </c>
+      <c r="N182" t="s">
+        <v>569</v>
+      </c>
+      <c r="O182" t="s">
+        <v>570</v>
+      </c>
+      <c r="P182" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q182" t="s">
+        <v>35</v>
+      </c>
+      <c r="R182" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="183" spans="13:18">
+      <c r="M183" t="s">
+        <v>17</v>
+      </c>
+      <c r="N183" t="s">
+        <v>571</v>
+      </c>
+      <c r="O183" t="s">
+        <v>572</v>
+      </c>
+      <c r="P183" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q183" t="s">
+        <v>35</v>
+      </c>
+      <c r="R183" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="184" spans="13:18">
+      <c r="M184" t="s">
+        <v>17</v>
+      </c>
+      <c r="N184" t="s">
+        <v>573</v>
+      </c>
+      <c r="O184" t="s">
+        <v>574</v>
+      </c>
+      <c r="P184" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q184" t="s">
+        <v>35</v>
+      </c>
+      <c r="R184" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="185" spans="13:18">
+      <c r="M185" t="s">
+        <v>17</v>
+      </c>
+      <c r="N185" t="s">
+        <v>575</v>
+      </c>
+      <c r="O185" t="s">
+        <v>576</v>
+      </c>
+      <c r="P185" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q185" t="s">
+        <v>35</v>
+      </c>
+      <c r="R185" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="186" spans="13:18">
+      <c r="M186" t="s">
+        <v>17</v>
+      </c>
+      <c r="N186" t="s">
+        <v>577</v>
+      </c>
+      <c r="O186" t="s">
+        <v>578</v>
+      </c>
+      <c r="P186" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q186" t="s">
+        <v>35</v>
+      </c>
+      <c r="R186" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="187" spans="13:18">
+      <c r="M187" t="s">
+        <v>17</v>
+      </c>
+      <c r="N187" t="s">
+        <v>579</v>
+      </c>
+      <c r="O187" t="s">
+        <v>580</v>
+      </c>
+      <c r="P187" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q187" t="s">
+        <v>35</v>
+      </c>
+      <c r="R187" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="188" spans="13:18">
+      <c r="M188" t="s">
+        <v>17</v>
+      </c>
+      <c r="N188" t="s">
+        <v>581</v>
+      </c>
+      <c r="O188" t="s">
+        <v>582</v>
+      </c>
+      <c r="P188" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q188" t="s">
+        <v>35</v>
+      </c>
+      <c r="R188" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="189" spans="13:18">
+      <c r="M189" t="s">
+        <v>17</v>
+      </c>
+      <c r="N189" t="s">
+        <v>583</v>
+      </c>
+      <c r="O189" t="s">
+        <v>584</v>
+      </c>
+      <c r="P189" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q189" t="s">
+        <v>35</v>
+      </c>
+      <c r="R189" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="190" spans="13:18">
+      <c r="M190" t="s">
+        <v>17</v>
+      </c>
+      <c r="N190" t="s">
+        <v>585</v>
+      </c>
+      <c r="O190" t="s">
+        <v>586</v>
+      </c>
+      <c r="P190" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q190" t="s">
+        <v>35</v>
+      </c>
+      <c r="R190" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="191" spans="13:18">
+      <c r="M191" t="s">
+        <v>17</v>
+      </c>
+      <c r="N191" t="s">
+        <v>587</v>
+      </c>
+      <c r="O191" t="s">
+        <v>588</v>
+      </c>
+      <c r="P191" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q191" t="s">
+        <v>35</v>
+      </c>
+      <c r="R191" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="192" spans="13:18">
+      <c r="M192" t="s">
+        <v>17</v>
+      </c>
+      <c r="N192" t="s">
+        <v>589</v>
+      </c>
+      <c r="O192" t="s">
+        <v>590</v>
+      </c>
+      <c r="P192" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q192" t="s">
+        <v>35</v>
+      </c>
+      <c r="R192" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="193" spans="13:18">
+      <c r="M193" t="s">
+        <v>17</v>
+      </c>
+      <c r="N193" t="s">
+        <v>591</v>
+      </c>
+      <c r="O193" t="s">
+        <v>592</v>
+      </c>
+      <c r="P193" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q193" t="s">
+        <v>35</v>
+      </c>
+      <c r="R193" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="194" spans="13:18">
+      <c r="M194" t="s">
+        <v>17</v>
+      </c>
+      <c r="N194" t="s">
+        <v>593</v>
+      </c>
+      <c r="O194" t="s">
+        <v>594</v>
+      </c>
+      <c r="P194" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q194" t="s">
+        <v>35</v>
+      </c>
+      <c r="R194" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="195" spans="13:18">
+      <c r="M195" t="s">
+        <v>17</v>
+      </c>
+      <c r="N195" t="s">
+        <v>595</v>
+      </c>
+      <c r="O195" t="s">
+        <v>596</v>
+      </c>
+      <c r="P195" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q195" t="s">
+        <v>35</v>
+      </c>
+      <c r="R195" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="196" spans="13:18">
+      <c r="M196" t="s">
+        <v>17</v>
+      </c>
+      <c r="N196" t="s">
+        <v>597</v>
+      </c>
+      <c r="O196" t="s">
+        <v>598</v>
+      </c>
+      <c r="P196" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q196" t="s">
+        <v>35</v>
+      </c>
+      <c r="R196" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="197" spans="13:18">
+      <c r="M197" t="s">
+        <v>17</v>
+      </c>
+      <c r="N197" t="s">
+        <v>599</v>
+      </c>
+      <c r="O197" t="s">
+        <v>600</v>
+      </c>
+      <c r="P197" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q197" t="s">
+        <v>35</v>
+      </c>
+      <c r="R197" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="198" spans="13:18">
+      <c r="M198" t="s">
+        <v>17</v>
+      </c>
+      <c r="N198" t="s">
+        <v>601</v>
+      </c>
+      <c r="O198" t="s">
+        <v>602</v>
+      </c>
+      <c r="P198" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q198" t="s">
+        <v>35</v>
+      </c>
+      <c r="R198" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="199" spans="13:18">
+      <c r="M199" t="s">
+        <v>17</v>
+      </c>
+      <c r="N199" t="s">
+        <v>603</v>
+      </c>
+      <c r="O199" t="s">
+        <v>604</v>
+      </c>
+      <c r="P199" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q199" t="s">
+        <v>35</v>
+      </c>
+      <c r="R199" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="200" spans="13:18">
+      <c r="M200" t="s">
+        <v>17</v>
+      </c>
+      <c r="N200" t="s">
+        <v>605</v>
+      </c>
+      <c r="O200" t="s">
+        <v>606</v>
+      </c>
+      <c r="P200" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q200" t="s">
+        <v>35</v>
+      </c>
+      <c r="R200" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="201" spans="13:18">
+      <c r="M201" t="s">
+        <v>17</v>
+      </c>
+      <c r="N201" t="s">
+        <v>607</v>
+      </c>
+      <c r="O201" t="s">
+        <v>608</v>
+      </c>
+      <c r="P201" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q201" t="s">
+        <v>35</v>
+      </c>
+      <c r="R201" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="202" spans="13:18">
+      <c r="M202" t="s">
+        <v>17</v>
+      </c>
+      <c r="N202" t="s">
+        <v>609</v>
+      </c>
+      <c r="O202" t="s">
+        <v>610</v>
+      </c>
+      <c r="P202" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q202" t="s">
+        <v>35</v>
+      </c>
+      <c r="R202" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="203" spans="13:18">
+      <c r="M203" t="s">
+        <v>17</v>
+      </c>
+      <c r="N203" t="s">
+        <v>611</v>
+      </c>
+      <c r="O203" t="s">
+        <v>612</v>
+      </c>
+      <c r="P203" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q203" t="s">
+        <v>35</v>
+      </c>
+      <c r="R203" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="204" spans="13:18">
+      <c r="M204" t="s">
+        <v>17</v>
+      </c>
+      <c r="N204" t="s">
+        <v>613</v>
+      </c>
+      <c r="O204" t="s">
+        <v>614</v>
+      </c>
+      <c r="P204" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q204" t="s">
+        <v>35</v>
+      </c>
+      <c r="R204" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="205" spans="13:18">
+      <c r="M205" t="s">
+        <v>17</v>
+      </c>
+      <c r="N205" t="s">
+        <v>615</v>
+      </c>
+      <c r="O205" t="s">
+        <v>616</v>
+      </c>
+      <c r="P205" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q205" t="s">
+        <v>35</v>
+      </c>
+      <c r="R205" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="206" spans="13:18">
+      <c r="M206" t="s">
+        <v>17</v>
+      </c>
+      <c r="N206" t="s">
+        <v>617</v>
+      </c>
+      <c r="O206" t="s">
+        <v>618</v>
+      </c>
+      <c r="P206" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q206" t="s">
+        <v>35</v>
+      </c>
+      <c r="R206" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="207" spans="13:18">
+      <c r="M207" t="s">
+        <v>17</v>
+      </c>
+      <c r="N207" t="s">
+        <v>619</v>
+      </c>
+      <c r="O207" t="s">
+        <v>620</v>
+      </c>
+      <c r="P207" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q207" t="s">
+        <v>35</v>
+      </c>
+      <c r="R207" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="208" spans="13:18">
+      <c r="M208" t="s">
+        <v>17</v>
+      </c>
+      <c r="N208" t="s">
+        <v>621</v>
+      </c>
+      <c r="O208" t="s">
+        <v>622</v>
+      </c>
+      <c r="P208" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q208" t="s">
+        <v>35</v>
+      </c>
+      <c r="R208" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="209" spans="13:18">
+      <c r="M209" t="s">
+        <v>17</v>
+      </c>
+      <c r="N209" t="s">
+        <v>623</v>
+      </c>
+      <c r="O209" t="s">
+        <v>624</v>
+      </c>
+      <c r="P209" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q209" t="s">
+        <v>35</v>
+      </c>
+      <c r="R209" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="210" spans="13:18">
+      <c r="M210" t="s">
+        <v>17</v>
+      </c>
+      <c r="N210" t="s">
+        <v>625</v>
+      </c>
+      <c r="O210" t="s">
+        <v>626</v>
+      </c>
+      <c r="P210" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q210" t="s">
+        <v>35</v>
+      </c>
+      <c r="R210" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="211" spans="13:18">
+      <c r="M211" t="s">
+        <v>17</v>
+      </c>
+      <c r="N211" t="s">
+        <v>627</v>
+      </c>
+      <c r="O211" t="s">
+        <v>628</v>
+      </c>
+      <c r="P211" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q211" t="s">
+        <v>35</v>
+      </c>
+      <c r="R211" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="212" spans="13:18">
+      <c r="M212" t="s">
+        <v>17</v>
+      </c>
+      <c r="N212" t="s">
+        <v>629</v>
+      </c>
+      <c r="O212" t="s">
+        <v>630</v>
+      </c>
+      <c r="P212" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q212" t="s">
+        <v>35</v>
+      </c>
+      <c r="R212" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="213" spans="13:18">
+      <c r="M213" t="s">
+        <v>17</v>
+      </c>
+      <c r="N213" t="s">
+        <v>631</v>
+      </c>
+      <c r="O213" t="s">
+        <v>632</v>
+      </c>
+      <c r="P213" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q213" t="s">
+        <v>35</v>
+      </c>
+      <c r="R213" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="214" spans="13:18">
+      <c r="M214" t="s">
+        <v>17</v>
+      </c>
+      <c r="N214" t="s">
+        <v>633</v>
+      </c>
+      <c r="O214" t="s">
+        <v>634</v>
+      </c>
+      <c r="P214" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q214" t="s">
+        <v>35</v>
+      </c>
+      <c r="R214" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="215" spans="13:18">
+      <c r="M215" t="s">
+        <v>17</v>
+      </c>
+      <c r="N215" t="s">
+        <v>635</v>
+      </c>
+      <c r="O215" t="s">
+        <v>636</v>
+      </c>
+      <c r="P215" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q215" t="s">
+        <v>35</v>
+      </c>
+      <c r="R215" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="216" spans="13:18">
+      <c r="M216" t="s">
+        <v>17</v>
+      </c>
+      <c r="N216" t="s">
+        <v>637</v>
+      </c>
+      <c r="O216" t="s">
+        <v>638</v>
+      </c>
+      <c r="P216" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q216" t="s">
+        <v>35</v>
+      </c>
+      <c r="R216" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="217" spans="13:18">
+      <c r="M217" t="s">
+        <v>17</v>
+      </c>
+      <c r="N217" t="s">
+        <v>639</v>
+      </c>
+      <c r="O217" t="s">
+        <v>640</v>
+      </c>
+      <c r="P217" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q217" t="s">
+        <v>35</v>
+      </c>
+      <c r="R217" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="218" spans="13:18">
+      <c r="M218" t="s">
+        <v>17</v>
+      </c>
+      <c r="N218" t="s">
+        <v>641</v>
+      </c>
+      <c r="O218" t="s">
+        <v>642</v>
+      </c>
+      <c r="P218" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q218" t="s">
+        <v>35</v>
+      </c>
+      <c r="R218" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="219" spans="13:18">
+      <c r="M219" t="s">
+        <v>17</v>
+      </c>
+      <c r="N219" t="s">
+        <v>643</v>
+      </c>
+      <c r="O219" t="s">
+        <v>644</v>
+      </c>
+      <c r="P219" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q219" t="s">
+        <v>35</v>
+      </c>
+      <c r="R219" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="220" spans="13:18">
+      <c r="M220" t="s">
+        <v>17</v>
+      </c>
+      <c r="N220" t="s">
+        <v>645</v>
+      </c>
+      <c r="O220" t="s">
+        <v>646</v>
+      </c>
+      <c r="P220" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q220" t="s">
+        <v>35</v>
+      </c>
+      <c r="R220" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="221" spans="13:18">
+      <c r="M221" t="s">
+        <v>17</v>
+      </c>
+      <c r="N221" t="s">
+        <v>647</v>
+      </c>
+      <c r="O221" t="s">
+        <v>648</v>
+      </c>
+      <c r="P221" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q221" t="s">
+        <v>35</v>
+      </c>
+      <c r="R221" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="222" spans="13:18">
+      <c r="M222" t="s">
+        <v>17</v>
+      </c>
+      <c r="N222" t="s">
+        <v>649</v>
+      </c>
+      <c r="O222" t="s">
+        <v>650</v>
+      </c>
+      <c r="P222" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q222" t="s">
+        <v>35</v>
+      </c>
+      <c r="R222" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="223" spans="13:18">
+      <c r="M223" t="s">
+        <v>17</v>
+      </c>
+      <c r="N223" t="s">
+        <v>651</v>
+      </c>
+      <c r="O223" t="s">
+        <v>652</v>
+      </c>
+      <c r="P223" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q223" t="s">
+        <v>35</v>
+      </c>
+      <c r="R223" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="224" spans="13:18">
+      <c r="M224" t="s">
+        <v>17</v>
+      </c>
+      <c r="N224" t="s">
+        <v>653</v>
+      </c>
+      <c r="O224" t="s">
+        <v>654</v>
+      </c>
+      <c r="P224" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q224" t="s">
+        <v>35</v>
+      </c>
+      <c r="R224" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="225" spans="13:18">
+      <c r="M225" t="s">
+        <v>17</v>
+      </c>
+      <c r="N225" t="s">
+        <v>655</v>
+      </c>
+      <c r="O225" t="s">
+        <v>656</v>
+      </c>
+      <c r="P225" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q225" t="s">
+        <v>35</v>
+      </c>
+      <c r="R225" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="226" spans="13:18">
+      <c r="M226" t="s">
+        <v>17</v>
+      </c>
+      <c r="N226" t="s">
+        <v>657</v>
+      </c>
+      <c r="O226" t="s">
+        <v>658</v>
+      </c>
+      <c r="P226" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q226" t="s">
+        <v>35</v>
+      </c>
+      <c r="R226" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="227" spans="13:18">
+      <c r="M227" t="s">
+        <v>17</v>
+      </c>
+      <c r="N227" t="s">
+        <v>659</v>
+      </c>
+      <c r="O227" t="s">
+        <v>660</v>
+      </c>
+      <c r="P227" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q227" t="s">
+        <v>35</v>
+      </c>
+      <c r="R227" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="228" spans="13:18">
+      <c r="M228" t="s">
+        <v>17</v>
+      </c>
+      <c r="N228" t="s">
+        <v>661</v>
+      </c>
+      <c r="O228" t="s">
+        <v>662</v>
+      </c>
+      <c r="P228" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q228" t="s">
+        <v>35</v>
+      </c>
+      <c r="R228" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="229" spans="13:18">
+      <c r="M229" t="s">
+        <v>17</v>
+      </c>
+      <c r="N229" t="s">
+        <v>663</v>
+      </c>
+      <c r="O229" t="s">
+        <v>664</v>
+      </c>
+      <c r="P229" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q229" t="s">
+        <v>35</v>
+      </c>
+      <c r="R229" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="230" spans="13:18">
+      <c r="M230" t="s">
+        <v>17</v>
+      </c>
+      <c r="N230" t="s">
+        <v>665</v>
+      </c>
+      <c r="O230" t="s">
+        <v>666</v>
+      </c>
+      <c r="P230" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q230" t="s">
+        <v>35</v>
+      </c>
+      <c r="R230" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="231" spans="13:18">
+      <c r="M231" t="s">
+        <v>17</v>
+      </c>
+      <c r="N231" t="s">
+        <v>667</v>
+      </c>
+      <c r="O231" t="s">
+        <v>668</v>
+      </c>
+      <c r="P231" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q231" t="s">
+        <v>35</v>
+      </c>
+      <c r="R231" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="232" spans="13:18">
+      <c r="M232" t="s">
+        <v>17</v>
+      </c>
+      <c r="N232" t="s">
+        <v>669</v>
+      </c>
+      <c r="O232" t="s">
+        <v>670</v>
+      </c>
+      <c r="P232" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q232" t="s">
+        <v>35</v>
+      </c>
+      <c r="R232" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="233" spans="13:18">
+      <c r="M233" t="s">
+        <v>17</v>
+      </c>
+      <c r="N233" t="s">
+        <v>671</v>
+      </c>
+      <c r="O233" t="s">
+        <v>672</v>
+      </c>
+      <c r="P233" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q233" t="s">
+        <v>35</v>
+      </c>
+      <c r="R233" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="234" spans="13:18">
+      <c r="M234" t="s">
+        <v>17</v>
+      </c>
+      <c r="N234" t="s">
+        <v>673</v>
+      </c>
+      <c r="O234" t="s">
+        <v>674</v>
+      </c>
+      <c r="P234" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q234" t="s">
+        <v>35</v>
+      </c>
+      <c r="R234" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="235" spans="13:18">
+      <c r="M235" t="s">
+        <v>17</v>
+      </c>
+      <c r="N235" t="s">
+        <v>675</v>
+      </c>
+      <c r="O235" t="s">
+        <v>676</v>
+      </c>
+      <c r="P235" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q235" t="s">
+        <v>35</v>
+      </c>
+      <c r="R235" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="236" spans="13:18">
+      <c r="M236" t="s">
+        <v>17</v>
+      </c>
+      <c r="N236" t="s">
+        <v>677</v>
+      </c>
+      <c r="O236" t="s">
+        <v>678</v>
+      </c>
+      <c r="P236" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q236" t="s">
+        <v>35</v>
+      </c>
+      <c r="R236" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="237" spans="13:18">
+      <c r="M237" t="s">
+        <v>17</v>
+      </c>
+      <c r="N237" t="s">
+        <v>679</v>
+      </c>
+      <c r="O237" t="s">
+        <v>680</v>
+      </c>
+      <c r="P237" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q237" t="s">
+        <v>35</v>
+      </c>
+      <c r="R237" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="238" spans="13:18">
+      <c r="M238" t="s">
+        <v>17</v>
+      </c>
+      <c r="N238" t="s">
+        <v>681</v>
+      </c>
+      <c r="O238" t="s">
+        <v>682</v>
+      </c>
+      <c r="P238" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q238" t="s">
+        <v>35</v>
+      </c>
+      <c r="R238" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="239" spans="13:18">
+      <c r="M239" t="s">
+        <v>17</v>
+      </c>
+      <c r="N239" t="s">
+        <v>683</v>
+      </c>
+      <c r="O239" t="s">
+        <v>684</v>
+      </c>
+      <c r="P239" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q239" t="s">
+        <v>35</v>
+      </c>
+      <c r="R239" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="240" spans="13:18">
+      <c r="M240" t="s">
+        <v>17</v>
+      </c>
+      <c r="N240" t="s">
+        <v>685</v>
+      </c>
+      <c r="O240" t="s">
+        <v>686</v>
+      </c>
+      <c r="P240" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q240" t="s">
+        <v>35</v>
+      </c>
+      <c r="R240" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="241" spans="13:18">
+      <c r="M241" t="s">
+        <v>17</v>
+      </c>
+      <c r="N241" t="s">
+        <v>687</v>
+      </c>
+      <c r="O241" t="s">
+        <v>688</v>
+      </c>
+      <c r="P241" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q241" t="s">
+        <v>35</v>
+      </c>
+      <c r="R241" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="242" spans="13:18">
+      <c r="M242" t="s">
+        <v>17</v>
+      </c>
+      <c r="N242" t="s">
+        <v>689</v>
+      </c>
+      <c r="O242" t="s">
+        <v>690</v>
+      </c>
+      <c r="P242" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q242" t="s">
+        <v>35</v>
+      </c>
+      <c r="R242" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="243" spans="13:18">
+      <c r="M243" t="s">
+        <v>17</v>
+      </c>
+      <c r="N243" t="s">
+        <v>691</v>
+      </c>
+      <c r="O243" t="s">
+        <v>692</v>
+      </c>
+      <c r="P243" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q243" t="s">
+        <v>35</v>
+      </c>
+      <c r="R243" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="244" spans="13:18">
+      <c r="M244" t="s">
+        <v>17</v>
+      </c>
+      <c r="N244" t="s">
+        <v>693</v>
+      </c>
+      <c r="O244" t="s">
+        <v>694</v>
+      </c>
+      <c r="P244" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q244" t="s">
+        <v>35</v>
+      </c>
+      <c r="R244" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="245" spans="13:18">
+      <c r="M245" t="s">
+        <v>17</v>
+      </c>
+      <c r="N245" t="s">
+        <v>695</v>
+      </c>
+      <c r="O245" t="s">
+        <v>696</v>
+      </c>
+      <c r="P245" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q245" t="s">
+        <v>35</v>
+      </c>
+      <c r="R245" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="246" spans="13:18">
+      <c r="M246" t="s">
+        <v>17</v>
+      </c>
+      <c r="N246" t="s">
+        <v>697</v>
+      </c>
+      <c r="O246" t="s">
+        <v>698</v>
+      </c>
+      <c r="P246" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q246" t="s">
+        <v>35</v>
+      </c>
+      <c r="R246" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="247" spans="13:18">
+      <c r="M247" t="s">
+        <v>17</v>
+      </c>
+      <c r="N247" t="s">
+        <v>699</v>
+      </c>
+      <c r="O247" t="s">
+        <v>700</v>
+      </c>
+      <c r="P247" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q247" t="s">
+        <v>35</v>
+      </c>
+      <c r="R247" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="248" spans="13:18">
+      <c r="M248" t="s">
+        <v>17</v>
+      </c>
+      <c r="N248" t="s">
+        <v>701</v>
+      </c>
+      <c r="O248" t="s">
+        <v>702</v>
+      </c>
+      <c r="P248" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q248" t="s">
+        <v>35</v>
+      </c>
+      <c r="R248" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="249" spans="13:18">
+      <c r="M249" t="s">
+        <v>17</v>
+      </c>
+      <c r="N249" t="s">
+        <v>703</v>
+      </c>
+      <c r="O249" t="s">
+        <v>704</v>
+      </c>
+      <c r="P249" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q249" t="s">
+        <v>35</v>
+      </c>
+      <c r="R249" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="250" spans="13:18">
+      <c r="M250" t="s">
+        <v>17</v>
+      </c>
+      <c r="N250" t="s">
+        <v>705</v>
+      </c>
+      <c r="O250" t="s">
+        <v>706</v>
+      </c>
+      <c r="P250" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q250" t="s">
+        <v>35</v>
+      </c>
+      <c r="R250" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="251" spans="13:18">
+      <c r="M251" t="s">
+        <v>17</v>
+      </c>
+      <c r="N251" t="s">
+        <v>707</v>
+      </c>
+      <c r="O251" t="s">
+        <v>708</v>
+      </c>
+      <c r="P251" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q251" t="s">
+        <v>35</v>
+      </c>
+      <c r="R251" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="252" spans="13:18">
+      <c r="M252" t="s">
+        <v>17</v>
+      </c>
+      <c r="N252" t="s">
+        <v>709</v>
+      </c>
+      <c r="O252" t="s">
+        <v>710</v>
+      </c>
+      <c r="P252" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q252" t="s">
+        <v>35</v>
+      </c>
+      <c r="R252" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="253" spans="13:18">
+      <c r="M253" t="s">
+        <v>17</v>
+      </c>
+      <c r="N253" t="s">
+        <v>711</v>
+      </c>
+      <c r="O253" t="s">
+        <v>712</v>
+      </c>
+      <c r="P253" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q253" t="s">
+        <v>35</v>
+      </c>
+      <c r="R253" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="254" spans="13:18">
+      <c r="M254" t="s">
+        <v>17</v>
+      </c>
+      <c r="N254" t="s">
+        <v>713</v>
+      </c>
+      <c r="O254" t="s">
+        <v>714</v>
+      </c>
+      <c r="P254" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q254" t="s">
+        <v>35</v>
+      </c>
+      <c r="R254" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="255" spans="13:18">
+      <c r="M255" t="s">
+        <v>17</v>
+      </c>
+      <c r="N255" t="s">
+        <v>715</v>
+      </c>
+      <c r="O255" t="s">
+        <v>716</v>
+      </c>
+      <c r="P255" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q255" t="s">
+        <v>35</v>
+      </c>
+      <c r="R255" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="256" spans="13:18">
+      <c r="M256" t="s">
+        <v>17</v>
+      </c>
+      <c r="N256" t="s">
+        <v>717</v>
+      </c>
+      <c r="O256" t="s">
+        <v>718</v>
+      </c>
+      <c r="P256" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q256" t="s">
+        <v>35</v>
+      </c>
+      <c r="R256" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="257" spans="13:18">
+      <c r="M257" t="s">
+        <v>17</v>
+      </c>
+      <c r="N257" t="s">
+        <v>719</v>
+      </c>
+      <c r="O257" t="s">
+        <v>720</v>
+      </c>
+      <c r="P257" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q257" t="s">
+        <v>35</v>
+      </c>
+      <c r="R257" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="258" spans="13:18">
+      <c r="M258" t="s">
+        <v>17</v>
+      </c>
+      <c r="N258" t="s">
+        <v>721</v>
+      </c>
+      <c r="O258" t="s">
+        <v>722</v>
+      </c>
+      <c r="P258" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q258" t="s">
+        <v>35</v>
+      </c>
+      <c r="R258" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="259" spans="13:18">
+      <c r="M259" t="s">
+        <v>17</v>
+      </c>
+      <c r="N259" t="s">
+        <v>723</v>
+      </c>
+      <c r="O259" t="s">
+        <v>724</v>
+      </c>
+      <c r="P259" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q259" t="s">
+        <v>35</v>
+      </c>
+      <c r="R259" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="260" spans="13:18">
+      <c r="M260" t="s">
+        <v>17</v>
+      </c>
+      <c r="N260" t="s">
+        <v>725</v>
+      </c>
+      <c r="O260" t="s">
+        <v>726</v>
+      </c>
+      <c r="P260" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q260" t="s">
+        <v>35</v>
+      </c>
+      <c r="R260" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="261" spans="13:18">
+      <c r="M261" t="s">
+        <v>17</v>
+      </c>
+      <c r="N261" t="s">
+        <v>727</v>
+      </c>
+      <c r="O261" t="s">
+        <v>728</v>
+      </c>
+      <c r="P261" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q261" t="s">
+        <v>35</v>
+      </c>
+      <c r="R261" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="262" spans="13:18">
+      <c r="M262" t="s">
+        <v>17</v>
+      </c>
+      <c r="N262" t="s">
+        <v>729</v>
+      </c>
+      <c r="O262" t="s">
+        <v>730</v>
+      </c>
+      <c r="P262" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q262" t="s">
+        <v>35</v>
+      </c>
+      <c r="R262" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="263" spans="13:18">
+      <c r="M263" t="s">
+        <v>17</v>
+      </c>
+      <c r="N263" t="s">
+        <v>731</v>
+      </c>
+      <c r="O263" t="s">
+        <v>732</v>
+      </c>
+      <c r="P263" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q263" t="s">
+        <v>35</v>
+      </c>
+      <c r="R263" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="264" spans="13:18">
+      <c r="M264" t="s">
+        <v>17</v>
+      </c>
+      <c r="N264" t="s">
+        <v>733</v>
+      </c>
+      <c r="O264" t="s">
+        <v>734</v>
+      </c>
+      <c r="P264" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q264" t="s">
+        <v>35</v>
+      </c>
+      <c r="R264" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="265" spans="13:18">
+      <c r="M265" t="s">
+        <v>17</v>
+      </c>
+      <c r="N265" t="s">
+        <v>735</v>
+      </c>
+      <c r="O265" t="s">
+        <v>736</v>
+      </c>
+      <c r="P265" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q265" t="s">
+        <v>35</v>
+      </c>
+      <c r="R265" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="266" spans="13:18">
+      <c r="M266" t="s">
+        <v>17</v>
+      </c>
+      <c r="N266" t="s">
+        <v>737</v>
+      </c>
+      <c r="O266" t="s">
+        <v>738</v>
+      </c>
+      <c r="P266" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q266" t="s">
+        <v>35</v>
+      </c>
+      <c r="R266" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="267" spans="13:18">
+      <c r="M267" t="s">
+        <v>17</v>
+      </c>
+      <c r="N267" t="s">
+        <v>739</v>
+      </c>
+      <c r="O267" t="s">
+        <v>740</v>
+      </c>
+      <c r="P267" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q267" t="s">
+        <v>35</v>
+      </c>
+      <c r="R267" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="268" spans="13:18">
+      <c r="M268" t="s">
+        <v>17</v>
+      </c>
+      <c r="N268" t="s">
+        <v>741</v>
+      </c>
+      <c r="O268" t="s">
+        <v>742</v>
+      </c>
+      <c r="P268" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q268" t="s">
+        <v>35</v>
+      </c>
+      <c r="R268" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="269" spans="13:18">
+      <c r="M269" t="s">
+        <v>17</v>
+      </c>
+      <c r="N269" t="s">
+        <v>743</v>
+      </c>
+      <c r="O269" t="s">
+        <v>744</v>
+      </c>
+      <c r="P269" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q269" t="s">
+        <v>35</v>
+      </c>
+      <c r="R269" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="270" spans="13:18">
+      <c r="M270" t="s">
+        <v>17</v>
+      </c>
+      <c r="N270" t="s">
+        <v>745</v>
+      </c>
+      <c r="O270" t="s">
+        <v>746</v>
+      </c>
+      <c r="P270" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q270" t="s">
+        <v>35</v>
+      </c>
+      <c r="R270" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="271" spans="13:18">
+      <c r="M271" t="s">
+        <v>17</v>
+      </c>
+      <c r="N271" t="s">
+        <v>747</v>
+      </c>
+      <c r="O271" t="s">
+        <v>748</v>
+      </c>
+      <c r="P271" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q271" t="s">
+        <v>35</v>
+      </c>
+      <c r="R271" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="272" spans="13:18">
+      <c r="M272" t="s">
+        <v>17</v>
+      </c>
+      <c r="N272" t="s">
+        <v>749</v>
+      </c>
+      <c r="O272" t="s">
+        <v>750</v>
+      </c>
+      <c r="P272" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q272" t="s">
+        <v>35</v>
+      </c>
+      <c r="R272" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="273" spans="13:18">
+      <c r="M273" t="s">
+        <v>17</v>
+      </c>
+      <c r="N273" t="s">
+        <v>751</v>
+      </c>
+      <c r="O273" t="s">
+        <v>752</v>
+      </c>
+      <c r="P273" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q273" t="s">
+        <v>35</v>
+      </c>
+      <c r="R273" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="274" spans="13:18">
+      <c r="M274" t="s">
+        <v>17</v>
+      </c>
+      <c r="N274" t="s">
+        <v>753</v>
+      </c>
+      <c r="O274" t="s">
+        <v>754</v>
+      </c>
+      <c r="P274" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q274" t="s">
+        <v>35</v>
+      </c>
+      <c r="R274" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="275" spans="13:18">
+      <c r="M275" t="s">
+        <v>17</v>
+      </c>
+      <c r="N275" t="s">
+        <v>755</v>
+      </c>
+      <c r="O275" t="s">
+        <v>756</v>
+      </c>
+      <c r="P275" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q275" t="s">
+        <v>35</v>
+      </c>
+      <c r="R275" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="276" spans="13:18">
+      <c r="M276" t="s">
+        <v>17</v>
+      </c>
+      <c r="N276" t="s">
+        <v>757</v>
+      </c>
+      <c r="O276" t="s">
+        <v>758</v>
+      </c>
+      <c r="P276" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q276" t="s">
+        <v>35</v>
+      </c>
+      <c r="R276" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="277" spans="13:18">
+      <c r="M277" t="s">
+        <v>17</v>
+      </c>
+      <c r="N277" t="s">
+        <v>759</v>
+      </c>
+      <c r="O277" t="s">
+        <v>760</v>
+      </c>
+      <c r="P277" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q277" t="s">
+        <v>35</v>
+      </c>
+      <c r="R277" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="278" spans="13:18">
+      <c r="M278" t="s">
+        <v>17</v>
+      </c>
+      <c r="N278" t="s">
+        <v>761</v>
+      </c>
+      <c r="O278" t="s">
+        <v>762</v>
+      </c>
+      <c r="P278" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q278" t="s">
+        <v>35</v>
+      </c>
+      <c r="R278" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="279" spans="13:18">
+      <c r="M279" t="s">
+        <v>17</v>
+      </c>
+      <c r="N279" t="s">
+        <v>763</v>
+      </c>
+      <c r="O279" t="s">
+        <v>764</v>
+      </c>
+      <c r="P279" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q279" t="s">
+        <v>35</v>
+      </c>
+      <c r="R279" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="280" spans="13:18">
+      <c r="M280" t="s">
+        <v>17</v>
+      </c>
+      <c r="N280" t="s">
+        <v>765</v>
+      </c>
+      <c r="O280" t="s">
+        <v>766</v>
+      </c>
+      <c r="P280" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q280" t="s">
+        <v>35</v>
+      </c>
+      <c r="R280" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="281" spans="13:18">
+      <c r="M281" t="s">
+        <v>17</v>
+      </c>
+      <c r="N281" t="s">
+        <v>767</v>
+      </c>
+      <c r="O281" t="s">
+        <v>768</v>
+      </c>
+      <c r="P281" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q281" t="s">
+        <v>35</v>
+      </c>
+      <c r="R281" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="282" spans="13:18">
+      <c r="M282" t="s">
+        <v>17</v>
+      </c>
+      <c r="N282" t="s">
+        <v>769</v>
+      </c>
+      <c r="O282" t="s">
+        <v>770</v>
+      </c>
+      <c r="P282" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q282" t="s">
+        <v>35</v>
+      </c>
+      <c r="R282" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="283" spans="13:18">
+      <c r="M283" t="s">
+        <v>17</v>
+      </c>
+      <c r="N283" t="s">
+        <v>771</v>
+      </c>
+      <c r="O283" t="s">
+        <v>772</v>
+      </c>
+      <c r="P283" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q283" t="s">
+        <v>35</v>
+      </c>
+      <c r="R283" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="284" spans="13:18">
+      <c r="M284" t="s">
+        <v>17</v>
+      </c>
+      <c r="N284" t="s">
+        <v>773</v>
+      </c>
+      <c r="O284" t="s">
+        <v>774</v>
+      </c>
+      <c r="P284" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q284" t="s">
+        <v>35</v>
+      </c>
+      <c r="R284" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="285" spans="13:18">
+      <c r="M285" t="s">
+        <v>17</v>
+      </c>
+      <c r="N285" t="s">
+        <v>775</v>
+      </c>
+      <c r="O285" t="s">
+        <v>776</v>
+      </c>
+      <c r="P285" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q285" t="s">
+        <v>35</v>
+      </c>
+      <c r="R285" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="286" spans="13:18">
+      <c r="M286" t="s">
+        <v>17</v>
+      </c>
+      <c r="N286" t="s">
+        <v>777</v>
+      </c>
+      <c r="O286" t="s">
+        <v>778</v>
+      </c>
+      <c r="P286" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q286" t="s">
+        <v>35</v>
+      </c>
+      <c r="R286" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="287" spans="13:18">
+      <c r="M287" t="s">
+        <v>17</v>
+      </c>
+      <c r="N287" t="s">
+        <v>779</v>
+      </c>
+      <c r="O287" t="s">
+        <v>780</v>
+      </c>
+      <c r="P287" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q287" t="s">
+        <v>35</v>
+      </c>
+      <c r="R287" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="288" spans="13:18">
+      <c r="M288" t="s">
+        <v>17</v>
+      </c>
+      <c r="N288" t="s">
+        <v>781</v>
+      </c>
+      <c r="O288" t="s">
+        <v>782</v>
+      </c>
+      <c r="P288" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q288" t="s">
+        <v>35</v>
+      </c>
+      <c r="R288" t="s">
+        <v>216</v>
       </c>
     </row>
   </sheetData>

--- a/VerveStacks_CHN/SysSettings.xlsx
+++ b/VerveStacks_CHN/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A090746B-41EF-46A1-8166-A4E355C4498C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9927CB8-7DFF-4459-A804-1265822C3869}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_CHN/SysSettings.xlsx
+++ b/VerveStacks_CHN/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9927CB8-7DFF-4459-A804-1265822C3869}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A14E87F-EBA8-454D-A20C-32B69E31791A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_CHN/SysSettings.xlsx
+++ b/VerveStacks_CHN/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A14E87F-EBA8-454D-A20C-32B69E31791A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EB4E8B1-D223-45F2-9EC4-AAE86A6F36F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_CHN/SysSettings.xlsx
+++ b/VerveStacks_CHN/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EB4E8B1-D223-45F2-9EC4-AAE86A6F36F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14755E61-8575-45A3-89DA-E81F67FF9C3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_CHN/SysSettings.xlsx
+++ b/VerveStacks_CHN/SysSettings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14755E61-8575-45A3-89DA-E81F67FF9C3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F970237D-295A-4B67-BDFC-DC69C14B43C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="system_settings" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2256" uniqueCount="783">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2257" uniqueCount="784">
   <si>
     <t>~BookRegions_Map</t>
   </si>
@@ -674,6 +674,9 @@
   </si>
   <si>
     <t>OIL</t>
+  </si>
+  <si>
+    <t>cap_bnd</t>
   </si>
   <si>
     <t>CHN</t>
@@ -4777,7 +4780,7 @@
         <v>7</v>
       </c>
       <c r="C4" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F4" t="s">
         <v>36</v>
@@ -4860,7 +4863,7 @@
         <v>16</v>
       </c>
       <c r="M4" s="5" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N4" s="5" t="s">
         <v>10</v>
@@ -4892,10 +4895,10 @@
         <v>17</v>
       </c>
       <c r="N5" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O5" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="P5" t="s">
         <v>25</v>
@@ -4904,7 +4907,7 @@
         <v>35</v>
       </c>
       <c r="R5" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="6" spans="2:18">
@@ -4921,10 +4924,10 @@
         <v>17</v>
       </c>
       <c r="N6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="P6" t="s">
         <v>25</v>
@@ -4933,7 +4936,7 @@
         <v>35</v>
       </c>
       <c r="R6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="7" spans="2:18">
@@ -4950,10 +4953,10 @@
         <v>17</v>
       </c>
       <c r="N7" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="O7" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P7" t="s">
         <v>25</v>
@@ -4962,7 +4965,7 @@
         <v>35</v>
       </c>
       <c r="R7" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="8" spans="2:18">
@@ -4979,10 +4982,10 @@
         <v>17</v>
       </c>
       <c r="N8" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="O8" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="P8" t="s">
         <v>25</v>
@@ -4991,7 +4994,7 @@
         <v>35</v>
       </c>
       <c r="R8" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="9" spans="2:18">
@@ -5008,10 +5011,10 @@
         <v>17</v>
       </c>
       <c r="N9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="O9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="P9" t="s">
         <v>25</v>
@@ -5020,7 +5023,7 @@
         <v>35</v>
       </c>
       <c r="R9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="10" spans="2:18">
@@ -5037,10 +5040,10 @@
         <v>17</v>
       </c>
       <c r="N10" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="O10" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="P10" t="s">
         <v>25</v>
@@ -5049,7 +5052,7 @@
         <v>35</v>
       </c>
       <c r="R10" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="11" spans="2:18">
@@ -5066,10 +5069,10 @@
         <v>17</v>
       </c>
       <c r="N11" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="O11" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="P11" t="s">
         <v>25</v>
@@ -5078,7 +5081,7 @@
         <v>35</v>
       </c>
       <c r="R11" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="12" spans="2:18">
@@ -5095,10 +5098,10 @@
         <v>17</v>
       </c>
       <c r="N12" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="O12" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="P12" t="s">
         <v>25</v>
@@ -5107,7 +5110,7 @@
         <v>35</v>
       </c>
       <c r="R12" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="13" spans="2:18">
@@ -5124,10 +5127,10 @@
         <v>17</v>
       </c>
       <c r="N13" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O13" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="P13" t="s">
         <v>25</v>
@@ -5136,7 +5139,7 @@
         <v>35</v>
       </c>
       <c r="R13" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="14" spans="2:18">
@@ -5156,10 +5159,10 @@
         <v>17</v>
       </c>
       <c r="N14" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O14" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="P14" t="s">
         <v>25</v>
@@ -5168,7 +5171,7 @@
         <v>35</v>
       </c>
       <c r="R14" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="15" spans="2:18">
@@ -5188,10 +5191,10 @@
         <v>17</v>
       </c>
       <c r="N15" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="O15" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="P15" t="s">
         <v>25</v>
@@ -5200,7 +5203,7 @@
         <v>35</v>
       </c>
       <c r="R15" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="16" spans="2:18">
@@ -5229,10 +5232,10 @@
         <v>17</v>
       </c>
       <c r="N16" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="O16" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="P16" t="s">
         <v>25</v>
@@ -5241,7 +5244,7 @@
         <v>35</v>
       </c>
       <c r="R16" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="17" spans="2:18">
@@ -5261,10 +5264,10 @@
         <v>17</v>
       </c>
       <c r="N17" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O17" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="P17" t="s">
         <v>25</v>
@@ -5273,7 +5276,7 @@
         <v>35</v>
       </c>
       <c r="R17" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="18" spans="2:18">
@@ -5293,10 +5296,10 @@
         <v>17</v>
       </c>
       <c r="N18" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="O18" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="P18" t="s">
         <v>25</v>
@@ -5305,7 +5308,7 @@
         <v>35</v>
       </c>
       <c r="R18" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="19" spans="2:18">
@@ -5325,10 +5328,10 @@
         <v>17</v>
       </c>
       <c r="N19" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="O19" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="P19" t="s">
         <v>25</v>
@@ -5337,7 +5340,7 @@
         <v>35</v>
       </c>
       <c r="R19" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="20" spans="2:18">
@@ -5357,10 +5360,10 @@
         <v>17</v>
       </c>
       <c r="N20" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="O20" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="P20" t="s">
         <v>25</v>
@@ -5369,7 +5372,7 @@
         <v>35</v>
       </c>
       <c r="R20" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="21" spans="2:18">
@@ -5395,10 +5398,10 @@
         <v>17</v>
       </c>
       <c r="N21" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O21" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="P21" t="s">
         <v>25</v>
@@ -5407,7 +5410,7 @@
         <v>35</v>
       </c>
       <c r="R21" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="22" spans="2:18">
@@ -5427,10 +5430,10 @@
         <v>17</v>
       </c>
       <c r="N22" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="O22" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="P22" t="s">
         <v>25</v>
@@ -5439,7 +5442,7 @@
         <v>35</v>
       </c>
       <c r="R22" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="23" spans="2:18">
@@ -5456,10 +5459,10 @@
         <v>17</v>
       </c>
       <c r="N23" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="O23" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="P23" t="s">
         <v>25</v>
@@ -5468,7 +5471,7 @@
         <v>35</v>
       </c>
       <c r="R23" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="24" spans="2:18">
@@ -5485,10 +5488,10 @@
         <v>17</v>
       </c>
       <c r="N24" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O24" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="P24" t="s">
         <v>25</v>
@@ -5497,7 +5500,7 @@
         <v>35</v>
       </c>
       <c r="R24" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="25" spans="2:18">
@@ -5505,10 +5508,10 @@
         <v>17</v>
       </c>
       <c r="N25" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="O25" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="P25" t="s">
         <v>25</v>
@@ -5517,7 +5520,7 @@
         <v>35</v>
       </c>
       <c r="R25" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="26" spans="2:18">
@@ -5525,10 +5528,10 @@
         <v>17</v>
       </c>
       <c r="N26" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="O26" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P26" t="s">
         <v>25</v>
@@ -5537,7 +5540,7 @@
         <v>35</v>
       </c>
       <c r="R26" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="27" spans="2:18">
@@ -5545,10 +5548,10 @@
         <v>17</v>
       </c>
       <c r="N27" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="O27" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="P27" t="s">
         <v>25</v>
@@ -5557,7 +5560,7 @@
         <v>35</v>
       </c>
       <c r="R27" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="28" spans="2:18">
@@ -5565,10 +5568,10 @@
         <v>17</v>
       </c>
       <c r="N28" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="O28" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="P28" t="s">
         <v>25</v>
@@ -5577,7 +5580,7 @@
         <v>35</v>
       </c>
       <c r="R28" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="29" spans="2:18">
@@ -5585,10 +5588,10 @@
         <v>17</v>
       </c>
       <c r="N29" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O29" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P29" t="s">
         <v>25</v>
@@ -5597,7 +5600,7 @@
         <v>35</v>
       </c>
       <c r="R29" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="30" spans="2:18">
@@ -5605,10 +5608,10 @@
         <v>17</v>
       </c>
       <c r="N30" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="O30" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P30" t="s">
         <v>25</v>
@@ -5617,7 +5620,7 @@
         <v>35</v>
       </c>
       <c r="R30" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="31" spans="2:18">
@@ -5625,10 +5628,10 @@
         <v>17</v>
       </c>
       <c r="N31" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="O31" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="P31" t="s">
         <v>25</v>
@@ -5637,7 +5640,7 @@
         <v>35</v>
       </c>
       <c r="R31" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="32" spans="2:18">
@@ -5645,10 +5648,10 @@
         <v>17</v>
       </c>
       <c r="N32" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O32" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="P32" t="s">
         <v>25</v>
@@ -5657,7 +5660,7 @@
         <v>35</v>
       </c>
       <c r="R32" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="33" spans="13:18">
@@ -5665,10 +5668,10 @@
         <v>17</v>
       </c>
       <c r="N33" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O33" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="P33" t="s">
         <v>25</v>
@@ -5677,7 +5680,7 @@
         <v>35</v>
       </c>
       <c r="R33" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="34" spans="13:18">
@@ -5685,10 +5688,10 @@
         <v>17</v>
       </c>
       <c r="N34" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O34" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="P34" t="s">
         <v>25</v>
@@ -5697,7 +5700,7 @@
         <v>35</v>
       </c>
       <c r="R34" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="35" spans="13:18">
@@ -5705,10 +5708,10 @@
         <v>17</v>
       </c>
       <c r="N35" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O35" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="P35" t="s">
         <v>25</v>
@@ -5717,7 +5720,7 @@
         <v>35</v>
       </c>
       <c r="R35" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="36" spans="13:18">
@@ -5725,10 +5728,10 @@
         <v>17</v>
       </c>
       <c r="N36" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O36" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="P36" t="s">
         <v>25</v>
@@ -5737,7 +5740,7 @@
         <v>35</v>
       </c>
       <c r="R36" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="37" spans="13:18">
@@ -5745,10 +5748,10 @@
         <v>17</v>
       </c>
       <c r="N37" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O37" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="P37" t="s">
         <v>25</v>
@@ -5757,7 +5760,7 @@
         <v>35</v>
       </c>
       <c r="R37" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="38" spans="13:18">
@@ -5765,10 +5768,10 @@
         <v>17</v>
       </c>
       <c r="N38" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O38" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="P38" t="s">
         <v>25</v>
@@ -5777,7 +5780,7 @@
         <v>35</v>
       </c>
       <c r="R38" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="39" spans="13:18">
@@ -5785,10 +5788,10 @@
         <v>17</v>
       </c>
       <c r="N39" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="O39" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="P39" t="s">
         <v>25</v>
@@ -5797,7 +5800,7 @@
         <v>35</v>
       </c>
       <c r="R39" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="40" spans="13:18">
@@ -5805,10 +5808,10 @@
         <v>17</v>
       </c>
       <c r="N40" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="O40" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="P40" t="s">
         <v>25</v>
@@ -5817,7 +5820,7 @@
         <v>35</v>
       </c>
       <c r="R40" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="41" spans="13:18">
@@ -5825,10 +5828,10 @@
         <v>17</v>
       </c>
       <c r="N41" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="O41" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="P41" t="s">
         <v>25</v>
@@ -5837,7 +5840,7 @@
         <v>35</v>
       </c>
       <c r="R41" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="42" spans="13:18">
@@ -5845,10 +5848,10 @@
         <v>17</v>
       </c>
       <c r="N42" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="O42" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="P42" t="s">
         <v>25</v>
@@ -5857,7 +5860,7 @@
         <v>35</v>
       </c>
       <c r="R42" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="43" spans="13:18">
@@ -5865,10 +5868,10 @@
         <v>17</v>
       </c>
       <c r="N43" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="O43" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="P43" t="s">
         <v>25</v>
@@ -5877,7 +5880,7 @@
         <v>35</v>
       </c>
       <c r="R43" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="44" spans="13:18">
@@ -5885,10 +5888,10 @@
         <v>17</v>
       </c>
       <c r="N44" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="O44" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="P44" t="s">
         <v>25</v>
@@ -5897,7 +5900,7 @@
         <v>35</v>
       </c>
       <c r="R44" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="45" spans="13:18">
@@ -5905,10 +5908,10 @@
         <v>17</v>
       </c>
       <c r="N45" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="O45" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="P45" t="s">
         <v>25</v>
@@ -5917,7 +5920,7 @@
         <v>35</v>
       </c>
       <c r="R45" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="46" spans="13:18">
@@ -5925,10 +5928,10 @@
         <v>17</v>
       </c>
       <c r="N46" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="O46" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="P46" t="s">
         <v>25</v>
@@ -5937,7 +5940,7 @@
         <v>35</v>
       </c>
       <c r="R46" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="47" spans="13:18">
@@ -5945,10 +5948,10 @@
         <v>17</v>
       </c>
       <c r="N47" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="O47" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="P47" t="s">
         <v>25</v>
@@ -5957,7 +5960,7 @@
         <v>35</v>
       </c>
       <c r="R47" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="48" spans="13:18">
@@ -5965,10 +5968,10 @@
         <v>17</v>
       </c>
       <c r="N48" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="O48" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="P48" t="s">
         <v>25</v>
@@ -5977,7 +5980,7 @@
         <v>35</v>
       </c>
       <c r="R48" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="49" spans="13:18">
@@ -5985,10 +5988,10 @@
         <v>17</v>
       </c>
       <c r="N49" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="O49" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P49" t="s">
         <v>25</v>
@@ -5997,7 +6000,7 @@
         <v>35</v>
       </c>
       <c r="R49" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="50" spans="13:18">
@@ -6005,10 +6008,10 @@
         <v>17</v>
       </c>
       <c r="N50" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O50" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="P50" t="s">
         <v>25</v>
@@ -6017,7 +6020,7 @@
         <v>35</v>
       </c>
       <c r="R50" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="51" spans="13:18">
@@ -6025,10 +6028,10 @@
         <v>17</v>
       </c>
       <c r="N51" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O51" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="P51" t="s">
         <v>25</v>
@@ -6037,7 +6040,7 @@
         <v>35</v>
       </c>
       <c r="R51" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="52" spans="13:18">
@@ -6045,10 +6048,10 @@
         <v>17</v>
       </c>
       <c r="N52" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="O52" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="P52" t="s">
         <v>25</v>
@@ -6057,7 +6060,7 @@
         <v>35</v>
       </c>
       <c r="R52" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="53" spans="13:18">
@@ -6065,10 +6068,10 @@
         <v>17</v>
       </c>
       <c r="N53" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="O53" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="P53" t="s">
         <v>25</v>
@@ -6077,7 +6080,7 @@
         <v>35</v>
       </c>
       <c r="R53" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="54" spans="13:18">
@@ -6085,10 +6088,10 @@
         <v>17</v>
       </c>
       <c r="N54" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="O54" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="P54" t="s">
         <v>25</v>
@@ -6097,7 +6100,7 @@
         <v>35</v>
       </c>
       <c r="R54" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="55" spans="13:18">
@@ -6105,10 +6108,10 @@
         <v>17</v>
       </c>
       <c r="N55" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="O55" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="P55" t="s">
         <v>25</v>
@@ -6117,7 +6120,7 @@
         <v>35</v>
       </c>
       <c r="R55" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="56" spans="13:18">
@@ -6125,10 +6128,10 @@
         <v>17</v>
       </c>
       <c r="N56" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O56" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="P56" t="s">
         <v>25</v>
@@ -6137,7 +6140,7 @@
         <v>35</v>
       </c>
       <c r="R56" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="57" spans="13:18">
@@ -6145,10 +6148,10 @@
         <v>17</v>
       </c>
       <c r="N57" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="O57" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="P57" t="s">
         <v>25</v>
@@ -6157,7 +6160,7 @@
         <v>35</v>
       </c>
       <c r="R57" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="58" spans="13:18">
@@ -6165,10 +6168,10 @@
         <v>17</v>
       </c>
       <c r="N58" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="O58" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="P58" t="s">
         <v>25</v>
@@ -6177,7 +6180,7 @@
         <v>35</v>
       </c>
       <c r="R58" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="59" spans="13:18">
@@ -6185,10 +6188,10 @@
         <v>17</v>
       </c>
       <c r="N59" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="O59" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="P59" t="s">
         <v>25</v>
@@ -6197,7 +6200,7 @@
         <v>35</v>
       </c>
       <c r="R59" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="60" spans="13:18">
@@ -6205,10 +6208,10 @@
         <v>17</v>
       </c>
       <c r="N60" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="O60" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="P60" t="s">
         <v>25</v>
@@ -6217,7 +6220,7 @@
         <v>35</v>
       </c>
       <c r="R60" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="61" spans="13:18">
@@ -6225,10 +6228,10 @@
         <v>17</v>
       </c>
       <c r="N61" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="O61" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="P61" t="s">
         <v>25</v>
@@ -6237,7 +6240,7 @@
         <v>35</v>
       </c>
       <c r="R61" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="62" spans="13:18">
@@ -6245,10 +6248,10 @@
         <v>17</v>
       </c>
       <c r="N62" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="O62" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="P62" t="s">
         <v>25</v>
@@ -6257,7 +6260,7 @@
         <v>35</v>
       </c>
       <c r="R62" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="63" spans="13:18">
@@ -6265,10 +6268,10 @@
         <v>17</v>
       </c>
       <c r="N63" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="O63" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="P63" t="s">
         <v>25</v>
@@ -6277,7 +6280,7 @@
         <v>35</v>
       </c>
       <c r="R63" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="64" spans="13:18">
@@ -6285,10 +6288,10 @@
         <v>17</v>
       </c>
       <c r="N64" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="O64" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="P64" t="s">
         <v>25</v>
@@ -6297,7 +6300,7 @@
         <v>35</v>
       </c>
       <c r="R64" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="65" spans="13:18">
@@ -6305,10 +6308,10 @@
         <v>17</v>
       </c>
       <c r="N65" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="O65" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="P65" t="s">
         <v>25</v>
@@ -6317,7 +6320,7 @@
         <v>35</v>
       </c>
       <c r="R65" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="66" spans="13:18">
@@ -6325,10 +6328,10 @@
         <v>17</v>
       </c>
       <c r="N66" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="O66" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="P66" t="s">
         <v>25</v>
@@ -6337,7 +6340,7 @@
         <v>35</v>
       </c>
       <c r="R66" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="67" spans="13:18">
@@ -6345,10 +6348,10 @@
         <v>17</v>
       </c>
       <c r="N67" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="O67" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="P67" t="s">
         <v>25</v>
@@ -6357,7 +6360,7 @@
         <v>35</v>
       </c>
       <c r="R67" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="68" spans="13:18">
@@ -6365,10 +6368,10 @@
         <v>17</v>
       </c>
       <c r="N68" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="O68" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="P68" t="s">
         <v>25</v>
@@ -6377,7 +6380,7 @@
         <v>35</v>
       </c>
       <c r="R68" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="69" spans="13:18">
@@ -6385,10 +6388,10 @@
         <v>17</v>
       </c>
       <c r="N69" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="O69" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="P69" t="s">
         <v>25</v>
@@ -6397,7 +6400,7 @@
         <v>35</v>
       </c>
       <c r="R69" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="70" spans="13:18">
@@ -6405,10 +6408,10 @@
         <v>17</v>
       </c>
       <c r="N70" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="O70" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="P70" t="s">
         <v>25</v>
@@ -6417,7 +6420,7 @@
         <v>35</v>
       </c>
       <c r="R70" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="71" spans="13:18">
@@ -6425,10 +6428,10 @@
         <v>17</v>
       </c>
       <c r="N71" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="O71" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="P71" t="s">
         <v>25</v>
@@ -6437,7 +6440,7 @@
         <v>35</v>
       </c>
       <c r="R71" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="72" spans="13:18">
@@ -6445,10 +6448,10 @@
         <v>17</v>
       </c>
       <c r="N72" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="O72" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="P72" t="s">
         <v>25</v>
@@ -6457,7 +6460,7 @@
         <v>35</v>
       </c>
       <c r="R72" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="73" spans="13:18">
@@ -6465,10 +6468,10 @@
         <v>17</v>
       </c>
       <c r="N73" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="O73" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="P73" t="s">
         <v>25</v>
@@ -6477,7 +6480,7 @@
         <v>35</v>
       </c>
       <c r="R73" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="74" spans="13:18">
@@ -6485,10 +6488,10 @@
         <v>17</v>
       </c>
       <c r="N74" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="O74" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="P74" t="s">
         <v>25</v>
@@ -6497,7 +6500,7 @@
         <v>35</v>
       </c>
       <c r="R74" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="75" spans="13:18">
@@ -6505,10 +6508,10 @@
         <v>17</v>
       </c>
       <c r="N75" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="O75" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="P75" t="s">
         <v>25</v>
@@ -6517,7 +6520,7 @@
         <v>35</v>
       </c>
       <c r="R75" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="76" spans="13:18">
@@ -6525,10 +6528,10 @@
         <v>17</v>
       </c>
       <c r="N76" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="O76" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="P76" t="s">
         <v>25</v>
@@ -6537,7 +6540,7 @@
         <v>35</v>
       </c>
       <c r="R76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="77" spans="13:18">
@@ -6545,10 +6548,10 @@
         <v>17</v>
       </c>
       <c r="N77" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="O77" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="P77" t="s">
         <v>25</v>
@@ -6557,7 +6560,7 @@
         <v>35</v>
       </c>
       <c r="R77" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="78" spans="13:18">
@@ -6565,10 +6568,10 @@
         <v>17</v>
       </c>
       <c r="N78" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="O78" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="P78" t="s">
         <v>25</v>
@@ -6577,7 +6580,7 @@
         <v>35</v>
       </c>
       <c r="R78" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="79" spans="13:18">
@@ -6585,10 +6588,10 @@
         <v>17</v>
       </c>
       <c r="N79" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="O79" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="P79" t="s">
         <v>25</v>
@@ -6597,7 +6600,7 @@
         <v>35</v>
       </c>
       <c r="R79" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="80" spans="13:18">
@@ -6605,10 +6608,10 @@
         <v>17</v>
       </c>
       <c r="N80" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="O80" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="P80" t="s">
         <v>25</v>
@@ -6617,7 +6620,7 @@
         <v>35</v>
       </c>
       <c r="R80" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="81" spans="13:18">
@@ -6625,10 +6628,10 @@
         <v>17</v>
       </c>
       <c r="N81" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="O81" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="P81" t="s">
         <v>25</v>
@@ -6637,7 +6640,7 @@
         <v>35</v>
       </c>
       <c r="R81" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="82" spans="13:18">
@@ -6645,10 +6648,10 @@
         <v>17</v>
       </c>
       <c r="N82" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="O82" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="P82" t="s">
         <v>25</v>
@@ -6657,7 +6660,7 @@
         <v>35</v>
       </c>
       <c r="R82" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="83" spans="13:18">
@@ -6665,10 +6668,10 @@
         <v>17</v>
       </c>
       <c r="N83" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="O83" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="P83" t="s">
         <v>25</v>
@@ -6677,7 +6680,7 @@
         <v>35</v>
       </c>
       <c r="R83" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="84" spans="13:18">
@@ -6685,10 +6688,10 @@
         <v>17</v>
       </c>
       <c r="N84" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="O84" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="P84" t="s">
         <v>25</v>
@@ -6697,7 +6700,7 @@
         <v>35</v>
       </c>
       <c r="R84" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="85" spans="13:18">
@@ -6705,10 +6708,10 @@
         <v>17</v>
       </c>
       <c r="N85" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="O85" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="P85" t="s">
         <v>25</v>
@@ -6717,7 +6720,7 @@
         <v>35</v>
       </c>
       <c r="R85" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="86" spans="13:18">
@@ -6725,10 +6728,10 @@
         <v>17</v>
       </c>
       <c r="N86" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="O86" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="P86" t="s">
         <v>25</v>
@@ -6737,7 +6740,7 @@
         <v>35</v>
       </c>
       <c r="R86" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="87" spans="13:18">
@@ -6745,10 +6748,10 @@
         <v>17</v>
       </c>
       <c r="N87" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="O87" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="P87" t="s">
         <v>25</v>
@@ -6757,7 +6760,7 @@
         <v>35</v>
       </c>
       <c r="R87" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="88" spans="13:18">
@@ -6765,10 +6768,10 @@
         <v>17</v>
       </c>
       <c r="N88" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="O88" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="P88" t="s">
         <v>25</v>
@@ -6777,7 +6780,7 @@
         <v>35</v>
       </c>
       <c r="R88" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="89" spans="13:18">
@@ -6785,10 +6788,10 @@
         <v>17</v>
       </c>
       <c r="N89" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="O89" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="P89" t="s">
         <v>25</v>
@@ -6797,7 +6800,7 @@
         <v>35</v>
       </c>
       <c r="R89" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="90" spans="13:18">
@@ -6805,10 +6808,10 @@
         <v>17</v>
       </c>
       <c r="N90" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="O90" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="P90" t="s">
         <v>25</v>
@@ -6817,7 +6820,7 @@
         <v>35</v>
       </c>
       <c r="R90" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="91" spans="13:18">
@@ -6825,10 +6828,10 @@
         <v>17</v>
       </c>
       <c r="N91" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="O91" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="P91" t="s">
         <v>25</v>
@@ -6837,7 +6840,7 @@
         <v>35</v>
       </c>
       <c r="R91" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="92" spans="13:18">
@@ -6845,10 +6848,10 @@
         <v>17</v>
       </c>
       <c r="N92" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="O92" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="P92" t="s">
         <v>25</v>
@@ -6857,7 +6860,7 @@
         <v>35</v>
       </c>
       <c r="R92" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="93" spans="13:18">
@@ -6865,10 +6868,10 @@
         <v>17</v>
       </c>
       <c r="N93" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="O93" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="P93" t="s">
         <v>25</v>
@@ -6877,7 +6880,7 @@
         <v>35</v>
       </c>
       <c r="R93" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="94" spans="13:18">
@@ -6885,10 +6888,10 @@
         <v>17</v>
       </c>
       <c r="N94" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="O94" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="P94" t="s">
         <v>25</v>
@@ -6897,7 +6900,7 @@
         <v>35</v>
       </c>
       <c r="R94" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="95" spans="13:18">
@@ -6905,10 +6908,10 @@
         <v>17</v>
       </c>
       <c r="N95" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="O95" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="P95" t="s">
         <v>25</v>
@@ -6917,7 +6920,7 @@
         <v>35</v>
       </c>
       <c r="R95" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="96" spans="13:18">
@@ -6925,10 +6928,10 @@
         <v>17</v>
       </c>
       <c r="N96" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="O96" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="P96" t="s">
         <v>25</v>
@@ -6937,7 +6940,7 @@
         <v>35</v>
       </c>
       <c r="R96" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="97" spans="13:18">
@@ -6945,10 +6948,10 @@
         <v>17</v>
       </c>
       <c r="N97" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="O97" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="P97" t="s">
         <v>25</v>
@@ -6957,7 +6960,7 @@
         <v>35</v>
       </c>
       <c r="R97" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="98" spans="13:18">
@@ -6965,10 +6968,10 @@
         <v>17</v>
       </c>
       <c r="N98" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="O98" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="P98" t="s">
         <v>25</v>
@@ -6977,7 +6980,7 @@
         <v>35</v>
       </c>
       <c r="R98" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="99" spans="13:18">
@@ -6985,10 +6988,10 @@
         <v>17</v>
       </c>
       <c r="N99" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="O99" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="P99" t="s">
         <v>25</v>
@@ -6997,7 +7000,7 @@
         <v>35</v>
       </c>
       <c r="R99" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="100" spans="13:18">
@@ -7005,10 +7008,10 @@
         <v>17</v>
       </c>
       <c r="N100" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="O100" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="P100" t="s">
         <v>25</v>
@@ -7017,7 +7020,7 @@
         <v>35</v>
       </c>
       <c r="R100" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="101" spans="13:18">
@@ -7025,10 +7028,10 @@
         <v>17</v>
       </c>
       <c r="N101" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="O101" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="P101" t="s">
         <v>25</v>
@@ -7037,7 +7040,7 @@
         <v>35</v>
       </c>
       <c r="R101" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="102" spans="13:18">
@@ -7045,10 +7048,10 @@
         <v>17</v>
       </c>
       <c r="N102" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="O102" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="P102" t="s">
         <v>25</v>
@@ -7057,7 +7060,7 @@
         <v>35</v>
       </c>
       <c r="R102" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="103" spans="13:18">
@@ -7065,10 +7068,10 @@
         <v>17</v>
       </c>
       <c r="N103" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="O103" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="P103" t="s">
         <v>25</v>
@@ -7077,7 +7080,7 @@
         <v>35</v>
       </c>
       <c r="R103" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="104" spans="13:18">
@@ -7085,10 +7088,10 @@
         <v>17</v>
       </c>
       <c r="N104" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="O104" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="P104" t="s">
         <v>25</v>
@@ -7097,7 +7100,7 @@
         <v>35</v>
       </c>
       <c r="R104" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="105" spans="13:18">
@@ -7105,10 +7108,10 @@
         <v>17</v>
       </c>
       <c r="N105" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="O105" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="P105" t="s">
         <v>25</v>
@@ -7117,7 +7120,7 @@
         <v>35</v>
       </c>
       <c r="R105" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="106" spans="13:18">
@@ -7125,10 +7128,10 @@
         <v>17</v>
       </c>
       <c r="N106" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="O106" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="P106" t="s">
         <v>25</v>
@@ -7137,7 +7140,7 @@
         <v>35</v>
       </c>
       <c r="R106" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="107" spans="13:18">
@@ -7145,10 +7148,10 @@
         <v>17</v>
       </c>
       <c r="N107" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="O107" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="P107" t="s">
         <v>25</v>
@@ -7157,7 +7160,7 @@
         <v>35</v>
       </c>
       <c r="R107" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="108" spans="13:18">
@@ -7165,10 +7168,10 @@
         <v>17</v>
       </c>
       <c r="N108" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="O108" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="P108" t="s">
         <v>25</v>
@@ -7177,7 +7180,7 @@
         <v>35</v>
       </c>
       <c r="R108" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="109" spans="13:18">
@@ -7185,10 +7188,10 @@
         <v>17</v>
       </c>
       <c r="N109" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="O109" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="P109" t="s">
         <v>25</v>
@@ -7197,7 +7200,7 @@
         <v>35</v>
       </c>
       <c r="R109" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="110" spans="13:18">
@@ -7205,10 +7208,10 @@
         <v>17</v>
       </c>
       <c r="N110" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="O110" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P110" t="s">
         <v>25</v>
@@ -7217,7 +7220,7 @@
         <v>35</v>
       </c>
       <c r="R110" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="111" spans="13:18">
@@ -7225,10 +7228,10 @@
         <v>17</v>
       </c>
       <c r="N111" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="O111" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="P111" t="s">
         <v>25</v>
@@ -7237,7 +7240,7 @@
         <v>35</v>
       </c>
       <c r="R111" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="112" spans="13:18">
@@ -7245,10 +7248,10 @@
         <v>17</v>
       </c>
       <c r="N112" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="O112" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="P112" t="s">
         <v>25</v>
@@ -7257,7 +7260,7 @@
         <v>35</v>
       </c>
       <c r="R112" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="113" spans="13:18">
@@ -7265,10 +7268,10 @@
         <v>17</v>
       </c>
       <c r="N113" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="O113" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="P113" t="s">
         <v>25</v>
@@ -7277,7 +7280,7 @@
         <v>35</v>
       </c>
       <c r="R113" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="114" spans="13:18">
@@ -7285,10 +7288,10 @@
         <v>17</v>
       </c>
       <c r="N114" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="O114" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="P114" t="s">
         <v>25</v>
@@ -7297,7 +7300,7 @@
         <v>35</v>
       </c>
       <c r="R114" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="115" spans="13:18">
@@ -7305,10 +7308,10 @@
         <v>17</v>
       </c>
       <c r="N115" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="O115" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="P115" t="s">
         <v>25</v>
@@ -7317,7 +7320,7 @@
         <v>35</v>
       </c>
       <c r="R115" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="116" spans="13:18">
@@ -7325,10 +7328,10 @@
         <v>17</v>
       </c>
       <c r="N116" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="O116" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="P116" t="s">
         <v>25</v>
@@ -7337,7 +7340,7 @@
         <v>35</v>
       </c>
       <c r="R116" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="117" spans="13:18">
@@ -7345,10 +7348,10 @@
         <v>17</v>
       </c>
       <c r="N117" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="O117" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="P117" t="s">
         <v>25</v>
@@ -7357,7 +7360,7 @@
         <v>35</v>
       </c>
       <c r="R117" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="118" spans="13:18">
@@ -7365,10 +7368,10 @@
         <v>17</v>
       </c>
       <c r="N118" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="O118" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="P118" t="s">
         <v>25</v>
@@ -7377,7 +7380,7 @@
         <v>35</v>
       </c>
       <c r="R118" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="119" spans="13:18">
@@ -7385,10 +7388,10 @@
         <v>17</v>
       </c>
       <c r="N119" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="O119" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="P119" t="s">
         <v>25</v>
@@ -7397,7 +7400,7 @@
         <v>35</v>
       </c>
       <c r="R119" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="120" spans="13:18">
@@ -7405,10 +7408,10 @@
         <v>17</v>
       </c>
       <c r="N120" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="O120" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="P120" t="s">
         <v>25</v>
@@ -7417,7 +7420,7 @@
         <v>35</v>
       </c>
       <c r="R120" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="121" spans="13:18">
@@ -7425,10 +7428,10 @@
         <v>17</v>
       </c>
       <c r="N121" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="O121" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="P121" t="s">
         <v>25</v>
@@ -7437,7 +7440,7 @@
         <v>35</v>
       </c>
       <c r="R121" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="122" spans="13:18">
@@ -7445,10 +7448,10 @@
         <v>17</v>
       </c>
       <c r="N122" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="O122" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="P122" t="s">
         <v>25</v>
@@ -7457,7 +7460,7 @@
         <v>35</v>
       </c>
       <c r="R122" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="123" spans="13:18">
@@ -7465,10 +7468,10 @@
         <v>17</v>
       </c>
       <c r="N123" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="O123" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="P123" t="s">
         <v>25</v>
@@ -7477,7 +7480,7 @@
         <v>35</v>
       </c>
       <c r="R123" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="124" spans="13:18">
@@ -7485,10 +7488,10 @@
         <v>17</v>
       </c>
       <c r="N124" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="O124" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="P124" t="s">
         <v>25</v>
@@ -7497,7 +7500,7 @@
         <v>35</v>
       </c>
       <c r="R124" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="125" spans="13:18">
@@ -7505,10 +7508,10 @@
         <v>17</v>
       </c>
       <c r="N125" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="O125" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="P125" t="s">
         <v>25</v>
@@ -7517,7 +7520,7 @@
         <v>35</v>
       </c>
       <c r="R125" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="126" spans="13:18">
@@ -7525,10 +7528,10 @@
         <v>17</v>
       </c>
       <c r="N126" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="O126" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="P126" t="s">
         <v>25</v>
@@ -7537,7 +7540,7 @@
         <v>35</v>
       </c>
       <c r="R126" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="127" spans="13:18">
@@ -7545,10 +7548,10 @@
         <v>17</v>
       </c>
       <c r="N127" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="O127" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="P127" t="s">
         <v>25</v>
@@ -7557,7 +7560,7 @@
         <v>35</v>
       </c>
       <c r="R127" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="128" spans="13:18">
@@ -7565,10 +7568,10 @@
         <v>17</v>
       </c>
       <c r="N128" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="O128" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="P128" t="s">
         <v>25</v>
@@ -7577,7 +7580,7 @@
         <v>35</v>
       </c>
       <c r="R128" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="129" spans="13:18">
@@ -7585,10 +7588,10 @@
         <v>17</v>
       </c>
       <c r="N129" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="O129" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="P129" t="s">
         <v>25</v>
@@ -7597,7 +7600,7 @@
         <v>35</v>
       </c>
       <c r="R129" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="130" spans="13:18">
@@ -7605,10 +7608,10 @@
         <v>17</v>
       </c>
       <c r="N130" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="O130" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="P130" t="s">
         <v>25</v>
@@ -7617,7 +7620,7 @@
         <v>35</v>
       </c>
       <c r="R130" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="131" spans="13:18">
@@ -7625,10 +7628,10 @@
         <v>17</v>
       </c>
       <c r="N131" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="O131" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="P131" t="s">
         <v>25</v>
@@ -7637,7 +7640,7 @@
         <v>35</v>
       </c>
       <c r="R131" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="132" spans="13:18">
@@ -7645,10 +7648,10 @@
         <v>17</v>
       </c>
       <c r="N132" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="O132" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="P132" t="s">
         <v>25</v>
@@ -7657,7 +7660,7 @@
         <v>35</v>
       </c>
       <c r="R132" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="133" spans="13:18">
@@ -7665,10 +7668,10 @@
         <v>17</v>
       </c>
       <c r="N133" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="O133" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="P133" t="s">
         <v>25</v>
@@ -7677,7 +7680,7 @@
         <v>35</v>
       </c>
       <c r="R133" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="134" spans="13:18">
@@ -7685,10 +7688,10 @@
         <v>17</v>
       </c>
       <c r="N134" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="O134" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="P134" t="s">
         <v>25</v>
@@ -7697,7 +7700,7 @@
         <v>35</v>
       </c>
       <c r="R134" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="135" spans="13:18">
@@ -7705,10 +7708,10 @@
         <v>17</v>
       </c>
       <c r="N135" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="O135" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="P135" t="s">
         <v>25</v>
@@ -7717,7 +7720,7 @@
         <v>35</v>
       </c>
       <c r="R135" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="136" spans="13:18">
@@ -7725,10 +7728,10 @@
         <v>17</v>
       </c>
       <c r="N136" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="O136" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="P136" t="s">
         <v>25</v>
@@ -7737,7 +7740,7 @@
         <v>35</v>
       </c>
       <c r="R136" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="137" spans="13:18">
@@ -7745,10 +7748,10 @@
         <v>17</v>
       </c>
       <c r="N137" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="O137" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="P137" t="s">
         <v>25</v>
@@ -7757,7 +7760,7 @@
         <v>35</v>
       </c>
       <c r="R137" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="138" spans="13:18">
@@ -7765,10 +7768,10 @@
         <v>17</v>
       </c>
       <c r="N138" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="O138" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="P138" t="s">
         <v>25</v>
@@ -7777,7 +7780,7 @@
         <v>35</v>
       </c>
       <c r="R138" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="139" spans="13:18">
@@ -7785,10 +7788,10 @@
         <v>17</v>
       </c>
       <c r="N139" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="O139" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="P139" t="s">
         <v>25</v>
@@ -7797,7 +7800,7 @@
         <v>35</v>
       </c>
       <c r="R139" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="140" spans="13:18">
@@ -7805,10 +7808,10 @@
         <v>17</v>
       </c>
       <c r="N140" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="O140" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="P140" t="s">
         <v>25</v>
@@ -7817,7 +7820,7 @@
         <v>35</v>
       </c>
       <c r="R140" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="141" spans="13:18">
@@ -7825,10 +7828,10 @@
         <v>17</v>
       </c>
       <c r="N141" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="O141" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="P141" t="s">
         <v>25</v>
@@ -7837,7 +7840,7 @@
         <v>35</v>
       </c>
       <c r="R141" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="142" spans="13:18">
@@ -7845,10 +7848,10 @@
         <v>17</v>
       </c>
       <c r="N142" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="O142" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="P142" t="s">
         <v>25</v>
@@ -7857,7 +7860,7 @@
         <v>35</v>
       </c>
       <c r="R142" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="143" spans="13:18">
@@ -7865,10 +7868,10 @@
         <v>17</v>
       </c>
       <c r="N143" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="O143" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="P143" t="s">
         <v>25</v>
@@ -7877,7 +7880,7 @@
         <v>35</v>
       </c>
       <c r="R143" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="144" spans="13:18">
@@ -7885,10 +7888,10 @@
         <v>17</v>
       </c>
       <c r="N144" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="O144" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="P144" t="s">
         <v>25</v>
@@ -7897,7 +7900,7 @@
         <v>35</v>
       </c>
       <c r="R144" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="145" spans="13:18">
@@ -7905,10 +7908,10 @@
         <v>17</v>
       </c>
       <c r="N145" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="O145" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="P145" t="s">
         <v>25</v>
@@ -7917,7 +7920,7 @@
         <v>35</v>
       </c>
       <c r="R145" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="146" spans="13:18">
@@ -7925,10 +7928,10 @@
         <v>17</v>
       </c>
       <c r="N146" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="O146" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="P146" t="s">
         <v>25</v>
@@ -7937,7 +7940,7 @@
         <v>35</v>
       </c>
       <c r="R146" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="147" spans="13:18">
@@ -7945,10 +7948,10 @@
         <v>17</v>
       </c>
       <c r="N147" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="O147" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="P147" t="s">
         <v>25</v>
@@ -7957,7 +7960,7 @@
         <v>35</v>
       </c>
       <c r="R147" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="148" spans="13:18">
@@ -7965,10 +7968,10 @@
         <v>17</v>
       </c>
       <c r="N148" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="O148" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="P148" t="s">
         <v>25</v>
@@ -7977,7 +7980,7 @@
         <v>35</v>
       </c>
       <c r="R148" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="149" spans="13:18">
@@ -7985,10 +7988,10 @@
         <v>17</v>
       </c>
       <c r="N149" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="O149" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="P149" t="s">
         <v>25</v>
@@ -7997,7 +8000,7 @@
         <v>35</v>
       </c>
       <c r="R149" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="150" spans="13:18">
@@ -8005,10 +8008,10 @@
         <v>17</v>
       </c>
       <c r="N150" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="O150" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="P150" t="s">
         <v>25</v>
@@ -8017,7 +8020,7 @@
         <v>35</v>
       </c>
       <c r="R150" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="151" spans="13:18">
@@ -8025,10 +8028,10 @@
         <v>17</v>
       </c>
       <c r="N151" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="O151" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="P151" t="s">
         <v>25</v>
@@ -8037,7 +8040,7 @@
         <v>35</v>
       </c>
       <c r="R151" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="152" spans="13:18">
@@ -8045,10 +8048,10 @@
         <v>17</v>
       </c>
       <c r="N152" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="O152" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="P152" t="s">
         <v>25</v>
@@ -8057,7 +8060,7 @@
         <v>35</v>
       </c>
       <c r="R152" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="153" spans="13:18">
@@ -8065,10 +8068,10 @@
         <v>17</v>
       </c>
       <c r="N153" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="O153" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="P153" t="s">
         <v>25</v>
@@ -8077,7 +8080,7 @@
         <v>35</v>
       </c>
       <c r="R153" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="154" spans="13:18">
@@ -8085,10 +8088,10 @@
         <v>17</v>
       </c>
       <c r="N154" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="O154" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="P154" t="s">
         <v>25</v>
@@ -8097,7 +8100,7 @@
         <v>35</v>
       </c>
       <c r="R154" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="155" spans="13:18">
@@ -8105,10 +8108,10 @@
         <v>17</v>
       </c>
       <c r="N155" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="O155" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="P155" t="s">
         <v>25</v>
@@ -8117,7 +8120,7 @@
         <v>35</v>
       </c>
       <c r="R155" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="156" spans="13:18">
@@ -8125,10 +8128,10 @@
         <v>17</v>
       </c>
       <c r="N156" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="O156" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="P156" t="s">
         <v>25</v>
@@ -8137,7 +8140,7 @@
         <v>35</v>
       </c>
       <c r="R156" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="157" spans="13:18">
@@ -8145,10 +8148,10 @@
         <v>17</v>
       </c>
       <c r="N157" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="O157" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="P157" t="s">
         <v>25</v>
@@ -8157,7 +8160,7 @@
         <v>35</v>
       </c>
       <c r="R157" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="158" spans="13:18">
@@ -8165,10 +8168,10 @@
         <v>17</v>
       </c>
       <c r="N158" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="O158" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="P158" t="s">
         <v>25</v>
@@ -8177,7 +8180,7 @@
         <v>35</v>
       </c>
       <c r="R158" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="159" spans="13:18">
@@ -8185,10 +8188,10 @@
         <v>17</v>
       </c>
       <c r="N159" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="O159" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="P159" t="s">
         <v>25</v>
@@ -8197,7 +8200,7 @@
         <v>35</v>
       </c>
       <c r="R159" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="160" spans="13:18">
@@ -8205,10 +8208,10 @@
         <v>17</v>
       </c>
       <c r="N160" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="O160" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="P160" t="s">
         <v>25</v>
@@ -8217,7 +8220,7 @@
         <v>35</v>
       </c>
       <c r="R160" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="161" spans="13:18">
@@ -8225,10 +8228,10 @@
         <v>17</v>
       </c>
       <c r="N161" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="O161" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="P161" t="s">
         <v>25</v>
@@ -8237,7 +8240,7 @@
         <v>35</v>
       </c>
       <c r="R161" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="162" spans="13:18">
@@ -8245,10 +8248,10 @@
         <v>17</v>
       </c>
       <c r="N162" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="O162" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="P162" t="s">
         <v>25</v>
@@ -8257,7 +8260,7 @@
         <v>35</v>
       </c>
       <c r="R162" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="163" spans="13:18">
@@ -8265,10 +8268,10 @@
         <v>17</v>
       </c>
       <c r="N163" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="O163" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="P163" t="s">
         <v>25</v>
@@ -8277,7 +8280,7 @@
         <v>35</v>
       </c>
       <c r="R163" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="164" spans="13:18">
@@ -8285,10 +8288,10 @@
         <v>17</v>
       </c>
       <c r="N164" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="O164" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="P164" t="s">
         <v>25</v>
@@ -8297,7 +8300,7 @@
         <v>35</v>
       </c>
       <c r="R164" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="165" spans="13:18">
@@ -8305,10 +8308,10 @@
         <v>17</v>
       </c>
       <c r="N165" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="O165" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="P165" t="s">
         <v>25</v>
@@ -8317,7 +8320,7 @@
         <v>35</v>
       </c>
       <c r="R165" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="166" spans="13:18">
@@ -8325,10 +8328,10 @@
         <v>17</v>
       </c>
       <c r="N166" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="O166" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="P166" t="s">
         <v>25</v>
@@ -8337,7 +8340,7 @@
         <v>35</v>
       </c>
       <c r="R166" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="167" spans="13:18">
@@ -8345,10 +8348,10 @@
         <v>17</v>
       </c>
       <c r="N167" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="O167" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="P167" t="s">
         <v>25</v>
@@ -8357,7 +8360,7 @@
         <v>35</v>
       </c>
       <c r="R167" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="168" spans="13:18">
@@ -8365,10 +8368,10 @@
         <v>17</v>
       </c>
       <c r="N168" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="O168" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="P168" t="s">
         <v>25</v>
@@ -8377,7 +8380,7 @@
         <v>35</v>
       </c>
       <c r="R168" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="169" spans="13:18">
@@ -8385,10 +8388,10 @@
         <v>17</v>
       </c>
       <c r="N169" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="O169" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="P169" t="s">
         <v>25</v>
@@ -8397,7 +8400,7 @@
         <v>35</v>
       </c>
       <c r="R169" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="170" spans="13:18">
@@ -8405,10 +8408,10 @@
         <v>17</v>
       </c>
       <c r="N170" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="O170" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="P170" t="s">
         <v>25</v>
@@ -8417,7 +8420,7 @@
         <v>35</v>
       </c>
       <c r="R170" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="171" spans="13:18">
@@ -8425,10 +8428,10 @@
         <v>17</v>
       </c>
       <c r="N171" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="O171" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="P171" t="s">
         <v>25</v>
@@ -8437,7 +8440,7 @@
         <v>35</v>
       </c>
       <c r="R171" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="172" spans="13:18">
@@ -8445,10 +8448,10 @@
         <v>17</v>
       </c>
       <c r="N172" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="O172" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="P172" t="s">
         <v>25</v>
@@ -8457,7 +8460,7 @@
         <v>35</v>
       </c>
       <c r="R172" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="173" spans="13:18">
@@ -8465,10 +8468,10 @@
         <v>17</v>
       </c>
       <c r="N173" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="O173" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="P173" t="s">
         <v>25</v>
@@ -8477,7 +8480,7 @@
         <v>35</v>
       </c>
       <c r="R173" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="174" spans="13:18">
@@ -8485,10 +8488,10 @@
         <v>17</v>
       </c>
       <c r="N174" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="O174" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="P174" t="s">
         <v>25</v>
@@ -8497,7 +8500,7 @@
         <v>35</v>
       </c>
       <c r="R174" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="175" spans="13:18">
@@ -8505,10 +8508,10 @@
         <v>17</v>
       </c>
       <c r="N175" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="O175" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="P175" t="s">
         <v>25</v>
@@ -8517,7 +8520,7 @@
         <v>35</v>
       </c>
       <c r="R175" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="176" spans="13:18">
@@ -8525,10 +8528,10 @@
         <v>17</v>
       </c>
       <c r="N176" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="O176" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="P176" t="s">
         <v>25</v>
@@ -8537,7 +8540,7 @@
         <v>35</v>
       </c>
       <c r="R176" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="177" spans="13:18">
@@ -8545,10 +8548,10 @@
         <v>17</v>
       </c>
       <c r="N177" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="O177" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="P177" t="s">
         <v>25</v>
@@ -8557,7 +8560,7 @@
         <v>35</v>
       </c>
       <c r="R177" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="178" spans="13:18">
@@ -8565,10 +8568,10 @@
         <v>17</v>
       </c>
       <c r="N178" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="O178" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="P178" t="s">
         <v>25</v>
@@ -8577,7 +8580,7 @@
         <v>35</v>
       </c>
       <c r="R178" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="179" spans="13:18">
@@ -8585,10 +8588,10 @@
         <v>17</v>
       </c>
       <c r="N179" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="O179" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="P179" t="s">
         <v>25</v>
@@ -8597,7 +8600,7 @@
         <v>35</v>
       </c>
       <c r="R179" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="180" spans="13:18">
@@ -8605,10 +8608,10 @@
         <v>17</v>
       </c>
       <c r="N180" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="O180" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="P180" t="s">
         <v>25</v>
@@ -8617,7 +8620,7 @@
         <v>35</v>
       </c>
       <c r="R180" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="181" spans="13:18">
@@ -8625,10 +8628,10 @@
         <v>17</v>
       </c>
       <c r="N181" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="O181" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="P181" t="s">
         <v>25</v>
@@ -8637,7 +8640,7 @@
         <v>35</v>
       </c>
       <c r="R181" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="182" spans="13:18">
@@ -8645,10 +8648,10 @@
         <v>17</v>
       </c>
       <c r="N182" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="O182" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="P182" t="s">
         <v>25</v>
@@ -8657,7 +8660,7 @@
         <v>35</v>
       </c>
       <c r="R182" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="183" spans="13:18">
@@ -8665,10 +8668,10 @@
         <v>17</v>
       </c>
       <c r="N183" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="O183" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="P183" t="s">
         <v>25</v>
@@ -8677,7 +8680,7 @@
         <v>35</v>
       </c>
       <c r="R183" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="184" spans="13:18">
@@ -8685,10 +8688,10 @@
         <v>17</v>
       </c>
       <c r="N184" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="O184" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="P184" t="s">
         <v>25</v>
@@ -8697,7 +8700,7 @@
         <v>35</v>
       </c>
       <c r="R184" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="185" spans="13:18">
@@ -8705,10 +8708,10 @@
         <v>17</v>
       </c>
       <c r="N185" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="O185" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="P185" t="s">
         <v>25</v>
@@ -8717,7 +8720,7 @@
         <v>35</v>
       </c>
       <c r="R185" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="186" spans="13:18">
@@ -8725,10 +8728,10 @@
         <v>17</v>
       </c>
       <c r="N186" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="O186" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="P186" t="s">
         <v>25</v>
@@ -8737,7 +8740,7 @@
         <v>35</v>
       </c>
       <c r="R186" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="187" spans="13:18">
@@ -8745,10 +8748,10 @@
         <v>17</v>
       </c>
       <c r="N187" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="O187" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="P187" t="s">
         <v>25</v>
@@ -8757,7 +8760,7 @@
         <v>35</v>
       </c>
       <c r="R187" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="188" spans="13:18">
@@ -8765,10 +8768,10 @@
         <v>17</v>
       </c>
       <c r="N188" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="O188" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="P188" t="s">
         <v>25</v>
@@ -8777,7 +8780,7 @@
         <v>35</v>
       </c>
       <c r="R188" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="189" spans="13:18">
@@ -8785,10 +8788,10 @@
         <v>17</v>
       </c>
       <c r="N189" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="O189" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="P189" t="s">
         <v>25</v>
@@ -8797,7 +8800,7 @@
         <v>35</v>
       </c>
       <c r="R189" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="190" spans="13:18">
@@ -8805,10 +8808,10 @@
         <v>17</v>
       </c>
       <c r="N190" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="O190" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="P190" t="s">
         <v>25</v>
@@ -8817,7 +8820,7 @@
         <v>35</v>
       </c>
       <c r="R190" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="191" spans="13:18">
@@ -8825,10 +8828,10 @@
         <v>17</v>
       </c>
       <c r="N191" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="O191" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="P191" t="s">
         <v>25</v>
@@ -8837,7 +8840,7 @@
         <v>35</v>
       </c>
       <c r="R191" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="192" spans="13:18">
@@ -8845,10 +8848,10 @@
         <v>17</v>
       </c>
       <c r="N192" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="O192" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="P192" t="s">
         <v>25</v>
@@ -8857,7 +8860,7 @@
         <v>35</v>
       </c>
       <c r="R192" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="193" spans="13:18">
@@ -8865,10 +8868,10 @@
         <v>17</v>
       </c>
       <c r="N193" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="O193" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="P193" t="s">
         <v>25</v>
@@ -8877,7 +8880,7 @@
         <v>35</v>
       </c>
       <c r="R193" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="194" spans="13:18">
@@ -8885,10 +8888,10 @@
         <v>17</v>
       </c>
       <c r="N194" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="O194" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="P194" t="s">
         <v>25</v>
@@ -8897,7 +8900,7 @@
         <v>35</v>
       </c>
       <c r="R194" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="195" spans="13:18">
@@ -8905,10 +8908,10 @@
         <v>17</v>
       </c>
       <c r="N195" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="O195" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="P195" t="s">
         <v>25</v>
@@ -8917,7 +8920,7 @@
         <v>35</v>
       </c>
       <c r="R195" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="196" spans="13:18">
@@ -8925,10 +8928,10 @@
         <v>17</v>
       </c>
       <c r="N196" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="O196" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="P196" t="s">
         <v>25</v>
@@ -8937,7 +8940,7 @@
         <v>35</v>
       </c>
       <c r="R196" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="197" spans="13:18">
@@ -8945,10 +8948,10 @@
         <v>17</v>
       </c>
       <c r="N197" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="O197" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="P197" t="s">
         <v>25</v>
@@ -8957,7 +8960,7 @@
         <v>35</v>
       </c>
       <c r="R197" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="198" spans="13:18">
@@ -8965,10 +8968,10 @@
         <v>17</v>
       </c>
       <c r="N198" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="O198" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="P198" t="s">
         <v>25</v>
@@ -8977,7 +8980,7 @@
         <v>35</v>
       </c>
       <c r="R198" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="199" spans="13:18">
@@ -8985,10 +8988,10 @@
         <v>17</v>
       </c>
       <c r="N199" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="O199" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="P199" t="s">
         <v>25</v>
@@ -8997,7 +9000,7 @@
         <v>35</v>
       </c>
       <c r="R199" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="200" spans="13:18">
@@ -9005,10 +9008,10 @@
         <v>17</v>
       </c>
       <c r="N200" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="O200" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="P200" t="s">
         <v>25</v>
@@ -9017,7 +9020,7 @@
         <v>35</v>
       </c>
       <c r="R200" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="201" spans="13:18">
@@ -9025,10 +9028,10 @@
         <v>17</v>
       </c>
       <c r="N201" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="O201" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="P201" t="s">
         <v>25</v>
@@ -9037,7 +9040,7 @@
         <v>35</v>
       </c>
       <c r="R201" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="202" spans="13:18">
@@ -9045,10 +9048,10 @@
         <v>17</v>
       </c>
       <c r="N202" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="O202" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="P202" t="s">
         <v>25</v>
@@ -9057,7 +9060,7 @@
         <v>35</v>
       </c>
       <c r="R202" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="203" spans="13:18">
@@ -9065,10 +9068,10 @@
         <v>17</v>
       </c>
       <c r="N203" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="O203" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="P203" t="s">
         <v>25</v>
@@ -9077,7 +9080,7 @@
         <v>35</v>
       </c>
       <c r="R203" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="204" spans="13:18">
@@ -9085,10 +9088,10 @@
         <v>17</v>
       </c>
       <c r="N204" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="O204" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="P204" t="s">
         <v>25</v>
@@ -9097,7 +9100,7 @@
         <v>35</v>
       </c>
       <c r="R204" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="205" spans="13:18">
@@ -9105,10 +9108,10 @@
         <v>17</v>
       </c>
       <c r="N205" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="O205" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="P205" t="s">
         <v>25</v>
@@ -9117,7 +9120,7 @@
         <v>35</v>
       </c>
       <c r="R205" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="206" spans="13:18">
@@ -9125,10 +9128,10 @@
         <v>17</v>
       </c>
       <c r="N206" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="O206" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="P206" t="s">
         <v>25</v>
@@ -9137,7 +9140,7 @@
         <v>35</v>
       </c>
       <c r="R206" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="207" spans="13:18">
@@ -9145,10 +9148,10 @@
         <v>17</v>
       </c>
       <c r="N207" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="O207" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="P207" t="s">
         <v>25</v>
@@ -9157,7 +9160,7 @@
         <v>35</v>
       </c>
       <c r="R207" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="208" spans="13:18">
@@ -9165,10 +9168,10 @@
         <v>17</v>
       </c>
       <c r="N208" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="O208" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="P208" t="s">
         <v>25</v>
@@ -9177,7 +9180,7 @@
         <v>35</v>
       </c>
       <c r="R208" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="209" spans="13:18">
@@ -9185,10 +9188,10 @@
         <v>17</v>
       </c>
       <c r="N209" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="O209" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="P209" t="s">
         <v>25</v>
@@ -9197,7 +9200,7 @@
         <v>35</v>
       </c>
       <c r="R209" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="210" spans="13:18">
@@ -9205,10 +9208,10 @@
         <v>17</v>
       </c>
       <c r="N210" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="O210" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="P210" t="s">
         <v>25</v>
@@ -9217,7 +9220,7 @@
         <v>35</v>
       </c>
       <c r="R210" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="211" spans="13:18">
@@ -9225,10 +9228,10 @@
         <v>17</v>
       </c>
       <c r="N211" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="O211" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="P211" t="s">
         <v>25</v>
@@ -9237,7 +9240,7 @@
         <v>35</v>
       </c>
       <c r="R211" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="212" spans="13:18">
@@ -9245,10 +9248,10 @@
         <v>17</v>
       </c>
       <c r="N212" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="O212" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="P212" t="s">
         <v>25</v>
@@ -9257,7 +9260,7 @@
         <v>35</v>
       </c>
       <c r="R212" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="213" spans="13:18">
@@ -9265,10 +9268,10 @@
         <v>17</v>
       </c>
       <c r="N213" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="O213" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="P213" t="s">
         <v>25</v>
@@ -9277,7 +9280,7 @@
         <v>35</v>
       </c>
       <c r="R213" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="214" spans="13:18">
@@ -9285,10 +9288,10 @@
         <v>17</v>
       </c>
       <c r="N214" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="O214" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="P214" t="s">
         <v>25</v>
@@ -9297,7 +9300,7 @@
         <v>35</v>
       </c>
       <c r="R214" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="215" spans="13:18">
@@ -9305,10 +9308,10 @@
         <v>17</v>
       </c>
       <c r="N215" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="O215" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="P215" t="s">
         <v>25</v>
@@ -9317,7 +9320,7 @@
         <v>35</v>
       </c>
       <c r="R215" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="216" spans="13:18">
@@ -9325,10 +9328,10 @@
         <v>17</v>
       </c>
       <c r="N216" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="O216" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="P216" t="s">
         <v>25</v>
@@ -9337,7 +9340,7 @@
         <v>35</v>
       </c>
       <c r="R216" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="217" spans="13:18">
@@ -9345,10 +9348,10 @@
         <v>17</v>
       </c>
       <c r="N217" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="O217" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="P217" t="s">
         <v>25</v>
@@ -9357,7 +9360,7 @@
         <v>35</v>
       </c>
       <c r="R217" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="218" spans="13:18">
@@ -9365,10 +9368,10 @@
         <v>17</v>
       </c>
       <c r="N218" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="O218" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="P218" t="s">
         <v>25</v>
@@ -9377,7 +9380,7 @@
         <v>35</v>
       </c>
       <c r="R218" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="219" spans="13:18">
@@ -9385,10 +9388,10 @@
         <v>17</v>
       </c>
       <c r="N219" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="O219" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="P219" t="s">
         <v>25</v>
@@ -9397,7 +9400,7 @@
         <v>35</v>
       </c>
       <c r="R219" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="220" spans="13:18">
@@ -9405,10 +9408,10 @@
         <v>17</v>
       </c>
       <c r="N220" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="O220" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="P220" t="s">
         <v>25</v>
@@ -9417,7 +9420,7 @@
         <v>35</v>
       </c>
       <c r="R220" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="221" spans="13:18">
@@ -9425,10 +9428,10 @@
         <v>17</v>
       </c>
       <c r="N221" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="O221" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="P221" t="s">
         <v>25</v>
@@ -9437,7 +9440,7 @@
         <v>35</v>
       </c>
       <c r="R221" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="222" spans="13:18">
@@ -9445,10 +9448,10 @@
         <v>17</v>
       </c>
       <c r="N222" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="O222" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="P222" t="s">
         <v>25</v>
@@ -9457,7 +9460,7 @@
         <v>35</v>
       </c>
       <c r="R222" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="223" spans="13:18">
@@ -9465,10 +9468,10 @@
         <v>17</v>
       </c>
       <c r="N223" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="O223" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="P223" t="s">
         <v>25</v>
@@ -9477,7 +9480,7 @@
         <v>35</v>
       </c>
       <c r="R223" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="224" spans="13:18">
@@ -9485,10 +9488,10 @@
         <v>17</v>
       </c>
       <c r="N224" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="O224" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="P224" t="s">
         <v>25</v>
@@ -9497,7 +9500,7 @@
         <v>35</v>
       </c>
       <c r="R224" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="225" spans="13:18">
@@ -9505,10 +9508,10 @@
         <v>17</v>
       </c>
       <c r="N225" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="O225" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="P225" t="s">
         <v>25</v>
@@ -9517,7 +9520,7 @@
         <v>35</v>
       </c>
       <c r="R225" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="226" spans="13:18">
@@ -9525,10 +9528,10 @@
         <v>17</v>
       </c>
       <c r="N226" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="O226" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="P226" t="s">
         <v>25</v>
@@ -9537,7 +9540,7 @@
         <v>35</v>
       </c>
       <c r="R226" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="227" spans="13:18">
@@ -9545,10 +9548,10 @@
         <v>17</v>
       </c>
       <c r="N227" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="O227" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="P227" t="s">
         <v>25</v>
@@ -9557,7 +9560,7 @@
         <v>35</v>
       </c>
       <c r="R227" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="228" spans="13:18">
@@ -9565,10 +9568,10 @@
         <v>17</v>
       </c>
       <c r="N228" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="O228" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="P228" t="s">
         <v>25</v>
@@ -9577,7 +9580,7 @@
         <v>35</v>
       </c>
       <c r="R228" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="229" spans="13:18">
@@ -9585,10 +9588,10 @@
         <v>17</v>
       </c>
       <c r="N229" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="O229" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="P229" t="s">
         <v>25</v>
@@ -9597,7 +9600,7 @@
         <v>35</v>
       </c>
       <c r="R229" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="230" spans="13:18">
@@ -9605,10 +9608,10 @@
         <v>17</v>
       </c>
       <c r="N230" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="O230" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="P230" t="s">
         <v>25</v>
@@ -9617,7 +9620,7 @@
         <v>35</v>
       </c>
       <c r="R230" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="231" spans="13:18">
@@ -9625,10 +9628,10 @@
         <v>17</v>
       </c>
       <c r="N231" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="O231" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="P231" t="s">
         <v>25</v>
@@ -9637,7 +9640,7 @@
         <v>35</v>
       </c>
       <c r="R231" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="232" spans="13:18">
@@ -9645,10 +9648,10 @@
         <v>17</v>
       </c>
       <c r="N232" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="O232" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="P232" t="s">
         <v>25</v>
@@ -9657,7 +9660,7 @@
         <v>35</v>
       </c>
       <c r="R232" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="233" spans="13:18">
@@ -9665,10 +9668,10 @@
         <v>17</v>
       </c>
       <c r="N233" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="O233" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="P233" t="s">
         <v>25</v>
@@ -9677,7 +9680,7 @@
         <v>35</v>
       </c>
       <c r="R233" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="234" spans="13:18">
@@ -9685,10 +9688,10 @@
         <v>17</v>
       </c>
       <c r="N234" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="O234" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="P234" t="s">
         <v>25</v>
@@ -9697,7 +9700,7 @@
         <v>35</v>
       </c>
       <c r="R234" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="235" spans="13:18">
@@ -9705,10 +9708,10 @@
         <v>17</v>
       </c>
       <c r="N235" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="O235" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="P235" t="s">
         <v>25</v>
@@ -9717,7 +9720,7 @@
         <v>35</v>
       </c>
       <c r="R235" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="236" spans="13:18">
@@ -9725,10 +9728,10 @@
         <v>17</v>
       </c>
       <c r="N236" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="O236" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="P236" t="s">
         <v>25</v>
@@ -9737,7 +9740,7 @@
         <v>35</v>
       </c>
       <c r="R236" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="237" spans="13:18">
@@ -9745,10 +9748,10 @@
         <v>17</v>
       </c>
       <c r="N237" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="O237" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="P237" t="s">
         <v>25</v>
@@ -9757,7 +9760,7 @@
         <v>35</v>
       </c>
       <c r="R237" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="238" spans="13:18">
@@ -9765,10 +9768,10 @@
         <v>17</v>
       </c>
       <c r="N238" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="O238" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="P238" t="s">
         <v>25</v>
@@ -9777,7 +9780,7 @@
         <v>35</v>
       </c>
       <c r="R238" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="239" spans="13:18">
@@ -9785,10 +9788,10 @@
         <v>17</v>
       </c>
       <c r="N239" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="O239" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="P239" t="s">
         <v>25</v>
@@ -9797,7 +9800,7 @@
         <v>35</v>
       </c>
       <c r="R239" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="240" spans="13:18">
@@ -9805,10 +9808,10 @@
         <v>17</v>
       </c>
       <c r="N240" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="O240" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="P240" t="s">
         <v>25</v>
@@ -9817,7 +9820,7 @@
         <v>35</v>
       </c>
       <c r="R240" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="241" spans="13:18">
@@ -9825,10 +9828,10 @@
         <v>17</v>
       </c>
       <c r="N241" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="O241" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="P241" t="s">
         <v>25</v>
@@ -9837,7 +9840,7 @@
         <v>35</v>
       </c>
       <c r="R241" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="242" spans="13:18">
@@ -9845,10 +9848,10 @@
         <v>17</v>
       </c>
       <c r="N242" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="O242" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="P242" t="s">
         <v>25</v>
@@ -9857,7 +9860,7 @@
         <v>35</v>
       </c>
       <c r="R242" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="243" spans="13:18">
@@ -9865,10 +9868,10 @@
         <v>17</v>
       </c>
       <c r="N243" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="O243" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="P243" t="s">
         <v>25</v>
@@ -9877,7 +9880,7 @@
         <v>35</v>
       </c>
       <c r="R243" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="244" spans="13:18">
@@ -9885,10 +9888,10 @@
         <v>17</v>
       </c>
       <c r="N244" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="O244" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="P244" t="s">
         <v>25</v>
@@ -9897,7 +9900,7 @@
         <v>35</v>
       </c>
       <c r="R244" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="245" spans="13:18">
@@ -9905,10 +9908,10 @@
         <v>17</v>
       </c>
       <c r="N245" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="O245" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="P245" t="s">
         <v>25</v>
@@ -9917,7 +9920,7 @@
         <v>35</v>
       </c>
       <c r="R245" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="246" spans="13:18">
@@ -9925,10 +9928,10 @@
         <v>17</v>
       </c>
       <c r="N246" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="O246" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="P246" t="s">
         <v>25</v>
@@ -9937,7 +9940,7 @@
         <v>35</v>
       </c>
       <c r="R246" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="247" spans="13:18">
@@ -9945,10 +9948,10 @@
         <v>17</v>
       </c>
       <c r="N247" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="O247" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="P247" t="s">
         <v>25</v>
@@ -9957,7 +9960,7 @@
         <v>35</v>
       </c>
       <c r="R247" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="248" spans="13:18">
@@ -9965,10 +9968,10 @@
         <v>17</v>
       </c>
       <c r="N248" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="O248" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="P248" t="s">
         <v>25</v>
@@ -9977,7 +9980,7 @@
         <v>35</v>
       </c>
       <c r="R248" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="249" spans="13:18">
@@ -9985,10 +9988,10 @@
         <v>17</v>
       </c>
       <c r="N249" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="O249" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="P249" t="s">
         <v>25</v>
@@ -9997,7 +10000,7 @@
         <v>35</v>
       </c>
       <c r="R249" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="250" spans="13:18">
@@ -10005,10 +10008,10 @@
         <v>17</v>
       </c>
       <c r="N250" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="O250" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="P250" t="s">
         <v>25</v>
@@ -10017,7 +10020,7 @@
         <v>35</v>
       </c>
       <c r="R250" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="251" spans="13:18">
@@ -10025,10 +10028,10 @@
         <v>17</v>
       </c>
       <c r="N251" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="O251" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="P251" t="s">
         <v>25</v>
@@ -10037,7 +10040,7 @@
         <v>35</v>
       </c>
       <c r="R251" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="252" spans="13:18">
@@ -10045,10 +10048,10 @@
         <v>17</v>
       </c>
       <c r="N252" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="O252" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="P252" t="s">
         <v>25</v>
@@ -10057,7 +10060,7 @@
         <v>35</v>
       </c>
       <c r="R252" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="253" spans="13:18">
@@ -10065,10 +10068,10 @@
         <v>17</v>
       </c>
       <c r="N253" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="O253" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="P253" t="s">
         <v>25</v>
@@ -10077,7 +10080,7 @@
         <v>35</v>
       </c>
       <c r="R253" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="254" spans="13:18">
@@ -10085,10 +10088,10 @@
         <v>17</v>
       </c>
       <c r="N254" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="O254" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="P254" t="s">
         <v>25</v>
@@ -10097,7 +10100,7 @@
         <v>35</v>
       </c>
       <c r="R254" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="255" spans="13:18">
@@ -10105,10 +10108,10 @@
         <v>17</v>
       </c>
       <c r="N255" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="O255" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="P255" t="s">
         <v>25</v>
@@ -10117,7 +10120,7 @@
         <v>35</v>
       </c>
       <c r="R255" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="256" spans="13:18">
@@ -10125,10 +10128,10 @@
         <v>17</v>
       </c>
       <c r="N256" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="O256" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="P256" t="s">
         <v>25</v>
@@ -10137,7 +10140,7 @@
         <v>35</v>
       </c>
       <c r="R256" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="257" spans="13:18">
@@ -10145,10 +10148,10 @@
         <v>17</v>
       </c>
       <c r="N257" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="O257" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="P257" t="s">
         <v>25</v>
@@ -10157,7 +10160,7 @@
         <v>35</v>
       </c>
       <c r="R257" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="258" spans="13:18">
@@ -10165,10 +10168,10 @@
         <v>17</v>
       </c>
       <c r="N258" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="O258" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="P258" t="s">
         <v>25</v>
@@ -10177,7 +10180,7 @@
         <v>35</v>
       </c>
       <c r="R258" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="259" spans="13:18">
@@ -10185,10 +10188,10 @@
         <v>17</v>
       </c>
       <c r="N259" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="O259" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="P259" t="s">
         <v>25</v>
@@ -10197,7 +10200,7 @@
         <v>35</v>
       </c>
       <c r="R259" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="260" spans="13:18">
@@ -10205,10 +10208,10 @@
         <v>17</v>
       </c>
       <c r="N260" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="O260" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="P260" t="s">
         <v>25</v>
@@ -10217,7 +10220,7 @@
         <v>35</v>
       </c>
       <c r="R260" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="261" spans="13:18">
@@ -10225,10 +10228,10 @@
         <v>17</v>
       </c>
       <c r="N261" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="O261" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="P261" t="s">
         <v>25</v>
@@ -10237,7 +10240,7 @@
         <v>35</v>
       </c>
       <c r="R261" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="262" spans="13:18">
@@ -10245,10 +10248,10 @@
         <v>17</v>
       </c>
       <c r="N262" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="O262" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="P262" t="s">
         <v>25</v>
@@ -10257,7 +10260,7 @@
         <v>35</v>
       </c>
       <c r="R262" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="263" spans="13:18">
@@ -10265,10 +10268,10 @@
         <v>17</v>
       </c>
       <c r="N263" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="O263" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="P263" t="s">
         <v>25</v>
@@ -10277,7 +10280,7 @@
         <v>35</v>
       </c>
       <c r="R263" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="264" spans="13:18">
@@ -10285,10 +10288,10 @@
         <v>17</v>
       </c>
       <c r="N264" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="O264" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="P264" t="s">
         <v>25</v>
@@ -10297,7 +10300,7 @@
         <v>35</v>
       </c>
       <c r="R264" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="265" spans="13:18">
@@ -10305,10 +10308,10 @@
         <v>17</v>
       </c>
       <c r="N265" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="O265" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="P265" t="s">
         <v>25</v>
@@ -10317,7 +10320,7 @@
         <v>35</v>
       </c>
       <c r="R265" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="266" spans="13:18">
@@ -10325,10 +10328,10 @@
         <v>17</v>
       </c>
       <c r="N266" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="O266" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="P266" t="s">
         <v>25</v>
@@ -10337,7 +10340,7 @@
         <v>35</v>
       </c>
       <c r="R266" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="267" spans="13:18">
@@ -10345,10 +10348,10 @@
         <v>17</v>
       </c>
       <c r="N267" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="O267" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="P267" t="s">
         <v>25</v>
@@ -10357,7 +10360,7 @@
         <v>35</v>
       </c>
       <c r="R267" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="268" spans="13:18">
@@ -10365,10 +10368,10 @@
         <v>17</v>
       </c>
       <c r="N268" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="O268" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="P268" t="s">
         <v>25</v>
@@ -10377,7 +10380,7 @@
         <v>35</v>
       </c>
       <c r="R268" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="269" spans="13:18">
@@ -10385,10 +10388,10 @@
         <v>17</v>
       </c>
       <c r="N269" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="O269" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="P269" t="s">
         <v>25</v>
@@ -10397,7 +10400,7 @@
         <v>35</v>
       </c>
       <c r="R269" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="270" spans="13:18">
@@ -10405,10 +10408,10 @@
         <v>17</v>
       </c>
       <c r="N270" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="O270" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="P270" t="s">
         <v>25</v>
@@ -10417,7 +10420,7 @@
         <v>35</v>
       </c>
       <c r="R270" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="271" spans="13:18">
@@ -10425,10 +10428,10 @@
         <v>17</v>
       </c>
       <c r="N271" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="O271" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="P271" t="s">
         <v>25</v>
@@ -10437,7 +10440,7 @@
         <v>35</v>
       </c>
       <c r="R271" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="272" spans="13:18">
@@ -10445,10 +10448,10 @@
         <v>17</v>
       </c>
       <c r="N272" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="O272" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="P272" t="s">
         <v>25</v>
@@ -10457,7 +10460,7 @@
         <v>35</v>
       </c>
       <c r="R272" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="273" spans="13:18">
@@ -10465,10 +10468,10 @@
         <v>17</v>
       </c>
       <c r="N273" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="O273" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="P273" t="s">
         <v>25</v>
@@ -10477,7 +10480,7 @@
         <v>35</v>
       </c>
       <c r="R273" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="274" spans="13:18">
@@ -10485,10 +10488,10 @@
         <v>17</v>
       </c>
       <c r="N274" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="O274" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="P274" t="s">
         <v>25</v>
@@ -10497,7 +10500,7 @@
         <v>35</v>
       </c>
       <c r="R274" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="275" spans="13:18">
@@ -10505,10 +10508,10 @@
         <v>17</v>
       </c>
       <c r="N275" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="O275" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="P275" t="s">
         <v>25</v>
@@ -10517,7 +10520,7 @@
         <v>35</v>
       </c>
       <c r="R275" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="276" spans="13:18">
@@ -10525,10 +10528,10 @@
         <v>17</v>
       </c>
       <c r="N276" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="O276" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="P276" t="s">
         <v>25</v>
@@ -10537,7 +10540,7 @@
         <v>35</v>
       </c>
       <c r="R276" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="277" spans="13:18">
@@ -10545,10 +10548,10 @@
         <v>17</v>
       </c>
       <c r="N277" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="O277" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="P277" t="s">
         <v>25</v>
@@ -10557,7 +10560,7 @@
         <v>35</v>
       </c>
       <c r="R277" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="278" spans="13:18">
@@ -10565,10 +10568,10 @@
         <v>17</v>
       </c>
       <c r="N278" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="O278" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="P278" t="s">
         <v>25</v>
@@ -10577,7 +10580,7 @@
         <v>35</v>
       </c>
       <c r="R278" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="279" spans="13:18">
@@ -10585,10 +10588,10 @@
         <v>17</v>
       </c>
       <c r="N279" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="O279" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="P279" t="s">
         <v>25</v>
@@ -10597,7 +10600,7 @@
         <v>35</v>
       </c>
       <c r="R279" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="280" spans="13:18">
@@ -10605,10 +10608,10 @@
         <v>17</v>
       </c>
       <c r="N280" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="O280" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="P280" t="s">
         <v>25</v>
@@ -10617,7 +10620,7 @@
         <v>35</v>
       </c>
       <c r="R280" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="281" spans="13:18">
@@ -10625,10 +10628,10 @@
         <v>17</v>
       </c>
       <c r="N281" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="O281" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="P281" t="s">
         <v>25</v>
@@ -10637,7 +10640,7 @@
         <v>35</v>
       </c>
       <c r="R281" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="282" spans="13:18">
@@ -10645,10 +10648,10 @@
         <v>17</v>
       </c>
       <c r="N282" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="O282" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="P282" t="s">
         <v>25</v>
@@ -10657,7 +10660,7 @@
         <v>35</v>
       </c>
       <c r="R282" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="283" spans="13:18">
@@ -10665,10 +10668,10 @@
         <v>17</v>
       </c>
       <c r="N283" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="O283" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="P283" t="s">
         <v>25</v>
@@ -10677,7 +10680,7 @@
         <v>35</v>
       </c>
       <c r="R283" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="284" spans="13:18">
@@ -10685,10 +10688,10 @@
         <v>17</v>
       </c>
       <c r="N284" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="O284" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="P284" t="s">
         <v>25</v>
@@ -10697,7 +10700,7 @@
         <v>35</v>
       </c>
       <c r="R284" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="285" spans="13:18">
@@ -10705,10 +10708,10 @@
         <v>17</v>
       </c>
       <c r="N285" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="O285" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="P285" t="s">
         <v>25</v>
@@ -10717,7 +10720,7 @@
         <v>35</v>
       </c>
       <c r="R285" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="286" spans="13:18">
@@ -10725,10 +10728,10 @@
         <v>17</v>
       </c>
       <c r="N286" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="O286" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="P286" t="s">
         <v>25</v>
@@ -10737,7 +10740,7 @@
         <v>35</v>
       </c>
       <c r="R286" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="287" spans="13:18">
@@ -10745,10 +10748,10 @@
         <v>17</v>
       </c>
       <c r="N287" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="O287" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="P287" t="s">
         <v>25</v>
@@ -10757,7 +10760,7 @@
         <v>35</v>
       </c>
       <c r="R287" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="288" spans="13:18">
@@ -10765,10 +10768,10 @@
         <v>17</v>
       </c>
       <c r="N288" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="O288" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="P288" t="s">
         <v>25</v>
@@ -10777,7 +10780,7 @@
         <v>35</v>
       </c>
       <c r="R288" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
   </sheetData>
@@ -11068,7 +11071,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A64C410-895F-4040-A7AB-3F7211AA7FBD}">
-  <dimension ref="B1:N41"/>
+  <dimension ref="B1:N42"/>
   <sheetFormatPr defaultColWidth="11.3984375" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="11.3984375" style="11"/>
@@ -11210,49 +11213,49 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="2:12">
-      <c r="B13" s="14" t="s">
+    <row r="11" spans="2:12">
+      <c r="D11" s="11" t="s">
+        <v>212</v>
+      </c>
+      <c r="E11" s="11">
+        <v>0</v>
+      </c>
+      <c r="F11" s="11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="2:12">
+      <c r="B14" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="14"/>
-    </row>
-    <row r="14" spans="2:12">
-      <c r="B14" s="15" t="s">
+      <c r="G14" s="14"/>
+      <c r="H14" s="14"/>
+      <c r="I14" s="14"/>
+    </row>
+    <row r="15" spans="2:12">
+      <c r="B15" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="C14" s="15" t="s">
+      <c r="C15" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="D14" s="15" t="s">
+      <c r="D15" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="E14" s="15" t="s">
+      <c r="E15" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="F14" s="15" t="s">
+      <c r="F15" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="G14" s="15" t="s">
+      <c r="G15" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="H14" s="15" t="s">
+      <c r="H15" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="I14" s="15" t="s">
+      <c r="I15" s="15" t="s">
         <v>56</v>
-      </c>
-    </row>
-    <row r="15" spans="2:12">
-      <c r="D15" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="F15" s="11">
-        <v>2222</v>
-      </c>
-      <c r="G15" s="11" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="16" spans="2:12">
@@ -11260,22 +11263,22 @@
         <v>66</v>
       </c>
       <c r="F16" s="11">
+        <v>2222</v>
+      </c>
+      <c r="G16" s="11" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="17" spans="2:14">
+      <c r="D17" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="F17" s="11">
         <v>8888</v>
       </c>
-      <c r="G16" s="11" t="s">
+      <c r="G17" s="11" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="17" spans="2:14" ht="12.75">
-      <c r="B17" s="13"/>
-      <c r="C17" s="13"/>
-      <c r="D17" s="13"/>
-      <c r="E17" s="13"/>
-      <c r="F17" s="13"/>
-      <c r="G17" s="13"/>
-      <c r="H17" s="13"/>
-      <c r="I17" s="13"/>
-      <c r="J17" s="13"/>
     </row>
     <row r="18" spans="2:14" ht="12.75">
       <c r="B18" s="13"/>
@@ -11299,20 +11302,16 @@
       <c r="I19" s="13"/>
       <c r="J19" s="13"/>
     </row>
-    <row r="20" spans="2:14" ht="14.25">
-      <c r="B20"/>
-      <c r="C20"/>
-      <c r="D20"/>
-      <c r="E20"/>
-      <c r="F20"/>
-      <c r="G20"/>
-      <c r="H20"/>
-      <c r="I20"/>
-      <c r="J20"/>
-      <c r="K20"/>
-      <c r="L20"/>
-      <c r="M20"/>
-      <c r="N20"/>
+    <row r="20" spans="2:14" ht="12.75">
+      <c r="B20" s="13"/>
+      <c r="C20" s="13"/>
+      <c r="D20" s="13"/>
+      <c r="E20" s="13"/>
+      <c r="F20" s="13"/>
+      <c r="G20" s="13"/>
+      <c r="H20" s="13"/>
+      <c r="I20" s="13"/>
+      <c r="J20" s="13"/>
     </row>
     <row r="21" spans="2:14" ht="14.25">
       <c r="B21"/>
@@ -11628,6 +11627,21 @@
       <c r="L41"/>
       <c r="M41"/>
       <c r="N41"/>
+    </row>
+    <row r="42" spans="2:14" ht="14.25">
+      <c r="B42"/>
+      <c r="C42"/>
+      <c r="D42"/>
+      <c r="E42"/>
+      <c r="F42"/>
+      <c r="G42"/>
+      <c r="H42"/>
+      <c r="I42"/>
+      <c r="J42"/>
+      <c r="K42"/>
+      <c r="L42"/>
+      <c r="M42"/>
+      <c r="N42"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/VerveStacks_CHN/SysSettings.xlsx
+++ b/VerveStacks_CHN/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F970237D-295A-4B67-BDFC-DC69C14B43C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15F4AF0C-5C4D-489D-8A46-FC5AC0D7C535}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_CHN/SysSettings.xlsx
+++ b/VerveStacks_CHN/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15F4AF0C-5C4D-489D-8A46-FC5AC0D7C535}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DD672C6-BF4C-4183-B547-BE9E60B39CA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_CHN/SysSettings.xlsx
+++ b/VerveStacks_CHN/SysSettings.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DD672C6-BF4C-4183-B547-BE9E60B39CA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56E2B75A-027B-46B6-A002-BBE41727E5C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_CHN/SysSettings.xlsx
+++ b/VerveStacks_CHN/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56E2B75A-027B-46B6-A002-BBE41727E5C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A792DC85-87DA-495F-8FBE-325F8501A254}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_CHN/SysSettings.xlsx
+++ b/VerveStacks_CHN/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A792DC85-87DA-495F-8FBE-325F8501A254}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3916C970-823D-45EA-8211-E69832647AA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_CHN/SysSettings.xlsx
+++ b/VerveStacks_CHN/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3916C970-823D-45EA-8211-E69832647AA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D039A94A-F48A-4848-AABB-ABA9034BF7E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_CHN/SysSettings.xlsx
+++ b/VerveStacks_CHN/SysSettings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D039A94A-F48A-4848-AABB-ABA9034BF7E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21DBFD19-75DA-46C4-96D1-24989D9B7BA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="system_settings" sheetId="1" r:id="rId1"/>

--- a/VerveStacks_CHN/SysSettings.xlsx
+++ b/VerveStacks_CHN/SysSettings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21DBFD19-75DA-46C4-96D1-24989D9B7BA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EEBAC32-A145-41EA-AE3A-498749AA667D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="system_settings" sheetId="1" r:id="rId1"/>

--- a/VerveStacks_CHN/SysSettings.xlsx
+++ b/VerveStacks_CHN/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EEBAC32-A145-41EA-AE3A-498749AA667D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{480460E1-FAF8-45D3-B07A-5EE179EBBC7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_CHN/SysSettings.xlsx
+++ b/VerveStacks_CHN/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{480460E1-FAF8-45D3-B07A-5EE179EBBC7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12507B26-34E4-4247-88EB-45320BE2B970}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_CHN/SysSettings.xlsx
+++ b/VerveStacks_CHN/SysSettings.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12507B26-34E4-4247-88EB-45320BE2B970}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{431FFCDE-C50A-4CDE-A62A-911380DF2FC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="system_settings" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2257" uniqueCount="784">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2264" uniqueCount="790">
   <si>
     <t>~BookRegions_Map</t>
   </si>
@@ -677,6 +677,24 @@
   </si>
   <si>
     <t>cap_bnd</t>
+  </si>
+  <si>
+    <t>~tfm_comgrp</t>
+  </si>
+  <si>
+    <t>allregions</t>
+  </si>
+  <si>
+    <t>cset_cn</t>
+  </si>
+  <si>
+    <t>ELC,e[_]*</t>
+  </si>
+  <si>
+    <t>y</t>
+  </si>
+  <si>
+    <t>ELC_BatIn</t>
   </si>
   <si>
     <t>CHN</t>
@@ -4780,7 +4798,7 @@
         <v>7</v>
       </c>
       <c r="C4" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="F4" t="s">
         <v>36</v>
@@ -4863,7 +4881,7 @@
         <v>16</v>
       </c>
       <c r="M4" s="5" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="N4" s="5" t="s">
         <v>10</v>
@@ -4895,10 +4913,10 @@
         <v>17</v>
       </c>
       <c r="N5" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="O5" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="P5" t="s">
         <v>25</v>
@@ -4907,7 +4925,7 @@
         <v>35</v>
       </c>
       <c r="R5" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="6" spans="2:18">
@@ -4924,10 +4942,10 @@
         <v>17</v>
       </c>
       <c r="N6" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="O6" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="P6" t="s">
         <v>25</v>
@@ -4936,7 +4954,7 @@
         <v>35</v>
       </c>
       <c r="R6" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="7" spans="2:18">
@@ -4953,10 +4971,10 @@
         <v>17</v>
       </c>
       <c r="N7" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="O7" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="P7" t="s">
         <v>25</v>
@@ -4965,7 +4983,7 @@
         <v>35</v>
       </c>
       <c r="R7" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="8" spans="2:18">
@@ -4982,10 +5000,10 @@
         <v>17</v>
       </c>
       <c r="N8" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="O8" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="P8" t="s">
         <v>25</v>
@@ -4994,7 +5012,7 @@
         <v>35</v>
       </c>
       <c r="R8" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="9" spans="2:18">
@@ -5011,10 +5029,10 @@
         <v>17</v>
       </c>
       <c r="N9" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="O9" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="P9" t="s">
         <v>25</v>
@@ -5023,7 +5041,7 @@
         <v>35</v>
       </c>
       <c r="R9" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="10" spans="2:18">
@@ -5040,10 +5058,10 @@
         <v>17</v>
       </c>
       <c r="N10" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="O10" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="P10" t="s">
         <v>25</v>
@@ -5052,7 +5070,7 @@
         <v>35</v>
       </c>
       <c r="R10" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="11" spans="2:18">
@@ -5069,10 +5087,10 @@
         <v>17</v>
       </c>
       <c r="N11" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="O11" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="P11" t="s">
         <v>25</v>
@@ -5081,7 +5099,7 @@
         <v>35</v>
       </c>
       <c r="R11" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="12" spans="2:18">
@@ -5098,10 +5116,10 @@
         <v>17</v>
       </c>
       <c r="N12" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="O12" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="P12" t="s">
         <v>25</v>
@@ -5110,7 +5128,7 @@
         <v>35</v>
       </c>
       <c r="R12" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="13" spans="2:18">
@@ -5127,10 +5145,10 @@
         <v>17</v>
       </c>
       <c r="N13" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="O13" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="P13" t="s">
         <v>25</v>
@@ -5139,7 +5157,7 @@
         <v>35</v>
       </c>
       <c r="R13" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="14" spans="2:18">
@@ -5159,10 +5177,10 @@
         <v>17</v>
       </c>
       <c r="N14" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="O14" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="P14" t="s">
         <v>25</v>
@@ -5171,7 +5189,7 @@
         <v>35</v>
       </c>
       <c r="R14" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="15" spans="2:18">
@@ -5191,10 +5209,10 @@
         <v>17</v>
       </c>
       <c r="N15" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="O15" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="P15" t="s">
         <v>25</v>
@@ -5203,7 +5221,7 @@
         <v>35</v>
       </c>
       <c r="R15" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="16" spans="2:18">
@@ -5232,10 +5250,10 @@
         <v>17</v>
       </c>
       <c r="N16" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="O16" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="P16" t="s">
         <v>25</v>
@@ -5244,7 +5262,7 @@
         <v>35</v>
       </c>
       <c r="R16" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="17" spans="2:18">
@@ -5264,10 +5282,10 @@
         <v>17</v>
       </c>
       <c r="N17" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="O17" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="P17" t="s">
         <v>25</v>
@@ -5276,7 +5294,7 @@
         <v>35</v>
       </c>
       <c r="R17" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="18" spans="2:18">
@@ -5296,10 +5314,10 @@
         <v>17</v>
       </c>
       <c r="N18" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="O18" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="P18" t="s">
         <v>25</v>
@@ -5308,7 +5326,7 @@
         <v>35</v>
       </c>
       <c r="R18" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="19" spans="2:18">
@@ -5328,10 +5346,10 @@
         <v>17</v>
       </c>
       <c r="N19" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="O19" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="P19" t="s">
         <v>25</v>
@@ -5340,7 +5358,7 @@
         <v>35</v>
       </c>
       <c r="R19" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="20" spans="2:18">
@@ -5360,10 +5378,10 @@
         <v>17</v>
       </c>
       <c r="N20" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="O20" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="P20" t="s">
         <v>25</v>
@@ -5372,7 +5390,7 @@
         <v>35</v>
       </c>
       <c r="R20" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="21" spans="2:18">
@@ -5398,10 +5416,10 @@
         <v>17</v>
       </c>
       <c r="N21" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="O21" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="P21" t="s">
         <v>25</v>
@@ -5410,7 +5428,7 @@
         <v>35</v>
       </c>
       <c r="R21" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="22" spans="2:18">
@@ -5430,10 +5448,10 @@
         <v>17</v>
       </c>
       <c r="N22" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="O22" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="P22" t="s">
         <v>25</v>
@@ -5442,7 +5460,7 @@
         <v>35</v>
       </c>
       <c r="R22" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="23" spans="2:18">
@@ -5459,10 +5477,10 @@
         <v>17</v>
       </c>
       <c r="N23" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="O23" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="P23" t="s">
         <v>25</v>
@@ -5471,7 +5489,7 @@
         <v>35</v>
       </c>
       <c r="R23" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="24" spans="2:18">
@@ -5488,10 +5506,10 @@
         <v>17</v>
       </c>
       <c r="N24" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="O24" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="P24" t="s">
         <v>25</v>
@@ -5500,7 +5518,7 @@
         <v>35</v>
       </c>
       <c r="R24" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="25" spans="2:18">
@@ -5508,10 +5526,10 @@
         <v>17</v>
       </c>
       <c r="N25" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="O25" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="P25" t="s">
         <v>25</v>
@@ -5520,7 +5538,7 @@
         <v>35</v>
       </c>
       <c r="R25" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="26" spans="2:18">
@@ -5528,10 +5546,10 @@
         <v>17</v>
       </c>
       <c r="N26" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="O26" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="P26" t="s">
         <v>25</v>
@@ -5540,7 +5558,7 @@
         <v>35</v>
       </c>
       <c r="R26" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="27" spans="2:18">
@@ -5548,10 +5566,10 @@
         <v>17</v>
       </c>
       <c r="N27" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="O27" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="P27" t="s">
         <v>25</v>
@@ -5560,58 +5578,81 @@
         <v>35</v>
       </c>
       <c r="R27" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="28" spans="2:18" ht="17.649999999999999" thickBot="1">
+      <c r="B28" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
+      <c r="M28" t="s">
+        <v>17</v>
+      </c>
+      <c r="N28" t="s">
+        <v>268</v>
+      </c>
+      <c r="O28" t="s">
+        <v>269</v>
+      </c>
+      <c r="P28" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>35</v>
+      </c>
+      <c r="R28" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="29" spans="2:18" ht="15" thickTop="1" thickBot="1">
+      <c r="B29" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="M29" t="s">
+        <v>17</v>
+      </c>
+      <c r="N29" t="s">
+        <v>270</v>
+      </c>
+      <c r="O29" t="s">
+        <v>271</v>
+      </c>
+      <c r="P29" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>35</v>
+      </c>
+      <c r="R29" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="30" spans="2:18">
+      <c r="B30" t="s">
+        <v>218</v>
+      </c>
+      <c r="C30" t="s">
         <v>217</v>
       </c>
-    </row>
-    <row r="28" spans="2:18">
-      <c r="M28" t="s">
-        <v>17</v>
-      </c>
-      <c r="N28" t="s">
-        <v>262</v>
-      </c>
-      <c r="O28" t="s">
-        <v>263</v>
-      </c>
-      <c r="P28" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q28" t="s">
-        <v>35</v>
-      </c>
-      <c r="R28" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="29" spans="2:18">
-      <c r="M29" t="s">
-        <v>17</v>
-      </c>
-      <c r="N29" t="s">
-        <v>264</v>
-      </c>
-      <c r="O29" t="s">
-        <v>265</v>
-      </c>
-      <c r="P29" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q29" t="s">
-        <v>35</v>
-      </c>
-      <c r="R29" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="30" spans="2:18">
+      <c r="D30" t="s">
+        <v>216</v>
+      </c>
       <c r="M30" t="s">
         <v>17</v>
       </c>
       <c r="N30" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="O30" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="P30" t="s">
         <v>25</v>
@@ -5620,7 +5661,7 @@
         <v>35</v>
       </c>
       <c r="R30" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="31" spans="2:18">
@@ -5628,10 +5669,10 @@
         <v>17</v>
       </c>
       <c r="N31" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="O31" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="P31" t="s">
         <v>25</v>
@@ -5640,7 +5681,7 @@
         <v>35</v>
       </c>
       <c r="R31" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="32" spans="2:18">
@@ -5648,10 +5689,10 @@
         <v>17</v>
       </c>
       <c r="N32" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="O32" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="P32" t="s">
         <v>25</v>
@@ -5660,7 +5701,7 @@
         <v>35</v>
       </c>
       <c r="R32" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="33" spans="13:18">
@@ -5668,10 +5709,10 @@
         <v>17</v>
       </c>
       <c r="N33" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="O33" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="P33" t="s">
         <v>25</v>
@@ -5680,7 +5721,7 @@
         <v>35</v>
       </c>
       <c r="R33" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="34" spans="13:18">
@@ -5688,10 +5729,10 @@
         <v>17</v>
       </c>
       <c r="N34" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="O34" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="P34" t="s">
         <v>25</v>
@@ -5700,7 +5741,7 @@
         <v>35</v>
       </c>
       <c r="R34" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="35" spans="13:18">
@@ -5708,10 +5749,10 @@
         <v>17</v>
       </c>
       <c r="N35" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="O35" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="P35" t="s">
         <v>25</v>
@@ -5720,7 +5761,7 @@
         <v>35</v>
       </c>
       <c r="R35" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="36" spans="13:18">
@@ -5728,10 +5769,10 @@
         <v>17</v>
       </c>
       <c r="N36" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="O36" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="P36" t="s">
         <v>25</v>
@@ -5740,7 +5781,7 @@
         <v>35</v>
       </c>
       <c r="R36" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="37" spans="13:18">
@@ -5748,10 +5789,10 @@
         <v>17</v>
       </c>
       <c r="N37" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="O37" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="P37" t="s">
         <v>25</v>
@@ -5760,7 +5801,7 @@
         <v>35</v>
       </c>
       <c r="R37" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="38" spans="13:18">
@@ -5768,10 +5809,10 @@
         <v>17</v>
       </c>
       <c r="N38" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="O38" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="P38" t="s">
         <v>25</v>
@@ -5780,7 +5821,7 @@
         <v>35</v>
       </c>
       <c r="R38" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="39" spans="13:18">
@@ -5788,10 +5829,10 @@
         <v>17</v>
       </c>
       <c r="N39" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="O39" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="P39" t="s">
         <v>25</v>
@@ -5800,7 +5841,7 @@
         <v>35</v>
       </c>
       <c r="R39" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="40" spans="13:18">
@@ -5808,10 +5849,10 @@
         <v>17</v>
       </c>
       <c r="N40" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="O40" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="P40" t="s">
         <v>25</v>
@@ -5820,7 +5861,7 @@
         <v>35</v>
       </c>
       <c r="R40" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="41" spans="13:18">
@@ -5828,10 +5869,10 @@
         <v>17</v>
       </c>
       <c r="N41" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="O41" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="P41" t="s">
         <v>25</v>
@@ -5840,7 +5881,7 @@
         <v>35</v>
       </c>
       <c r="R41" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="42" spans="13:18">
@@ -5848,10 +5889,10 @@
         <v>17</v>
       </c>
       <c r="N42" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="O42" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="P42" t="s">
         <v>25</v>
@@ -5860,7 +5901,7 @@
         <v>35</v>
       </c>
       <c r="R42" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="43" spans="13:18">
@@ -5868,10 +5909,10 @@
         <v>17</v>
       </c>
       <c r="N43" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="O43" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="P43" t="s">
         <v>25</v>
@@ -5880,7 +5921,7 @@
         <v>35</v>
       </c>
       <c r="R43" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="44" spans="13:18">
@@ -5888,10 +5929,10 @@
         <v>17</v>
       </c>
       <c r="N44" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="O44" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="P44" t="s">
         <v>25</v>
@@ -5900,7 +5941,7 @@
         <v>35</v>
       </c>
       <c r="R44" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="45" spans="13:18">
@@ -5908,10 +5949,10 @@
         <v>17</v>
       </c>
       <c r="N45" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="O45" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="P45" t="s">
         <v>25</v>
@@ -5920,7 +5961,7 @@
         <v>35</v>
       </c>
       <c r="R45" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="46" spans="13:18">
@@ -5928,10 +5969,10 @@
         <v>17</v>
       </c>
       <c r="N46" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="O46" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="P46" t="s">
         <v>25</v>
@@ -5940,7 +5981,7 @@
         <v>35</v>
       </c>
       <c r="R46" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="47" spans="13:18">
@@ -5948,10 +5989,10 @@
         <v>17</v>
       </c>
       <c r="N47" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="O47" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="P47" t="s">
         <v>25</v>
@@ -5960,7 +6001,7 @@
         <v>35</v>
       </c>
       <c r="R47" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="48" spans="13:18">
@@ -5968,10 +6009,10 @@
         <v>17</v>
       </c>
       <c r="N48" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="O48" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="P48" t="s">
         <v>25</v>
@@ -5980,7 +6021,7 @@
         <v>35</v>
       </c>
       <c r="R48" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="49" spans="13:18">
@@ -5988,10 +6029,10 @@
         <v>17</v>
       </c>
       <c r="N49" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="O49" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="P49" t="s">
         <v>25</v>
@@ -6000,7 +6041,7 @@
         <v>35</v>
       </c>
       <c r="R49" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="50" spans="13:18">
@@ -6008,10 +6049,10 @@
         <v>17</v>
       </c>
       <c r="N50" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="O50" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="P50" t="s">
         <v>25</v>
@@ -6020,7 +6061,7 @@
         <v>35</v>
       </c>
       <c r="R50" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="51" spans="13:18">
@@ -6028,10 +6069,10 @@
         <v>17</v>
       </c>
       <c r="N51" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="O51" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="P51" t="s">
         <v>25</v>
@@ -6040,7 +6081,7 @@
         <v>35</v>
       </c>
       <c r="R51" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="52" spans="13:18">
@@ -6048,10 +6089,10 @@
         <v>17</v>
       </c>
       <c r="N52" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="O52" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="P52" t="s">
         <v>25</v>
@@ -6060,7 +6101,7 @@
         <v>35</v>
       </c>
       <c r="R52" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="53" spans="13:18">
@@ -6068,10 +6109,10 @@
         <v>17</v>
       </c>
       <c r="N53" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="O53" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="P53" t="s">
         <v>25</v>
@@ -6080,7 +6121,7 @@
         <v>35</v>
       </c>
       <c r="R53" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="54" spans="13:18">
@@ -6088,10 +6129,10 @@
         <v>17</v>
       </c>
       <c r="N54" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="O54" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="P54" t="s">
         <v>25</v>
@@ -6100,7 +6141,7 @@
         <v>35</v>
       </c>
       <c r="R54" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="55" spans="13:18">
@@ -6108,10 +6149,10 @@
         <v>17</v>
       </c>
       <c r="N55" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="O55" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="P55" t="s">
         <v>25</v>
@@ -6120,7 +6161,7 @@
         <v>35</v>
       </c>
       <c r="R55" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="56" spans="13:18">
@@ -6128,10 +6169,10 @@
         <v>17</v>
       </c>
       <c r="N56" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="O56" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="P56" t="s">
         <v>25</v>
@@ -6140,7 +6181,7 @@
         <v>35</v>
       </c>
       <c r="R56" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="57" spans="13:18">
@@ -6148,10 +6189,10 @@
         <v>17</v>
       </c>
       <c r="N57" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="O57" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="P57" t="s">
         <v>25</v>
@@ -6160,7 +6201,7 @@
         <v>35</v>
       </c>
       <c r="R57" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="58" spans="13:18">
@@ -6168,10 +6209,10 @@
         <v>17</v>
       </c>
       <c r="N58" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="O58" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="P58" t="s">
         <v>25</v>
@@ -6180,7 +6221,7 @@
         <v>35</v>
       </c>
       <c r="R58" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="59" spans="13:18">
@@ -6188,10 +6229,10 @@
         <v>17</v>
       </c>
       <c r="N59" t="s">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="O59" t="s">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="P59" t="s">
         <v>25</v>
@@ -6200,7 +6241,7 @@
         <v>35</v>
       </c>
       <c r="R59" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="60" spans="13:18">
@@ -6208,10 +6249,10 @@
         <v>17</v>
       </c>
       <c r="N60" t="s">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="O60" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="P60" t="s">
         <v>25</v>
@@ -6220,7 +6261,7 @@
         <v>35</v>
       </c>
       <c r="R60" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="61" spans="13:18">
@@ -6228,10 +6269,10 @@
         <v>17</v>
       </c>
       <c r="N61" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="O61" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="P61" t="s">
         <v>25</v>
@@ -6240,7 +6281,7 @@
         <v>35</v>
       </c>
       <c r="R61" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="62" spans="13:18">
@@ -6248,10 +6289,10 @@
         <v>17</v>
       </c>
       <c r="N62" t="s">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="O62" t="s">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="P62" t="s">
         <v>25</v>
@@ -6260,7 +6301,7 @@
         <v>35</v>
       </c>
       <c r="R62" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="63" spans="13:18">
@@ -6268,10 +6309,10 @@
         <v>17</v>
       </c>
       <c r="N63" t="s">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="O63" t="s">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="P63" t="s">
         <v>25</v>
@@ -6280,7 +6321,7 @@
         <v>35</v>
       </c>
       <c r="R63" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="64" spans="13:18">
@@ -6288,10 +6329,10 @@
         <v>17</v>
       </c>
       <c r="N64" t="s">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="O64" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="P64" t="s">
         <v>25</v>
@@ -6300,7 +6341,7 @@
         <v>35</v>
       </c>
       <c r="R64" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="65" spans="13:18">
@@ -6308,10 +6349,10 @@
         <v>17</v>
       </c>
       <c r="N65" t="s">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="O65" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="P65" t="s">
         <v>25</v>
@@ -6320,7 +6361,7 @@
         <v>35</v>
       </c>
       <c r="R65" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="66" spans="13:18">
@@ -6328,10 +6369,10 @@
         <v>17</v>
       </c>
       <c r="N66" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="O66" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="P66" t="s">
         <v>25</v>
@@ -6340,7 +6381,7 @@
         <v>35</v>
       </c>
       <c r="R66" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="67" spans="13:18">
@@ -6348,10 +6389,10 @@
         <v>17</v>
       </c>
       <c r="N67" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="O67" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="P67" t="s">
         <v>25</v>
@@ -6360,7 +6401,7 @@
         <v>35</v>
       </c>
       <c r="R67" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="68" spans="13:18">
@@ -6368,10 +6409,10 @@
         <v>17</v>
       </c>
       <c r="N68" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="O68" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="P68" t="s">
         <v>25</v>
@@ -6380,7 +6421,7 @@
         <v>35</v>
       </c>
       <c r="R68" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="69" spans="13:18">
@@ -6388,10 +6429,10 @@
         <v>17</v>
       </c>
       <c r="N69" t="s">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="O69" t="s">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="P69" t="s">
         <v>25</v>
@@ -6400,7 +6441,7 @@
         <v>35</v>
       </c>
       <c r="R69" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="70" spans="13:18">
@@ -6408,10 +6449,10 @@
         <v>17</v>
       </c>
       <c r="N70" t="s">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="O70" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="P70" t="s">
         <v>25</v>
@@ -6420,7 +6461,7 @@
         <v>35</v>
       </c>
       <c r="R70" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="71" spans="13:18">
@@ -6428,10 +6469,10 @@
         <v>17</v>
       </c>
       <c r="N71" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="O71" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="P71" t="s">
         <v>25</v>
@@ -6440,7 +6481,7 @@
         <v>35</v>
       </c>
       <c r="R71" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="72" spans="13:18">
@@ -6448,10 +6489,10 @@
         <v>17</v>
       </c>
       <c r="N72" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="O72" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="P72" t="s">
         <v>25</v>
@@ -6460,7 +6501,7 @@
         <v>35</v>
       </c>
       <c r="R72" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="73" spans="13:18">
@@ -6468,10 +6509,10 @@
         <v>17</v>
       </c>
       <c r="N73" t="s">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="O73" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="P73" t="s">
         <v>25</v>
@@ -6480,7 +6521,7 @@
         <v>35</v>
       </c>
       <c r="R73" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="74" spans="13:18">
@@ -6488,10 +6529,10 @@
         <v>17</v>
       </c>
       <c r="N74" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="O74" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="P74" t="s">
         <v>25</v>
@@ -6500,7 +6541,7 @@
         <v>35</v>
       </c>
       <c r="R74" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="75" spans="13:18">
@@ -6508,10 +6549,10 @@
         <v>17</v>
       </c>
       <c r="N75" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="O75" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="P75" t="s">
         <v>25</v>
@@ -6520,7 +6561,7 @@
         <v>35</v>
       </c>
       <c r="R75" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="76" spans="13:18">
@@ -6528,10 +6569,10 @@
         <v>17</v>
       </c>
       <c r="N76" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="O76" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="P76" t="s">
         <v>25</v>
@@ -6540,7 +6581,7 @@
         <v>35</v>
       </c>
       <c r="R76" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="77" spans="13:18">
@@ -6548,10 +6589,10 @@
         <v>17</v>
       </c>
       <c r="N77" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="O77" t="s">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="P77" t="s">
         <v>25</v>
@@ -6560,7 +6601,7 @@
         <v>35</v>
       </c>
       <c r="R77" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="78" spans="13:18">
@@ -6568,10 +6609,10 @@
         <v>17</v>
       </c>
       <c r="N78" t="s">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="O78" t="s">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="P78" t="s">
         <v>25</v>
@@ -6580,7 +6621,7 @@
         <v>35</v>
       </c>
       <c r="R78" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="79" spans="13:18">
@@ -6588,10 +6629,10 @@
         <v>17</v>
       </c>
       <c r="N79" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="O79" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="P79" t="s">
         <v>25</v>
@@ -6600,7 +6641,7 @@
         <v>35</v>
       </c>
       <c r="R79" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="80" spans="13:18">
@@ -6608,10 +6649,10 @@
         <v>17</v>
       </c>
       <c r="N80" t="s">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c r="O80" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="P80" t="s">
         <v>25</v>
@@ -6620,7 +6661,7 @@
         <v>35</v>
       </c>
       <c r="R80" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="81" spans="13:18">
@@ -6628,10 +6669,10 @@
         <v>17</v>
       </c>
       <c r="N81" t="s">
-        <v>368</v>
+        <v>374</v>
       </c>
       <c r="O81" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="P81" t="s">
         <v>25</v>
@@ -6640,7 +6681,7 @@
         <v>35</v>
       </c>
       <c r="R81" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="82" spans="13:18">
@@ -6648,10 +6689,10 @@
         <v>17</v>
       </c>
       <c r="N82" t="s">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="O82" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="P82" t="s">
         <v>25</v>
@@ -6660,7 +6701,7 @@
         <v>35</v>
       </c>
       <c r="R82" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="83" spans="13:18">
@@ -6668,10 +6709,10 @@
         <v>17</v>
       </c>
       <c r="N83" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="O83" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="P83" t="s">
         <v>25</v>
@@ -6680,7 +6721,7 @@
         <v>35</v>
       </c>
       <c r="R83" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="84" spans="13:18">
@@ -6688,10 +6729,10 @@
         <v>17</v>
       </c>
       <c r="N84" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="O84" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="P84" t="s">
         <v>25</v>
@@ -6700,7 +6741,7 @@
         <v>35</v>
       </c>
       <c r="R84" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="85" spans="13:18">
@@ -6708,10 +6749,10 @@
         <v>17</v>
       </c>
       <c r="N85" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="O85" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="P85" t="s">
         <v>25</v>
@@ -6720,7 +6761,7 @@
         <v>35</v>
       </c>
       <c r="R85" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="86" spans="13:18">
@@ -6728,10 +6769,10 @@
         <v>17</v>
       </c>
       <c r="N86" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="O86" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="P86" t="s">
         <v>25</v>
@@ -6740,7 +6781,7 @@
         <v>35</v>
       </c>
       <c r="R86" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="87" spans="13:18">
@@ -6748,10 +6789,10 @@
         <v>17</v>
       </c>
       <c r="N87" t="s">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="O87" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="P87" t="s">
         <v>25</v>
@@ -6760,7 +6801,7 @@
         <v>35</v>
       </c>
       <c r="R87" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="88" spans="13:18">
@@ -6768,10 +6809,10 @@
         <v>17</v>
       </c>
       <c r="N88" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="O88" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="P88" t="s">
         <v>25</v>
@@ -6780,7 +6821,7 @@
         <v>35</v>
       </c>
       <c r="R88" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="89" spans="13:18">
@@ -6788,10 +6829,10 @@
         <v>17</v>
       </c>
       <c r="N89" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="O89" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="P89" t="s">
         <v>25</v>
@@ -6800,7 +6841,7 @@
         <v>35</v>
       </c>
       <c r="R89" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="90" spans="13:18">
@@ -6808,10 +6849,10 @@
         <v>17</v>
       </c>
       <c r="N90" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="O90" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="P90" t="s">
         <v>25</v>
@@ -6820,7 +6861,7 @@
         <v>35</v>
       </c>
       <c r="R90" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="91" spans="13:18">
@@ -6828,10 +6869,10 @@
         <v>17</v>
       </c>
       <c r="N91" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="O91" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="P91" t="s">
         <v>25</v>
@@ -6840,7 +6881,7 @@
         <v>35</v>
       </c>
       <c r="R91" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="92" spans="13:18">
@@ -6848,10 +6889,10 @@
         <v>17</v>
       </c>
       <c r="N92" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="O92" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="P92" t="s">
         <v>25</v>
@@ -6860,7 +6901,7 @@
         <v>35</v>
       </c>
       <c r="R92" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="93" spans="13:18">
@@ -6868,10 +6909,10 @@
         <v>17</v>
       </c>
       <c r="N93" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="O93" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="P93" t="s">
         <v>25</v>
@@ -6880,7 +6921,7 @@
         <v>35</v>
       </c>
       <c r="R93" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="94" spans="13:18">
@@ -6888,10 +6929,10 @@
         <v>17</v>
       </c>
       <c r="N94" t="s">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="O94" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
       <c r="P94" t="s">
         <v>25</v>
@@ -6900,7 +6941,7 @@
         <v>35</v>
       </c>
       <c r="R94" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="95" spans="13:18">
@@ -6908,10 +6949,10 @@
         <v>17</v>
       </c>
       <c r="N95" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="O95" t="s">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="P95" t="s">
         <v>25</v>
@@ -6920,7 +6961,7 @@
         <v>35</v>
       </c>
       <c r="R95" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="96" spans="13:18">
@@ -6928,10 +6969,10 @@
         <v>17</v>
       </c>
       <c r="N96" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="O96" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="P96" t="s">
         <v>25</v>
@@ -6940,7 +6981,7 @@
         <v>35</v>
       </c>
       <c r="R96" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="97" spans="13:18">
@@ -6948,10 +6989,10 @@
         <v>17</v>
       </c>
       <c r="N97" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="O97" t="s">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="P97" t="s">
         <v>25</v>
@@ -6960,7 +7001,7 @@
         <v>35</v>
       </c>
       <c r="R97" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="98" spans="13:18">
@@ -6968,10 +7009,10 @@
         <v>17</v>
       </c>
       <c r="N98" t="s">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="O98" t="s">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="P98" t="s">
         <v>25</v>
@@ -6980,7 +7021,7 @@
         <v>35</v>
       </c>
       <c r="R98" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="99" spans="13:18">
@@ -6988,10 +7029,10 @@
         <v>17</v>
       </c>
       <c r="N99" t="s">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="O99" t="s">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="P99" t="s">
         <v>25</v>
@@ -7000,7 +7041,7 @@
         <v>35</v>
       </c>
       <c r="R99" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="100" spans="13:18">
@@ -7008,10 +7049,10 @@
         <v>17</v>
       </c>
       <c r="N100" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="O100" t="s">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="P100" t="s">
         <v>25</v>
@@ -7020,7 +7061,7 @@
         <v>35</v>
       </c>
       <c r="R100" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="101" spans="13:18">
@@ -7028,10 +7069,10 @@
         <v>17</v>
       </c>
       <c r="N101" t="s">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="O101" t="s">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="P101" t="s">
         <v>25</v>
@@ -7040,7 +7081,7 @@
         <v>35</v>
       </c>
       <c r="R101" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="102" spans="13:18">
@@ -7048,10 +7089,10 @@
         <v>17</v>
       </c>
       <c r="N102" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="O102" t="s">
-        <v>411</v>
+        <v>417</v>
       </c>
       <c r="P102" t="s">
         <v>25</v>
@@ -7060,7 +7101,7 @@
         <v>35</v>
       </c>
       <c r="R102" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="103" spans="13:18">
@@ -7068,10 +7109,10 @@
         <v>17</v>
       </c>
       <c r="N103" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
       <c r="O103" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="P103" t="s">
         <v>25</v>
@@ -7080,7 +7121,7 @@
         <v>35</v>
       </c>
       <c r="R103" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="104" spans="13:18">
@@ -7088,10 +7129,10 @@
         <v>17</v>
       </c>
       <c r="N104" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="O104" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="P104" t="s">
         <v>25</v>
@@ -7100,7 +7141,7 @@
         <v>35</v>
       </c>
       <c r="R104" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="105" spans="13:18">
@@ -7108,10 +7149,10 @@
         <v>17</v>
       </c>
       <c r="N105" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="O105" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="P105" t="s">
         <v>25</v>
@@ -7120,7 +7161,7 @@
         <v>35</v>
       </c>
       <c r="R105" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="106" spans="13:18">
@@ -7128,10 +7169,10 @@
         <v>17</v>
       </c>
       <c r="N106" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="O106" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="P106" t="s">
         <v>25</v>
@@ -7140,7 +7181,7 @@
         <v>35</v>
       </c>
       <c r="R106" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="107" spans="13:18">
@@ -7148,10 +7189,10 @@
         <v>17</v>
       </c>
       <c r="N107" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="O107" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="P107" t="s">
         <v>25</v>
@@ -7160,7 +7201,7 @@
         <v>35</v>
       </c>
       <c r="R107" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="108" spans="13:18">
@@ -7168,10 +7209,10 @@
         <v>17</v>
       </c>
       <c r="N108" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="O108" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="P108" t="s">
         <v>25</v>
@@ -7180,7 +7221,7 @@
         <v>35</v>
       </c>
       <c r="R108" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="109" spans="13:18">
@@ -7188,10 +7229,10 @@
         <v>17</v>
       </c>
       <c r="N109" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="O109" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="P109" t="s">
         <v>25</v>
@@ -7200,7 +7241,7 @@
         <v>35</v>
       </c>
       <c r="R109" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="110" spans="13:18">
@@ -7208,10 +7249,10 @@
         <v>17</v>
       </c>
       <c r="N110" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="O110" t="s">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="P110" t="s">
         <v>25</v>
@@ -7220,7 +7261,7 @@
         <v>35</v>
       </c>
       <c r="R110" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="111" spans="13:18">
@@ -7228,10 +7269,10 @@
         <v>17</v>
       </c>
       <c r="N111" t="s">
-        <v>428</v>
+        <v>434</v>
       </c>
       <c r="O111" t="s">
-        <v>429</v>
+        <v>435</v>
       </c>
       <c r="P111" t="s">
         <v>25</v>
@@ -7240,7 +7281,7 @@
         <v>35</v>
       </c>
       <c r="R111" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="112" spans="13:18">
@@ -7248,10 +7289,10 @@
         <v>17</v>
       </c>
       <c r="N112" t="s">
-        <v>430</v>
+        <v>436</v>
       </c>
       <c r="O112" t="s">
-        <v>431</v>
+        <v>437</v>
       </c>
       <c r="P112" t="s">
         <v>25</v>
@@ -7260,7 +7301,7 @@
         <v>35</v>
       </c>
       <c r="R112" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="113" spans="13:18">
@@ -7268,10 +7309,10 @@
         <v>17</v>
       </c>
       <c r="N113" t="s">
-        <v>432</v>
+        <v>438</v>
       </c>
       <c r="O113" t="s">
-        <v>433</v>
+        <v>439</v>
       </c>
       <c r="P113" t="s">
         <v>25</v>
@@ -7280,7 +7321,7 @@
         <v>35</v>
       </c>
       <c r="R113" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="114" spans="13:18">
@@ -7288,10 +7329,10 @@
         <v>17</v>
       </c>
       <c r="N114" t="s">
-        <v>434</v>
+        <v>440</v>
       </c>
       <c r="O114" t="s">
-        <v>435</v>
+        <v>441</v>
       </c>
       <c r="P114" t="s">
         <v>25</v>
@@ -7300,7 +7341,7 @@
         <v>35</v>
       </c>
       <c r="R114" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="115" spans="13:18">
@@ -7308,10 +7349,10 @@
         <v>17</v>
       </c>
       <c r="N115" t="s">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="O115" t="s">
-        <v>437</v>
+        <v>443</v>
       </c>
       <c r="P115" t="s">
         <v>25</v>
@@ -7320,7 +7361,7 @@
         <v>35</v>
       </c>
       <c r="R115" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="116" spans="13:18">
@@ -7328,10 +7369,10 @@
         <v>17</v>
       </c>
       <c r="N116" t="s">
-        <v>438</v>
+        <v>444</v>
       </c>
       <c r="O116" t="s">
-        <v>439</v>
+        <v>445</v>
       </c>
       <c r="P116" t="s">
         <v>25</v>
@@ -7340,7 +7381,7 @@
         <v>35</v>
       </c>
       <c r="R116" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="117" spans="13:18">
@@ -7348,10 +7389,10 @@
         <v>17</v>
       </c>
       <c r="N117" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="O117" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="P117" t="s">
         <v>25</v>
@@ -7360,7 +7401,7 @@
         <v>35</v>
       </c>
       <c r="R117" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="118" spans="13:18">
@@ -7368,10 +7409,10 @@
         <v>17</v>
       </c>
       <c r="N118" t="s">
-        <v>442</v>
+        <v>448</v>
       </c>
       <c r="O118" t="s">
-        <v>443</v>
+        <v>449</v>
       </c>
       <c r="P118" t="s">
         <v>25</v>
@@ -7380,7 +7421,7 @@
         <v>35</v>
       </c>
       <c r="R118" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="119" spans="13:18">
@@ -7388,10 +7429,10 @@
         <v>17</v>
       </c>
       <c r="N119" t="s">
-        <v>444</v>
+        <v>450</v>
       </c>
       <c r="O119" t="s">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c r="P119" t="s">
         <v>25</v>
@@ -7400,7 +7441,7 @@
         <v>35</v>
       </c>
       <c r="R119" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="120" spans="13:18">
@@ -7408,10 +7449,10 @@
         <v>17</v>
       </c>
       <c r="N120" t="s">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c r="O120" t="s">
-        <v>447</v>
+        <v>453</v>
       </c>
       <c r="P120" t="s">
         <v>25</v>
@@ -7420,7 +7461,7 @@
         <v>35</v>
       </c>
       <c r="R120" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="121" spans="13:18">
@@ -7428,10 +7469,10 @@
         <v>17</v>
       </c>
       <c r="N121" t="s">
-        <v>448</v>
+        <v>454</v>
       </c>
       <c r="O121" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="P121" t="s">
         <v>25</v>
@@ -7440,7 +7481,7 @@
         <v>35</v>
       </c>
       <c r="R121" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="122" spans="13:18">
@@ -7448,10 +7489,10 @@
         <v>17</v>
       </c>
       <c r="N122" t="s">
-        <v>450</v>
+        <v>456</v>
       </c>
       <c r="O122" t="s">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="P122" t="s">
         <v>25</v>
@@ -7460,7 +7501,7 @@
         <v>35</v>
       </c>
       <c r="R122" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="123" spans="13:18">
@@ -7468,10 +7509,10 @@
         <v>17</v>
       </c>
       <c r="N123" t="s">
-        <v>452</v>
+        <v>458</v>
       </c>
       <c r="O123" t="s">
-        <v>453</v>
+        <v>459</v>
       </c>
       <c r="P123" t="s">
         <v>25</v>
@@ -7480,7 +7521,7 @@
         <v>35</v>
       </c>
       <c r="R123" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="124" spans="13:18">
@@ -7488,10 +7529,10 @@
         <v>17</v>
       </c>
       <c r="N124" t="s">
-        <v>454</v>
+        <v>460</v>
       </c>
       <c r="O124" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="P124" t="s">
         <v>25</v>
@@ -7500,7 +7541,7 @@
         <v>35</v>
       </c>
       <c r="R124" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="125" spans="13:18">
@@ -7508,10 +7549,10 @@
         <v>17</v>
       </c>
       <c r="N125" t="s">
-        <v>456</v>
+        <v>462</v>
       </c>
       <c r="O125" t="s">
-        <v>457</v>
+        <v>463</v>
       </c>
       <c r="P125" t="s">
         <v>25</v>
@@ -7520,7 +7561,7 @@
         <v>35</v>
       </c>
       <c r="R125" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="126" spans="13:18">
@@ -7528,10 +7569,10 @@
         <v>17</v>
       </c>
       <c r="N126" t="s">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="O126" t="s">
-        <v>459</v>
+        <v>465</v>
       </c>
       <c r="P126" t="s">
         <v>25</v>
@@ -7540,7 +7581,7 @@
         <v>35</v>
       </c>
       <c r="R126" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="127" spans="13:18">
@@ -7548,10 +7589,10 @@
         <v>17</v>
       </c>
       <c r="N127" t="s">
-        <v>460</v>
+        <v>466</v>
       </c>
       <c r="O127" t="s">
-        <v>461</v>
+        <v>467</v>
       </c>
       <c r="P127" t="s">
         <v>25</v>
@@ -7560,7 +7601,7 @@
         <v>35</v>
       </c>
       <c r="R127" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="128" spans="13:18">
@@ -7568,10 +7609,10 @@
         <v>17</v>
       </c>
       <c r="N128" t="s">
-        <v>462</v>
+        <v>468</v>
       </c>
       <c r="O128" t="s">
-        <v>463</v>
+        <v>469</v>
       </c>
       <c r="P128" t="s">
         <v>25</v>
@@ -7580,7 +7621,7 @@
         <v>35</v>
       </c>
       <c r="R128" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="129" spans="13:18">
@@ -7588,10 +7629,10 @@
         <v>17</v>
       </c>
       <c r="N129" t="s">
-        <v>464</v>
+        <v>470</v>
       </c>
       <c r="O129" t="s">
-        <v>465</v>
+        <v>471</v>
       </c>
       <c r="P129" t="s">
         <v>25</v>
@@ -7600,7 +7641,7 @@
         <v>35</v>
       </c>
       <c r="R129" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="130" spans="13:18">
@@ -7608,10 +7649,10 @@
         <v>17</v>
       </c>
       <c r="N130" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
       <c r="O130" t="s">
-        <v>467</v>
+        <v>473</v>
       </c>
       <c r="P130" t="s">
         <v>25</v>
@@ -7620,7 +7661,7 @@
         <v>35</v>
       </c>
       <c r="R130" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="131" spans="13:18">
@@ -7628,10 +7669,10 @@
         <v>17</v>
       </c>
       <c r="N131" t="s">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="O131" t="s">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="P131" t="s">
         <v>25</v>
@@ -7640,7 +7681,7 @@
         <v>35</v>
       </c>
       <c r="R131" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="132" spans="13:18">
@@ -7648,10 +7689,10 @@
         <v>17</v>
       </c>
       <c r="N132" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
       <c r="O132" t="s">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c r="P132" t="s">
         <v>25</v>
@@ -7660,7 +7701,7 @@
         <v>35</v>
       </c>
       <c r="R132" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="133" spans="13:18">
@@ -7668,10 +7709,10 @@
         <v>17</v>
       </c>
       <c r="N133" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="O133" t="s">
-        <v>473</v>
+        <v>479</v>
       </c>
       <c r="P133" t="s">
         <v>25</v>
@@ -7680,7 +7721,7 @@
         <v>35</v>
       </c>
       <c r="R133" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="134" spans="13:18">
@@ -7688,10 +7729,10 @@
         <v>17</v>
       </c>
       <c r="N134" t="s">
-        <v>474</v>
+        <v>480</v>
       </c>
       <c r="O134" t="s">
-        <v>475</v>
+        <v>481</v>
       </c>
       <c r="P134" t="s">
         <v>25</v>
@@ -7700,7 +7741,7 @@
         <v>35</v>
       </c>
       <c r="R134" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="135" spans="13:18">
@@ -7708,10 +7749,10 @@
         <v>17</v>
       </c>
       <c r="N135" t="s">
-        <v>476</v>
+        <v>482</v>
       </c>
       <c r="O135" t="s">
-        <v>477</v>
+        <v>483</v>
       </c>
       <c r="P135" t="s">
         <v>25</v>
@@ -7720,7 +7761,7 @@
         <v>35</v>
       </c>
       <c r="R135" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="136" spans="13:18">
@@ -7728,10 +7769,10 @@
         <v>17</v>
       </c>
       <c r="N136" t="s">
-        <v>478</v>
+        <v>484</v>
       </c>
       <c r="O136" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
       <c r="P136" t="s">
         <v>25</v>
@@ -7740,7 +7781,7 @@
         <v>35</v>
       </c>
       <c r="R136" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="137" spans="13:18">
@@ -7748,10 +7789,10 @@
         <v>17</v>
       </c>
       <c r="N137" t="s">
-        <v>480</v>
+        <v>486</v>
       </c>
       <c r="O137" t="s">
-        <v>481</v>
+        <v>487</v>
       </c>
       <c r="P137" t="s">
         <v>25</v>
@@ -7760,7 +7801,7 @@
         <v>35</v>
       </c>
       <c r="R137" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="138" spans="13:18">
@@ -7768,10 +7809,10 @@
         <v>17</v>
       </c>
       <c r="N138" t="s">
-        <v>482</v>
+        <v>488</v>
       </c>
       <c r="O138" t="s">
-        <v>483</v>
+        <v>489</v>
       </c>
       <c r="P138" t="s">
         <v>25</v>
@@ -7780,7 +7821,7 @@
         <v>35</v>
       </c>
       <c r="R138" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="139" spans="13:18">
@@ -7788,10 +7829,10 @@
         <v>17</v>
       </c>
       <c r="N139" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
       <c r="O139" t="s">
-        <v>485</v>
+        <v>491</v>
       </c>
       <c r="P139" t="s">
         <v>25</v>
@@ -7800,7 +7841,7 @@
         <v>35</v>
       </c>
       <c r="R139" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="140" spans="13:18">
@@ -7808,10 +7849,10 @@
         <v>17</v>
       </c>
       <c r="N140" t="s">
-        <v>486</v>
+        <v>492</v>
       </c>
       <c r="O140" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="P140" t="s">
         <v>25</v>
@@ -7820,7 +7861,7 @@
         <v>35</v>
       </c>
       <c r="R140" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="141" spans="13:18">
@@ -7828,10 +7869,10 @@
         <v>17</v>
       </c>
       <c r="N141" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
       <c r="O141" t="s">
-        <v>489</v>
+        <v>495</v>
       </c>
       <c r="P141" t="s">
         <v>25</v>
@@ -7840,7 +7881,7 @@
         <v>35</v>
       </c>
       <c r="R141" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="142" spans="13:18">
@@ -7848,10 +7889,10 @@
         <v>17</v>
       </c>
       <c r="N142" t="s">
-        <v>490</v>
+        <v>496</v>
       </c>
       <c r="O142" t="s">
-        <v>491</v>
+        <v>497</v>
       </c>
       <c r="P142" t="s">
         <v>25</v>
@@ -7860,7 +7901,7 @@
         <v>35</v>
       </c>
       <c r="R142" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="143" spans="13:18">
@@ -7868,10 +7909,10 @@
         <v>17</v>
       </c>
       <c r="N143" t="s">
-        <v>492</v>
+        <v>498</v>
       </c>
       <c r="O143" t="s">
-        <v>493</v>
+        <v>499</v>
       </c>
       <c r="P143" t="s">
         <v>25</v>
@@ -7880,7 +7921,7 @@
         <v>35</v>
       </c>
       <c r="R143" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="144" spans="13:18">
@@ -7888,10 +7929,10 @@
         <v>17</v>
       </c>
       <c r="N144" t="s">
-        <v>494</v>
+        <v>500</v>
       </c>
       <c r="O144" t="s">
-        <v>495</v>
+        <v>501</v>
       </c>
       <c r="P144" t="s">
         <v>25</v>
@@ -7900,7 +7941,7 @@
         <v>35</v>
       </c>
       <c r="R144" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="145" spans="13:18">
@@ -7908,10 +7949,10 @@
         <v>17</v>
       </c>
       <c r="N145" t="s">
-        <v>496</v>
+        <v>502</v>
       </c>
       <c r="O145" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="P145" t="s">
         <v>25</v>
@@ -7920,7 +7961,7 @@
         <v>35</v>
       </c>
       <c r="R145" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="146" spans="13:18">
@@ -7928,10 +7969,10 @@
         <v>17</v>
       </c>
       <c r="N146" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="O146" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="P146" t="s">
         <v>25</v>
@@ -7940,7 +7981,7 @@
         <v>35</v>
       </c>
       <c r="R146" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="147" spans="13:18">
@@ -7948,10 +7989,10 @@
         <v>17</v>
       </c>
       <c r="N147" t="s">
-        <v>500</v>
+        <v>506</v>
       </c>
       <c r="O147" t="s">
-        <v>501</v>
+        <v>507</v>
       </c>
       <c r="P147" t="s">
         <v>25</v>
@@ -7960,7 +8001,7 @@
         <v>35</v>
       </c>
       <c r="R147" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="148" spans="13:18">
@@ -7968,10 +8009,10 @@
         <v>17</v>
       </c>
       <c r="N148" t="s">
-        <v>502</v>
+        <v>508</v>
       </c>
       <c r="O148" t="s">
-        <v>503</v>
+        <v>509</v>
       </c>
       <c r="P148" t="s">
         <v>25</v>
@@ -7980,7 +8021,7 @@
         <v>35</v>
       </c>
       <c r="R148" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="149" spans="13:18">
@@ -7988,10 +8029,10 @@
         <v>17</v>
       </c>
       <c r="N149" t="s">
-        <v>504</v>
+        <v>510</v>
       </c>
       <c r="O149" t="s">
-        <v>505</v>
+        <v>511</v>
       </c>
       <c r="P149" t="s">
         <v>25</v>
@@ -8000,7 +8041,7 @@
         <v>35</v>
       </c>
       <c r="R149" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="150" spans="13:18">
@@ -8008,10 +8049,10 @@
         <v>17</v>
       </c>
       <c r="N150" t="s">
-        <v>506</v>
+        <v>512</v>
       </c>
       <c r="O150" t="s">
-        <v>507</v>
+        <v>513</v>
       </c>
       <c r="P150" t="s">
         <v>25</v>
@@ -8020,7 +8061,7 @@
         <v>35</v>
       </c>
       <c r="R150" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="151" spans="13:18">
@@ -8028,10 +8069,10 @@
         <v>17</v>
       </c>
       <c r="N151" t="s">
-        <v>508</v>
+        <v>514</v>
       </c>
       <c r="O151" t="s">
-        <v>509</v>
+        <v>515</v>
       </c>
       <c r="P151" t="s">
         <v>25</v>
@@ -8040,7 +8081,7 @@
         <v>35</v>
       </c>
       <c r="R151" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="152" spans="13:18">
@@ -8048,10 +8089,10 @@
         <v>17</v>
       </c>
       <c r="N152" t="s">
-        <v>510</v>
+        <v>516</v>
       </c>
       <c r="O152" t="s">
-        <v>511</v>
+        <v>517</v>
       </c>
       <c r="P152" t="s">
         <v>25</v>
@@ -8060,7 +8101,7 @@
         <v>35</v>
       </c>
       <c r="R152" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="153" spans="13:18">
@@ -8068,10 +8109,10 @@
         <v>17</v>
       </c>
       <c r="N153" t="s">
-        <v>512</v>
+        <v>518</v>
       </c>
       <c r="O153" t="s">
-        <v>513</v>
+        <v>519</v>
       </c>
       <c r="P153" t="s">
         <v>25</v>
@@ -8080,7 +8121,7 @@
         <v>35</v>
       </c>
       <c r="R153" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="154" spans="13:18">
@@ -8088,10 +8129,10 @@
         <v>17</v>
       </c>
       <c r="N154" t="s">
-        <v>514</v>
+        <v>520</v>
       </c>
       <c r="O154" t="s">
-        <v>515</v>
+        <v>521</v>
       </c>
       <c r="P154" t="s">
         <v>25</v>
@@ -8100,7 +8141,7 @@
         <v>35</v>
       </c>
       <c r="R154" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="155" spans="13:18">
@@ -8108,10 +8149,10 @@
         <v>17</v>
       </c>
       <c r="N155" t="s">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="O155" t="s">
-        <v>517</v>
+        <v>523</v>
       </c>
       <c r="P155" t="s">
         <v>25</v>
@@ -8120,7 +8161,7 @@
         <v>35</v>
       </c>
       <c r="R155" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="156" spans="13:18">
@@ -8128,10 +8169,10 @@
         <v>17</v>
       </c>
       <c r="N156" t="s">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="O156" t="s">
-        <v>519</v>
+        <v>525</v>
       </c>
       <c r="P156" t="s">
         <v>25</v>
@@ -8140,7 +8181,7 @@
         <v>35</v>
       </c>
       <c r="R156" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="157" spans="13:18">
@@ -8148,10 +8189,10 @@
         <v>17</v>
       </c>
       <c r="N157" t="s">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="O157" t="s">
-        <v>521</v>
+        <v>527</v>
       </c>
       <c r="P157" t="s">
         <v>25</v>
@@ -8160,7 +8201,7 @@
         <v>35</v>
       </c>
       <c r="R157" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="158" spans="13:18">
@@ -8168,10 +8209,10 @@
         <v>17</v>
       </c>
       <c r="N158" t="s">
-        <v>522</v>
+        <v>528</v>
       </c>
       <c r="O158" t="s">
-        <v>523</v>
+        <v>529</v>
       </c>
       <c r="P158" t="s">
         <v>25</v>
@@ -8180,7 +8221,7 @@
         <v>35</v>
       </c>
       <c r="R158" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="159" spans="13:18">
@@ -8188,10 +8229,10 @@
         <v>17</v>
       </c>
       <c r="N159" t="s">
-        <v>524</v>
+        <v>530</v>
       </c>
       <c r="O159" t="s">
-        <v>525</v>
+        <v>531</v>
       </c>
       <c r="P159" t="s">
         <v>25</v>
@@ -8200,7 +8241,7 @@
         <v>35</v>
       </c>
       <c r="R159" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="160" spans="13:18">
@@ -8208,10 +8249,10 @@
         <v>17</v>
       </c>
       <c r="N160" t="s">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="O160" t="s">
-        <v>527</v>
+        <v>533</v>
       </c>
       <c r="P160" t="s">
         <v>25</v>
@@ -8220,7 +8261,7 @@
         <v>35</v>
       </c>
       <c r="R160" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="161" spans="13:18">
@@ -8228,10 +8269,10 @@
         <v>17</v>
       </c>
       <c r="N161" t="s">
-        <v>528</v>
+        <v>534</v>
       </c>
       <c r="O161" t="s">
-        <v>529</v>
+        <v>535</v>
       </c>
       <c r="P161" t="s">
         <v>25</v>
@@ -8240,7 +8281,7 @@
         <v>35</v>
       </c>
       <c r="R161" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="162" spans="13:18">
@@ -8248,10 +8289,10 @@
         <v>17</v>
       </c>
       <c r="N162" t="s">
-        <v>530</v>
+        <v>536</v>
       </c>
       <c r="O162" t="s">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="P162" t="s">
         <v>25</v>
@@ -8260,7 +8301,7 @@
         <v>35</v>
       </c>
       <c r="R162" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="163" spans="13:18">
@@ -8268,10 +8309,10 @@
         <v>17</v>
       </c>
       <c r="N163" t="s">
-        <v>532</v>
+        <v>538</v>
       </c>
       <c r="O163" t="s">
-        <v>533</v>
+        <v>539</v>
       </c>
       <c r="P163" t="s">
         <v>25</v>
@@ -8280,7 +8321,7 @@
         <v>35</v>
       </c>
       <c r="R163" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="164" spans="13:18">
@@ -8288,10 +8329,10 @@
         <v>17</v>
       </c>
       <c r="N164" t="s">
-        <v>534</v>
+        <v>540</v>
       </c>
       <c r="O164" t="s">
-        <v>535</v>
+        <v>541</v>
       </c>
       <c r="P164" t="s">
         <v>25</v>
@@ -8300,7 +8341,7 @@
         <v>35</v>
       </c>
       <c r="R164" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="165" spans="13:18">
@@ -8308,10 +8349,10 @@
         <v>17</v>
       </c>
       <c r="N165" t="s">
-        <v>536</v>
+        <v>542</v>
       </c>
       <c r="O165" t="s">
-        <v>537</v>
+        <v>543</v>
       </c>
       <c r="P165" t="s">
         <v>25</v>
@@ -8320,7 +8361,7 @@
         <v>35</v>
       </c>
       <c r="R165" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="166" spans="13:18">
@@ -8328,10 +8369,10 @@
         <v>17</v>
       </c>
       <c r="N166" t="s">
-        <v>538</v>
+        <v>544</v>
       </c>
       <c r="O166" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="P166" t="s">
         <v>25</v>
@@ -8340,7 +8381,7 @@
         <v>35</v>
       </c>
       <c r="R166" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="167" spans="13:18">
@@ -8348,10 +8389,10 @@
         <v>17</v>
       </c>
       <c r="N167" t="s">
-        <v>540</v>
+        <v>546</v>
       </c>
       <c r="O167" t="s">
-        <v>541</v>
+        <v>547</v>
       </c>
       <c r="P167" t="s">
         <v>25</v>
@@ -8360,7 +8401,7 @@
         <v>35</v>
       </c>
       <c r="R167" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="168" spans="13:18">
@@ -8368,10 +8409,10 @@
         <v>17</v>
       </c>
       <c r="N168" t="s">
-        <v>542</v>
+        <v>548</v>
       </c>
       <c r="O168" t="s">
-        <v>543</v>
+        <v>549</v>
       </c>
       <c r="P168" t="s">
         <v>25</v>
@@ -8380,7 +8421,7 @@
         <v>35</v>
       </c>
       <c r="R168" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="169" spans="13:18">
@@ -8388,10 +8429,10 @@
         <v>17</v>
       </c>
       <c r="N169" t="s">
-        <v>544</v>
+        <v>550</v>
       </c>
       <c r="O169" t="s">
-        <v>545</v>
+        <v>551</v>
       </c>
       <c r="P169" t="s">
         <v>25</v>
@@ -8400,7 +8441,7 @@
         <v>35</v>
       </c>
       <c r="R169" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="170" spans="13:18">
@@ -8408,10 +8449,10 @@
         <v>17</v>
       </c>
       <c r="N170" t="s">
-        <v>546</v>
+        <v>552</v>
       </c>
       <c r="O170" t="s">
-        <v>547</v>
+        <v>553</v>
       </c>
       <c r="P170" t="s">
         <v>25</v>
@@ -8420,7 +8461,7 @@
         <v>35</v>
       </c>
       <c r="R170" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="171" spans="13:18">
@@ -8428,10 +8469,10 @@
         <v>17</v>
       </c>
       <c r="N171" t="s">
-        <v>548</v>
+        <v>554</v>
       </c>
       <c r="O171" t="s">
-        <v>549</v>
+        <v>555</v>
       </c>
       <c r="P171" t="s">
         <v>25</v>
@@ -8440,7 +8481,7 @@
         <v>35</v>
       </c>
       <c r="R171" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="172" spans="13:18">
@@ -8448,10 +8489,10 @@
         <v>17</v>
       </c>
       <c r="N172" t="s">
-        <v>550</v>
+        <v>556</v>
       </c>
       <c r="O172" t="s">
-        <v>551</v>
+        <v>557</v>
       </c>
       <c r="P172" t="s">
         <v>25</v>
@@ -8460,7 +8501,7 @@
         <v>35</v>
       </c>
       <c r="R172" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="173" spans="13:18">
@@ -8468,10 +8509,10 @@
         <v>17</v>
       </c>
       <c r="N173" t="s">
-        <v>552</v>
+        <v>558</v>
       </c>
       <c r="O173" t="s">
-        <v>553</v>
+        <v>559</v>
       </c>
       <c r="P173" t="s">
         <v>25</v>
@@ -8480,7 +8521,7 @@
         <v>35</v>
       </c>
       <c r="R173" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="174" spans="13:18">
@@ -8488,10 +8529,10 @@
         <v>17</v>
       </c>
       <c r="N174" t="s">
-        <v>554</v>
+        <v>560</v>
       </c>
       <c r="O174" t="s">
-        <v>555</v>
+        <v>561</v>
       </c>
       <c r="P174" t="s">
         <v>25</v>
@@ -8500,7 +8541,7 @@
         <v>35</v>
       </c>
       <c r="R174" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="175" spans="13:18">
@@ -8508,10 +8549,10 @@
         <v>17</v>
       </c>
       <c r="N175" t="s">
-        <v>556</v>
+        <v>562</v>
       </c>
       <c r="O175" t="s">
-        <v>557</v>
+        <v>563</v>
       </c>
       <c r="P175" t="s">
         <v>25</v>
@@ -8520,7 +8561,7 @@
         <v>35</v>
       </c>
       <c r="R175" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="176" spans="13:18">
@@ -8528,10 +8569,10 @@
         <v>17</v>
       </c>
       <c r="N176" t="s">
-        <v>558</v>
+        <v>564</v>
       </c>
       <c r="O176" t="s">
-        <v>559</v>
+        <v>565</v>
       </c>
       <c r="P176" t="s">
         <v>25</v>
@@ -8540,7 +8581,7 @@
         <v>35</v>
       </c>
       <c r="R176" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="177" spans="13:18">
@@ -8548,10 +8589,10 @@
         <v>17</v>
       </c>
       <c r="N177" t="s">
-        <v>560</v>
+        <v>566</v>
       </c>
       <c r="O177" t="s">
-        <v>561</v>
+        <v>567</v>
       </c>
       <c r="P177" t="s">
         <v>25</v>
@@ -8560,7 +8601,7 @@
         <v>35</v>
       </c>
       <c r="R177" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="178" spans="13:18">
@@ -8568,10 +8609,10 @@
         <v>17</v>
       </c>
       <c r="N178" t="s">
-        <v>562</v>
+        <v>568</v>
       </c>
       <c r="O178" t="s">
-        <v>563</v>
+        <v>569</v>
       </c>
       <c r="P178" t="s">
         <v>25</v>
@@ -8580,7 +8621,7 @@
         <v>35</v>
       </c>
       <c r="R178" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="179" spans="13:18">
@@ -8588,10 +8629,10 @@
         <v>17</v>
       </c>
       <c r="N179" t="s">
-        <v>564</v>
+        <v>570</v>
       </c>
       <c r="O179" t="s">
-        <v>565</v>
+        <v>571</v>
       </c>
       <c r="P179" t="s">
         <v>25</v>
@@ -8600,7 +8641,7 @@
         <v>35</v>
       </c>
       <c r="R179" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="180" spans="13:18">
@@ -8608,10 +8649,10 @@
         <v>17</v>
       </c>
       <c r="N180" t="s">
-        <v>566</v>
+        <v>572</v>
       </c>
       <c r="O180" t="s">
-        <v>567</v>
+        <v>573</v>
       </c>
       <c r="P180" t="s">
         <v>25</v>
@@ -8620,7 +8661,7 @@
         <v>35</v>
       </c>
       <c r="R180" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="181" spans="13:18">
@@ -8628,10 +8669,10 @@
         <v>17</v>
       </c>
       <c r="N181" t="s">
-        <v>568</v>
+        <v>574</v>
       </c>
       <c r="O181" t="s">
-        <v>569</v>
+        <v>575</v>
       </c>
       <c r="P181" t="s">
         <v>25</v>
@@ -8640,7 +8681,7 @@
         <v>35</v>
       </c>
       <c r="R181" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="182" spans="13:18">
@@ -8648,10 +8689,10 @@
         <v>17</v>
       </c>
       <c r="N182" t="s">
-        <v>570</v>
+        <v>576</v>
       </c>
       <c r="O182" t="s">
-        <v>571</v>
+        <v>577</v>
       </c>
       <c r="P182" t="s">
         <v>25</v>
@@ -8660,7 +8701,7 @@
         <v>35</v>
       </c>
       <c r="R182" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="183" spans="13:18">
@@ -8668,10 +8709,10 @@
         <v>17</v>
       </c>
       <c r="N183" t="s">
-        <v>572</v>
+        <v>578</v>
       </c>
       <c r="O183" t="s">
-        <v>573</v>
+        <v>579</v>
       </c>
       <c r="P183" t="s">
         <v>25</v>
@@ -8680,7 +8721,7 @@
         <v>35</v>
       </c>
       <c r="R183" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="184" spans="13:18">
@@ -8688,10 +8729,10 @@
         <v>17</v>
       </c>
       <c r="N184" t="s">
-        <v>574</v>
+        <v>580</v>
       </c>
       <c r="O184" t="s">
-        <v>575</v>
+        <v>581</v>
       </c>
       <c r="P184" t="s">
         <v>25</v>
@@ -8700,7 +8741,7 @@
         <v>35</v>
       </c>
       <c r="R184" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="185" spans="13:18">
@@ -8708,10 +8749,10 @@
         <v>17</v>
       </c>
       <c r="N185" t="s">
-        <v>576</v>
+        <v>582</v>
       </c>
       <c r="O185" t="s">
-        <v>577</v>
+        <v>583</v>
       </c>
       <c r="P185" t="s">
         <v>25</v>
@@ -8720,7 +8761,7 @@
         <v>35</v>
       </c>
       <c r="R185" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="186" spans="13:18">
@@ -8728,10 +8769,10 @@
         <v>17</v>
       </c>
       <c r="N186" t="s">
-        <v>578</v>
+        <v>584</v>
       </c>
       <c r="O186" t="s">
-        <v>579</v>
+        <v>585</v>
       </c>
       <c r="P186" t="s">
         <v>25</v>
@@ -8740,7 +8781,7 @@
         <v>35</v>
       </c>
       <c r="R186" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="187" spans="13:18">
@@ -8748,10 +8789,10 @@
         <v>17</v>
       </c>
       <c r="N187" t="s">
-        <v>580</v>
+        <v>586</v>
       </c>
       <c r="O187" t="s">
-        <v>581</v>
+        <v>587</v>
       </c>
       <c r="P187" t="s">
         <v>25</v>
@@ -8760,7 +8801,7 @@
         <v>35</v>
       </c>
       <c r="R187" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="188" spans="13:18">
@@ -8768,10 +8809,10 @@
         <v>17</v>
       </c>
       <c r="N188" t="s">
-        <v>582</v>
+        <v>588</v>
       </c>
       <c r="O188" t="s">
-        <v>583</v>
+        <v>589</v>
       </c>
       <c r="P188" t="s">
         <v>25</v>
@@ -8780,7 +8821,7 @@
         <v>35</v>
       </c>
       <c r="R188" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="189" spans="13:18">
@@ -8788,10 +8829,10 @@
         <v>17</v>
       </c>
       <c r="N189" t="s">
-        <v>584</v>
+        <v>590</v>
       </c>
       <c r="O189" t="s">
-        <v>585</v>
+        <v>591</v>
       </c>
       <c r="P189" t="s">
         <v>25</v>
@@ -8800,7 +8841,7 @@
         <v>35</v>
       </c>
       <c r="R189" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="190" spans="13:18">
@@ -8808,10 +8849,10 @@
         <v>17</v>
       </c>
       <c r="N190" t="s">
-        <v>586</v>
+        <v>592</v>
       </c>
       <c r="O190" t="s">
-        <v>587</v>
+        <v>593</v>
       </c>
       <c r="P190" t="s">
         <v>25</v>
@@ -8820,7 +8861,7 @@
         <v>35</v>
       </c>
       <c r="R190" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="191" spans="13:18">
@@ -8828,10 +8869,10 @@
         <v>17</v>
       </c>
       <c r="N191" t="s">
-        <v>588</v>
+        <v>594</v>
       </c>
       <c r="O191" t="s">
-        <v>589</v>
+        <v>595</v>
       </c>
       <c r="P191" t="s">
         <v>25</v>
@@ -8840,7 +8881,7 @@
         <v>35</v>
       </c>
       <c r="R191" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="192" spans="13:18">
@@ -8848,10 +8889,10 @@
         <v>17</v>
       </c>
       <c r="N192" t="s">
-        <v>590</v>
+        <v>596</v>
       </c>
       <c r="O192" t="s">
-        <v>591</v>
+        <v>597</v>
       </c>
       <c r="P192" t="s">
         <v>25</v>
@@ -8860,7 +8901,7 @@
         <v>35</v>
       </c>
       <c r="R192" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="193" spans="13:18">
@@ -8868,10 +8909,10 @@
         <v>17</v>
       </c>
       <c r="N193" t="s">
-        <v>592</v>
+        <v>598</v>
       </c>
       <c r="O193" t="s">
-        <v>593</v>
+        <v>599</v>
       </c>
       <c r="P193" t="s">
         <v>25</v>
@@ -8880,7 +8921,7 @@
         <v>35</v>
       </c>
       <c r="R193" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="194" spans="13:18">
@@ -8888,10 +8929,10 @@
         <v>17</v>
       </c>
       <c r="N194" t="s">
-        <v>594</v>
+        <v>600</v>
       </c>
       <c r="O194" t="s">
-        <v>595</v>
+        <v>601</v>
       </c>
       <c r="P194" t="s">
         <v>25</v>
@@ -8900,7 +8941,7 @@
         <v>35</v>
       </c>
       <c r="R194" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="195" spans="13:18">
@@ -8908,10 +8949,10 @@
         <v>17</v>
       </c>
       <c r="N195" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="O195" t="s">
-        <v>597</v>
+        <v>603</v>
       </c>
       <c r="P195" t="s">
         <v>25</v>
@@ -8920,7 +8961,7 @@
         <v>35</v>
       </c>
       <c r="R195" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="196" spans="13:18">
@@ -8928,10 +8969,10 @@
         <v>17</v>
       </c>
       <c r="N196" t="s">
-        <v>598</v>
+        <v>604</v>
       </c>
       <c r="O196" t="s">
-        <v>599</v>
+        <v>605</v>
       </c>
       <c r="P196" t="s">
         <v>25</v>
@@ -8940,7 +8981,7 @@
         <v>35</v>
       </c>
       <c r="R196" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="197" spans="13:18">
@@ -8948,10 +8989,10 @@
         <v>17</v>
       </c>
       <c r="N197" t="s">
-        <v>600</v>
+        <v>606</v>
       </c>
       <c r="O197" t="s">
-        <v>601</v>
+        <v>607</v>
       </c>
       <c r="P197" t="s">
         <v>25</v>
@@ -8960,7 +9001,7 @@
         <v>35</v>
       </c>
       <c r="R197" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="198" spans="13:18">
@@ -8968,10 +9009,10 @@
         <v>17</v>
       </c>
       <c r="N198" t="s">
-        <v>602</v>
+        <v>608</v>
       </c>
       <c r="O198" t="s">
-        <v>603</v>
+        <v>609</v>
       </c>
       <c r="P198" t="s">
         <v>25</v>
@@ -8980,7 +9021,7 @@
         <v>35</v>
       </c>
       <c r="R198" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="199" spans="13:18">
@@ -8988,10 +9029,10 @@
         <v>17</v>
       </c>
       <c r="N199" t="s">
-        <v>604</v>
+        <v>610</v>
       </c>
       <c r="O199" t="s">
-        <v>605</v>
+        <v>611</v>
       </c>
       <c r="P199" t="s">
         <v>25</v>
@@ -9000,7 +9041,7 @@
         <v>35</v>
       </c>
       <c r="R199" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="200" spans="13:18">
@@ -9008,10 +9049,10 @@
         <v>17</v>
       </c>
       <c r="N200" t="s">
-        <v>606</v>
+        <v>612</v>
       </c>
       <c r="O200" t="s">
-        <v>607</v>
+        <v>613</v>
       </c>
       <c r="P200" t="s">
         <v>25</v>
@@ -9020,7 +9061,7 @@
         <v>35</v>
       </c>
       <c r="R200" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="201" spans="13:18">
@@ -9028,10 +9069,10 @@
         <v>17</v>
       </c>
       <c r="N201" t="s">
-        <v>608</v>
+        <v>614</v>
       </c>
       <c r="O201" t="s">
-        <v>609</v>
+        <v>615</v>
       </c>
       <c r="P201" t="s">
         <v>25</v>
@@ -9040,7 +9081,7 @@
         <v>35</v>
       </c>
       <c r="R201" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="202" spans="13:18">
@@ -9048,10 +9089,10 @@
         <v>17</v>
       </c>
       <c r="N202" t="s">
-        <v>610</v>
+        <v>616</v>
       </c>
       <c r="O202" t="s">
-        <v>611</v>
+        <v>617</v>
       </c>
       <c r="P202" t="s">
         <v>25</v>
@@ -9060,7 +9101,7 @@
         <v>35</v>
       </c>
       <c r="R202" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="203" spans="13:18">
@@ -9068,10 +9109,10 @@
         <v>17</v>
       </c>
       <c r="N203" t="s">
-        <v>612</v>
+        <v>618</v>
       </c>
       <c r="O203" t="s">
-        <v>613</v>
+        <v>619</v>
       </c>
       <c r="P203" t="s">
         <v>25</v>
@@ -9080,7 +9121,7 @@
         <v>35</v>
       </c>
       <c r="R203" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="204" spans="13:18">
@@ -9088,10 +9129,10 @@
         <v>17</v>
       </c>
       <c r="N204" t="s">
-        <v>614</v>
+        <v>620</v>
       </c>
       <c r="O204" t="s">
-        <v>615</v>
+        <v>621</v>
       </c>
       <c r="P204" t="s">
         <v>25</v>
@@ -9100,7 +9141,7 @@
         <v>35</v>
       </c>
       <c r="R204" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="205" spans="13:18">
@@ -9108,10 +9149,10 @@
         <v>17</v>
       </c>
       <c r="N205" t="s">
-        <v>616</v>
+        <v>622</v>
       </c>
       <c r="O205" t="s">
-        <v>617</v>
+        <v>623</v>
       </c>
       <c r="P205" t="s">
         <v>25</v>
@@ -9120,7 +9161,7 @@
         <v>35</v>
       </c>
       <c r="R205" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="206" spans="13:18">
@@ -9128,10 +9169,10 @@
         <v>17</v>
       </c>
       <c r="N206" t="s">
-        <v>618</v>
+        <v>624</v>
       </c>
       <c r="O206" t="s">
-        <v>619</v>
+        <v>625</v>
       </c>
       <c r="P206" t="s">
         <v>25</v>
@@ -9140,7 +9181,7 @@
         <v>35</v>
       </c>
       <c r="R206" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="207" spans="13:18">
@@ -9148,10 +9189,10 @@
         <v>17</v>
       </c>
       <c r="N207" t="s">
-        <v>620</v>
+        <v>626</v>
       </c>
       <c r="O207" t="s">
-        <v>621</v>
+        <v>627</v>
       </c>
       <c r="P207" t="s">
         <v>25</v>
@@ -9160,7 +9201,7 @@
         <v>35</v>
       </c>
       <c r="R207" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="208" spans="13:18">
@@ -9168,10 +9209,10 @@
         <v>17</v>
       </c>
       <c r="N208" t="s">
-        <v>622</v>
+        <v>628</v>
       </c>
       <c r="O208" t="s">
-        <v>623</v>
+        <v>629</v>
       </c>
       <c r="P208" t="s">
         <v>25</v>
@@ -9180,7 +9221,7 @@
         <v>35</v>
       </c>
       <c r="R208" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="209" spans="13:18">
@@ -9188,10 +9229,10 @@
         <v>17</v>
       </c>
       <c r="N209" t="s">
-        <v>624</v>
+        <v>630</v>
       </c>
       <c r="O209" t="s">
-        <v>625</v>
+        <v>631</v>
       </c>
       <c r="P209" t="s">
         <v>25</v>
@@ -9200,7 +9241,7 @@
         <v>35</v>
       </c>
       <c r="R209" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="210" spans="13:18">
@@ -9208,10 +9249,10 @@
         <v>17</v>
       </c>
       <c r="N210" t="s">
-        <v>626</v>
+        <v>632</v>
       </c>
       <c r="O210" t="s">
-        <v>627</v>
+        <v>633</v>
       </c>
       <c r="P210" t="s">
         <v>25</v>
@@ -9220,7 +9261,7 @@
         <v>35</v>
       </c>
       <c r="R210" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="211" spans="13:18">
@@ -9228,10 +9269,10 @@
         <v>17</v>
       </c>
       <c r="N211" t="s">
-        <v>628</v>
+        <v>634</v>
       </c>
       <c r="O211" t="s">
-        <v>629</v>
+        <v>635</v>
       </c>
       <c r="P211" t="s">
         <v>25</v>
@@ -9240,7 +9281,7 @@
         <v>35</v>
       </c>
       <c r="R211" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="212" spans="13:18">
@@ -9248,10 +9289,10 @@
         <v>17</v>
       </c>
       <c r="N212" t="s">
-        <v>630</v>
+        <v>636</v>
       </c>
       <c r="O212" t="s">
-        <v>631</v>
+        <v>637</v>
       </c>
       <c r="P212" t="s">
         <v>25</v>
@@ -9260,7 +9301,7 @@
         <v>35</v>
       </c>
       <c r="R212" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="213" spans="13:18">
@@ -9268,10 +9309,10 @@
         <v>17</v>
       </c>
       <c r="N213" t="s">
-        <v>632</v>
+        <v>638</v>
       </c>
       <c r="O213" t="s">
-        <v>633</v>
+        <v>639</v>
       </c>
       <c r="P213" t="s">
         <v>25</v>
@@ -9280,7 +9321,7 @@
         <v>35</v>
       </c>
       <c r="R213" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="214" spans="13:18">
@@ -9288,10 +9329,10 @@
         <v>17</v>
       </c>
       <c r="N214" t="s">
-        <v>634</v>
+        <v>640</v>
       </c>
       <c r="O214" t="s">
-        <v>635</v>
+        <v>641</v>
       </c>
       <c r="P214" t="s">
         <v>25</v>
@@ -9300,7 +9341,7 @@
         <v>35</v>
       </c>
       <c r="R214" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="215" spans="13:18">
@@ -9308,10 +9349,10 @@
         <v>17</v>
       </c>
       <c r="N215" t="s">
-        <v>636</v>
+        <v>642</v>
       </c>
       <c r="O215" t="s">
-        <v>637</v>
+        <v>643</v>
       </c>
       <c r="P215" t="s">
         <v>25</v>
@@ -9320,7 +9361,7 @@
         <v>35</v>
       </c>
       <c r="R215" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="216" spans="13:18">
@@ -9328,10 +9369,10 @@
         <v>17</v>
       </c>
       <c r="N216" t="s">
-        <v>638</v>
+        <v>644</v>
       </c>
       <c r="O216" t="s">
-        <v>639</v>
+        <v>645</v>
       </c>
       <c r="P216" t="s">
         <v>25</v>
@@ -9340,7 +9381,7 @@
         <v>35</v>
       </c>
       <c r="R216" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="217" spans="13:18">
@@ -9348,10 +9389,10 @@
         <v>17</v>
       </c>
       <c r="N217" t="s">
-        <v>640</v>
+        <v>646</v>
       </c>
       <c r="O217" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="P217" t="s">
         <v>25</v>
@@ -9360,7 +9401,7 @@
         <v>35</v>
       </c>
       <c r="R217" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="218" spans="13:18">
@@ -9368,10 +9409,10 @@
         <v>17</v>
       </c>
       <c r="N218" t="s">
-        <v>642</v>
+        <v>648</v>
       </c>
       <c r="O218" t="s">
-        <v>643</v>
+        <v>649</v>
       </c>
       <c r="P218" t="s">
         <v>25</v>
@@ -9380,7 +9421,7 @@
         <v>35</v>
       </c>
       <c r="R218" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="219" spans="13:18">
@@ -9388,10 +9429,10 @@
         <v>17</v>
       </c>
       <c r="N219" t="s">
-        <v>644</v>
+        <v>650</v>
       </c>
       <c r="O219" t="s">
-        <v>645</v>
+        <v>651</v>
       </c>
       <c r="P219" t="s">
         <v>25</v>
@@ -9400,7 +9441,7 @@
         <v>35</v>
       </c>
       <c r="R219" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="220" spans="13:18">
@@ -9408,10 +9449,10 @@
         <v>17</v>
       </c>
       <c r="N220" t="s">
-        <v>646</v>
+        <v>652</v>
       </c>
       <c r="O220" t="s">
-        <v>647</v>
+        <v>653</v>
       </c>
       <c r="P220" t="s">
         <v>25</v>
@@ -9420,7 +9461,7 @@
         <v>35</v>
       </c>
       <c r="R220" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="221" spans="13:18">
@@ -9428,10 +9469,10 @@
         <v>17</v>
       </c>
       <c r="N221" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="O221" t="s">
-        <v>649</v>
+        <v>655</v>
       </c>
       <c r="P221" t="s">
         <v>25</v>
@@ -9440,7 +9481,7 @@
         <v>35</v>
       </c>
       <c r="R221" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="222" spans="13:18">
@@ -9448,10 +9489,10 @@
         <v>17</v>
       </c>
       <c r="N222" t="s">
-        <v>650</v>
+        <v>656</v>
       </c>
       <c r="O222" t="s">
-        <v>651</v>
+        <v>657</v>
       </c>
       <c r="P222" t="s">
         <v>25</v>
@@ -9460,7 +9501,7 @@
         <v>35</v>
       </c>
       <c r="R222" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="223" spans="13:18">
@@ -9468,10 +9509,10 @@
         <v>17</v>
       </c>
       <c r="N223" t="s">
-        <v>652</v>
+        <v>658</v>
       </c>
       <c r="O223" t="s">
-        <v>653</v>
+        <v>659</v>
       </c>
       <c r="P223" t="s">
         <v>25</v>
@@ -9480,7 +9521,7 @@
         <v>35</v>
       </c>
       <c r="R223" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="224" spans="13:18">
@@ -9488,10 +9529,10 @@
         <v>17</v>
       </c>
       <c r="N224" t="s">
-        <v>654</v>
+        <v>660</v>
       </c>
       <c r="O224" t="s">
-        <v>655</v>
+        <v>661</v>
       </c>
       <c r="P224" t="s">
         <v>25</v>
@@ -9500,7 +9541,7 @@
         <v>35</v>
       </c>
       <c r="R224" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="225" spans="13:18">
@@ -9508,10 +9549,10 @@
         <v>17</v>
       </c>
       <c r="N225" t="s">
-        <v>656</v>
+        <v>662</v>
       </c>
       <c r="O225" t="s">
-        <v>657</v>
+        <v>663</v>
       </c>
       <c r="P225" t="s">
         <v>25</v>
@@ -9520,7 +9561,7 @@
         <v>35</v>
       </c>
       <c r="R225" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="226" spans="13:18">
@@ -9528,10 +9569,10 @@
         <v>17</v>
       </c>
       <c r="N226" t="s">
-        <v>658</v>
+        <v>664</v>
       </c>
       <c r="O226" t="s">
-        <v>659</v>
+        <v>665</v>
       </c>
       <c r="P226" t="s">
         <v>25</v>
@@ -9540,7 +9581,7 @@
         <v>35</v>
       </c>
       <c r="R226" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="227" spans="13:18">
@@ -9548,10 +9589,10 @@
         <v>17</v>
       </c>
       <c r="N227" t="s">
-        <v>660</v>
+        <v>666</v>
       </c>
       <c r="O227" t="s">
-        <v>661</v>
+        <v>667</v>
       </c>
       <c r="P227" t="s">
         <v>25</v>
@@ -9560,7 +9601,7 @@
         <v>35</v>
       </c>
       <c r="R227" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="228" spans="13:18">
@@ -9568,10 +9609,10 @@
         <v>17</v>
       </c>
       <c r="N228" t="s">
-        <v>662</v>
+        <v>668</v>
       </c>
       <c r="O228" t="s">
-        <v>663</v>
+        <v>669</v>
       </c>
       <c r="P228" t="s">
         <v>25</v>
@@ -9580,7 +9621,7 @@
         <v>35</v>
       </c>
       <c r="R228" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="229" spans="13:18">
@@ -9588,10 +9629,10 @@
         <v>17</v>
       </c>
       <c r="N229" t="s">
-        <v>664</v>
+        <v>670</v>
       </c>
       <c r="O229" t="s">
-        <v>665</v>
+        <v>671</v>
       </c>
       <c r="P229" t="s">
         <v>25</v>
@@ -9600,7 +9641,7 @@
         <v>35</v>
       </c>
       <c r="R229" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="230" spans="13:18">
@@ -9608,10 +9649,10 @@
         <v>17</v>
       </c>
       <c r="N230" t="s">
-        <v>666</v>
+        <v>672</v>
       </c>
       <c r="O230" t="s">
-        <v>667</v>
+        <v>673</v>
       </c>
       <c r="P230" t="s">
         <v>25</v>
@@ -9620,7 +9661,7 @@
         <v>35</v>
       </c>
       <c r="R230" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="231" spans="13:18">
@@ -9628,10 +9669,10 @@
         <v>17</v>
       </c>
       <c r="N231" t="s">
-        <v>668</v>
+        <v>674</v>
       </c>
       <c r="O231" t="s">
-        <v>669</v>
+        <v>675</v>
       </c>
       <c r="P231" t="s">
         <v>25</v>
@@ -9640,7 +9681,7 @@
         <v>35</v>
       </c>
       <c r="R231" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="232" spans="13:18">
@@ -9648,10 +9689,10 @@
         <v>17</v>
       </c>
       <c r="N232" t="s">
-        <v>670</v>
+        <v>676</v>
       </c>
       <c r="O232" t="s">
-        <v>671</v>
+        <v>677</v>
       </c>
       <c r="P232" t="s">
         <v>25</v>
@@ -9660,7 +9701,7 @@
         <v>35</v>
       </c>
       <c r="R232" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="233" spans="13:18">
@@ -9668,10 +9709,10 @@
         <v>17</v>
       </c>
       <c r="N233" t="s">
-        <v>672</v>
+        <v>678</v>
       </c>
       <c r="O233" t="s">
-        <v>673</v>
+        <v>679</v>
       </c>
       <c r="P233" t="s">
         <v>25</v>
@@ -9680,7 +9721,7 @@
         <v>35</v>
       </c>
       <c r="R233" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="234" spans="13:18">
@@ -9688,10 +9729,10 @@
         <v>17</v>
       </c>
       <c r="N234" t="s">
-        <v>674</v>
+        <v>680</v>
       </c>
       <c r="O234" t="s">
-        <v>675</v>
+        <v>681</v>
       </c>
       <c r="P234" t="s">
         <v>25</v>
@@ -9700,7 +9741,7 @@
         <v>35</v>
       </c>
       <c r="R234" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="235" spans="13:18">
@@ -9708,10 +9749,10 @@
         <v>17</v>
       </c>
       <c r="N235" t="s">
-        <v>676</v>
+        <v>682</v>
       </c>
       <c r="O235" t="s">
-        <v>677</v>
+        <v>683</v>
       </c>
       <c r="P235" t="s">
         <v>25</v>
@@ -9720,7 +9761,7 @@
         <v>35</v>
       </c>
       <c r="R235" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="236" spans="13:18">
@@ -9728,10 +9769,10 @@
         <v>17</v>
       </c>
       <c r="N236" t="s">
-        <v>678</v>
+        <v>684</v>
       </c>
       <c r="O236" t="s">
-        <v>679</v>
+        <v>685</v>
       </c>
       <c r="P236" t="s">
         <v>25</v>
@@ -9740,7 +9781,7 @@
         <v>35</v>
       </c>
       <c r="R236" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="237" spans="13:18">
@@ -9748,10 +9789,10 @@
         <v>17</v>
       </c>
       <c r="N237" t="s">
-        <v>680</v>
+        <v>686</v>
       </c>
       <c r="O237" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="P237" t="s">
         <v>25</v>
@@ -9760,7 +9801,7 @@
         <v>35</v>
       </c>
       <c r="R237" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="238" spans="13:18">
@@ -9768,10 +9809,10 @@
         <v>17</v>
       </c>
       <c r="N238" t="s">
-        <v>682</v>
+        <v>688</v>
       </c>
       <c r="O238" t="s">
-        <v>683</v>
+        <v>689</v>
       </c>
       <c r="P238" t="s">
         <v>25</v>
@@ -9780,7 +9821,7 @@
         <v>35</v>
       </c>
       <c r="R238" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="239" spans="13:18">
@@ -9788,10 +9829,10 @@
         <v>17</v>
       </c>
       <c r="N239" t="s">
-        <v>684</v>
+        <v>690</v>
       </c>
       <c r="O239" t="s">
-        <v>685</v>
+        <v>691</v>
       </c>
       <c r="P239" t="s">
         <v>25</v>
@@ -9800,7 +9841,7 @@
         <v>35</v>
       </c>
       <c r="R239" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="240" spans="13:18">
@@ -9808,10 +9849,10 @@
         <v>17</v>
       </c>
       <c r="N240" t="s">
-        <v>686</v>
+        <v>692</v>
       </c>
       <c r="O240" t="s">
-        <v>687</v>
+        <v>693</v>
       </c>
       <c r="P240" t="s">
         <v>25</v>
@@ -9820,7 +9861,7 @@
         <v>35</v>
       </c>
       <c r="R240" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="241" spans="13:18">
@@ -9828,10 +9869,10 @@
         <v>17</v>
       </c>
       <c r="N241" t="s">
-        <v>688</v>
+        <v>694</v>
       </c>
       <c r="O241" t="s">
-        <v>689</v>
+        <v>695</v>
       </c>
       <c r="P241" t="s">
         <v>25</v>
@@ -9840,7 +9881,7 @@
         <v>35</v>
       </c>
       <c r="R241" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="242" spans="13:18">
@@ -9848,10 +9889,10 @@
         <v>17</v>
       </c>
       <c r="N242" t="s">
-        <v>690</v>
+        <v>696</v>
       </c>
       <c r="O242" t="s">
-        <v>691</v>
+        <v>697</v>
       </c>
       <c r="P242" t="s">
         <v>25</v>
@@ -9860,7 +9901,7 @@
         <v>35</v>
       </c>
       <c r="R242" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="243" spans="13:18">
@@ -9868,10 +9909,10 @@
         <v>17</v>
       </c>
       <c r="N243" t="s">
-        <v>692</v>
+        <v>698</v>
       </c>
       <c r="O243" t="s">
-        <v>693</v>
+        <v>699</v>
       </c>
       <c r="P243" t="s">
         <v>25</v>
@@ -9880,7 +9921,7 @@
         <v>35</v>
       </c>
       <c r="R243" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="244" spans="13:18">
@@ -9888,10 +9929,10 @@
         <v>17</v>
       </c>
       <c r="N244" t="s">
-        <v>694</v>
+        <v>700</v>
       </c>
       <c r="O244" t="s">
-        <v>695</v>
+        <v>701</v>
       </c>
       <c r="P244" t="s">
         <v>25</v>
@@ -9900,7 +9941,7 @@
         <v>35</v>
       </c>
       <c r="R244" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="245" spans="13:18">
@@ -9908,10 +9949,10 @@
         <v>17</v>
       </c>
       <c r="N245" t="s">
-        <v>696</v>
+        <v>702</v>
       </c>
       <c r="O245" t="s">
-        <v>697</v>
+        <v>703</v>
       </c>
       <c r="P245" t="s">
         <v>25</v>
@@ -9920,7 +9961,7 @@
         <v>35</v>
       </c>
       <c r="R245" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="246" spans="13:18">
@@ -9928,10 +9969,10 @@
         <v>17</v>
       </c>
       <c r="N246" t="s">
-        <v>698</v>
+        <v>704</v>
       </c>
       <c r="O246" t="s">
-        <v>699</v>
+        <v>705</v>
       </c>
       <c r="P246" t="s">
         <v>25</v>
@@ -9940,7 +9981,7 @@
         <v>35</v>
       </c>
       <c r="R246" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="247" spans="13:18">
@@ -9948,10 +9989,10 @@
         <v>17</v>
       </c>
       <c r="N247" t="s">
-        <v>700</v>
+        <v>706</v>
       </c>
       <c r="O247" t="s">
-        <v>701</v>
+        <v>707</v>
       </c>
       <c r="P247" t="s">
         <v>25</v>
@@ -9960,7 +10001,7 @@
         <v>35</v>
       </c>
       <c r="R247" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="248" spans="13:18">
@@ -9968,10 +10009,10 @@
         <v>17</v>
       </c>
       <c r="N248" t="s">
-        <v>702</v>
+        <v>708</v>
       </c>
       <c r="O248" t="s">
-        <v>703</v>
+        <v>709</v>
       </c>
       <c r="P248" t="s">
         <v>25</v>
@@ -9980,7 +10021,7 @@
         <v>35</v>
       </c>
       <c r="R248" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="249" spans="13:18">
@@ -9988,10 +10029,10 @@
         <v>17</v>
       </c>
       <c r="N249" t="s">
-        <v>704</v>
+        <v>710</v>
       </c>
       <c r="O249" t="s">
-        <v>705</v>
+        <v>711</v>
       </c>
       <c r="P249" t="s">
         <v>25</v>
@@ -10000,7 +10041,7 @@
         <v>35</v>
       </c>
       <c r="R249" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="250" spans="13:18">
@@ -10008,10 +10049,10 @@
         <v>17</v>
       </c>
       <c r="N250" t="s">
-        <v>706</v>
+        <v>712</v>
       </c>
       <c r="O250" t="s">
-        <v>707</v>
+        <v>713</v>
       </c>
       <c r="P250" t="s">
         <v>25</v>
@@ -10020,7 +10061,7 @@
         <v>35</v>
       </c>
       <c r="R250" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="251" spans="13:18">
@@ -10028,10 +10069,10 @@
         <v>17</v>
       </c>
       <c r="N251" t="s">
-        <v>708</v>
+        <v>714</v>
       </c>
       <c r="O251" t="s">
-        <v>709</v>
+        <v>715</v>
       </c>
       <c r="P251" t="s">
         <v>25</v>
@@ -10040,7 +10081,7 @@
         <v>35</v>
       </c>
       <c r="R251" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="252" spans="13:18">
@@ -10048,10 +10089,10 @@
         <v>17</v>
       </c>
       <c r="N252" t="s">
-        <v>710</v>
+        <v>716</v>
       </c>
       <c r="O252" t="s">
-        <v>711</v>
+        <v>717</v>
       </c>
       <c r="P252" t="s">
         <v>25</v>
@@ -10060,7 +10101,7 @@
         <v>35</v>
       </c>
       <c r="R252" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="253" spans="13:18">
@@ -10068,10 +10109,10 @@
         <v>17</v>
       </c>
       <c r="N253" t="s">
-        <v>712</v>
+        <v>718</v>
       </c>
       <c r="O253" t="s">
-        <v>713</v>
+        <v>719</v>
       </c>
       <c r="P253" t="s">
         <v>25</v>
@@ -10080,7 +10121,7 @@
         <v>35</v>
       </c>
       <c r="R253" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="254" spans="13:18">
@@ -10088,10 +10129,10 @@
         <v>17</v>
       </c>
       <c r="N254" t="s">
-        <v>714</v>
+        <v>720</v>
       </c>
       <c r="O254" t="s">
-        <v>715</v>
+        <v>721</v>
       </c>
       <c r="P254" t="s">
         <v>25</v>
@@ -10100,7 +10141,7 @@
         <v>35</v>
       </c>
       <c r="R254" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="255" spans="13:18">
@@ -10108,10 +10149,10 @@
         <v>17</v>
       </c>
       <c r="N255" t="s">
-        <v>716</v>
+        <v>722</v>
       </c>
       <c r="O255" t="s">
-        <v>717</v>
+        <v>723</v>
       </c>
       <c r="P255" t="s">
         <v>25</v>
@@ -10120,7 +10161,7 @@
         <v>35</v>
       </c>
       <c r="R255" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="256" spans="13:18">
@@ -10128,10 +10169,10 @@
         <v>17</v>
       </c>
       <c r="N256" t="s">
-        <v>718</v>
+        <v>724</v>
       </c>
       <c r="O256" t="s">
-        <v>719</v>
+        <v>725</v>
       </c>
       <c r="P256" t="s">
         <v>25</v>
@@ -10140,7 +10181,7 @@
         <v>35</v>
       </c>
       <c r="R256" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="257" spans="13:18">
@@ -10148,10 +10189,10 @@
         <v>17</v>
       </c>
       <c r="N257" t="s">
-        <v>720</v>
+        <v>726</v>
       </c>
       <c r="O257" t="s">
-        <v>721</v>
+        <v>727</v>
       </c>
       <c r="P257" t="s">
         <v>25</v>
@@ -10160,7 +10201,7 @@
         <v>35</v>
       </c>
       <c r="R257" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="258" spans="13:18">
@@ -10168,10 +10209,10 @@
         <v>17</v>
       </c>
       <c r="N258" t="s">
-        <v>722</v>
+        <v>728</v>
       </c>
       <c r="O258" t="s">
-        <v>723</v>
+        <v>729</v>
       </c>
       <c r="P258" t="s">
         <v>25</v>
@@ -10180,7 +10221,7 @@
         <v>35</v>
       </c>
       <c r="R258" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="259" spans="13:18">
@@ -10188,10 +10229,10 @@
         <v>17</v>
       </c>
       <c r="N259" t="s">
-        <v>724</v>
+        <v>730</v>
       </c>
       <c r="O259" t="s">
-        <v>725</v>
+        <v>731</v>
       </c>
       <c r="P259" t="s">
         <v>25</v>
@@ -10200,7 +10241,7 @@
         <v>35</v>
       </c>
       <c r="R259" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="260" spans="13:18">
@@ -10208,10 +10249,10 @@
         <v>17</v>
       </c>
       <c r="N260" t="s">
-        <v>726</v>
+        <v>732</v>
       </c>
       <c r="O260" t="s">
-        <v>727</v>
+        <v>733</v>
       </c>
       <c r="P260" t="s">
         <v>25</v>
@@ -10220,7 +10261,7 @@
         <v>35</v>
       </c>
       <c r="R260" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="261" spans="13:18">
@@ -10228,10 +10269,10 @@
         <v>17</v>
       </c>
       <c r="N261" t="s">
-        <v>728</v>
+        <v>734</v>
       </c>
       <c r="O261" t="s">
-        <v>729</v>
+        <v>735</v>
       </c>
       <c r="P261" t="s">
         <v>25</v>
@@ -10240,7 +10281,7 @@
         <v>35</v>
       </c>
       <c r="R261" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="262" spans="13:18">
@@ -10248,10 +10289,10 @@
         <v>17</v>
       </c>
       <c r="N262" t="s">
-        <v>730</v>
+        <v>736</v>
       </c>
       <c r="O262" t="s">
-        <v>731</v>
+        <v>737</v>
       </c>
       <c r="P262" t="s">
         <v>25</v>
@@ -10260,7 +10301,7 @@
         <v>35</v>
       </c>
       <c r="R262" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="263" spans="13:18">
@@ -10268,10 +10309,10 @@
         <v>17</v>
       </c>
       <c r="N263" t="s">
-        <v>732</v>
+        <v>738</v>
       </c>
       <c r="O263" t="s">
-        <v>733</v>
+        <v>739</v>
       </c>
       <c r="P263" t="s">
         <v>25</v>
@@ -10280,7 +10321,7 @@
         <v>35</v>
       </c>
       <c r="R263" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="264" spans="13:18">
@@ -10288,10 +10329,10 @@
         <v>17</v>
       </c>
       <c r="N264" t="s">
-        <v>734</v>
+        <v>740</v>
       </c>
       <c r="O264" t="s">
-        <v>735</v>
+        <v>741</v>
       </c>
       <c r="P264" t="s">
         <v>25</v>
@@ -10300,7 +10341,7 @@
         <v>35</v>
       </c>
       <c r="R264" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="265" spans="13:18">
@@ -10308,10 +10349,10 @@
         <v>17</v>
       </c>
       <c r="N265" t="s">
-        <v>736</v>
+        <v>742</v>
       </c>
       <c r="O265" t="s">
-        <v>737</v>
+        <v>743</v>
       </c>
       <c r="P265" t="s">
         <v>25</v>
@@ -10320,7 +10361,7 @@
         <v>35</v>
       </c>
       <c r="R265" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="266" spans="13:18">
@@ -10328,10 +10369,10 @@
         <v>17</v>
       </c>
       <c r="N266" t="s">
-        <v>738</v>
+        <v>744</v>
       </c>
       <c r="O266" t="s">
-        <v>739</v>
+        <v>745</v>
       </c>
       <c r="P266" t="s">
         <v>25</v>
@@ -10340,7 +10381,7 @@
         <v>35</v>
       </c>
       <c r="R266" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="267" spans="13:18">
@@ -10348,10 +10389,10 @@
         <v>17</v>
       </c>
       <c r="N267" t="s">
-        <v>740</v>
+        <v>746</v>
       </c>
       <c r="O267" t="s">
-        <v>741</v>
+        <v>747</v>
       </c>
       <c r="P267" t="s">
         <v>25</v>
@@ -10360,7 +10401,7 @@
         <v>35</v>
       </c>
       <c r="R267" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="268" spans="13:18">
@@ -10368,10 +10409,10 @@
         <v>17</v>
       </c>
       <c r="N268" t="s">
-        <v>742</v>
+        <v>748</v>
       </c>
       <c r="O268" t="s">
-        <v>743</v>
+        <v>749</v>
       </c>
       <c r="P268" t="s">
         <v>25</v>
@@ -10380,7 +10421,7 @@
         <v>35</v>
       </c>
       <c r="R268" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="269" spans="13:18">
@@ -10388,10 +10429,10 @@
         <v>17</v>
       </c>
       <c r="N269" t="s">
-        <v>744</v>
+        <v>750</v>
       </c>
       <c r="O269" t="s">
-        <v>745</v>
+        <v>751</v>
       </c>
       <c r="P269" t="s">
         <v>25</v>
@@ -10400,7 +10441,7 @@
         <v>35</v>
       </c>
       <c r="R269" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="270" spans="13:18">
@@ -10408,10 +10449,10 @@
         <v>17</v>
       </c>
       <c r="N270" t="s">
-        <v>746</v>
+        <v>752</v>
       </c>
       <c r="O270" t="s">
-        <v>747</v>
+        <v>753</v>
       </c>
       <c r="P270" t="s">
         <v>25</v>
@@ -10420,7 +10461,7 @@
         <v>35</v>
       </c>
       <c r="R270" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="271" spans="13:18">
@@ -10428,10 +10469,10 @@
         <v>17</v>
       </c>
       <c r="N271" t="s">
-        <v>748</v>
+        <v>754</v>
       </c>
       <c r="O271" t="s">
-        <v>749</v>
+        <v>755</v>
       </c>
       <c r="P271" t="s">
         <v>25</v>
@@ -10440,7 +10481,7 @@
         <v>35</v>
       </c>
       <c r="R271" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="272" spans="13:18">
@@ -10448,10 +10489,10 @@
         <v>17</v>
       </c>
       <c r="N272" t="s">
-        <v>750</v>
+        <v>756</v>
       </c>
       <c r="O272" t="s">
-        <v>751</v>
+        <v>757</v>
       </c>
       <c r="P272" t="s">
         <v>25</v>
@@ -10460,7 +10501,7 @@
         <v>35</v>
       </c>
       <c r="R272" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="273" spans="13:18">
@@ -10468,10 +10509,10 @@
         <v>17</v>
       </c>
       <c r="N273" t="s">
-        <v>752</v>
+        <v>758</v>
       </c>
       <c r="O273" t="s">
-        <v>753</v>
+        <v>759</v>
       </c>
       <c r="P273" t="s">
         <v>25</v>
@@ -10480,7 +10521,7 @@
         <v>35</v>
       </c>
       <c r="R273" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="274" spans="13:18">
@@ -10488,10 +10529,10 @@
         <v>17</v>
       </c>
       <c r="N274" t="s">
-        <v>754</v>
+        <v>760</v>
       </c>
       <c r="O274" t="s">
-        <v>755</v>
+        <v>761</v>
       </c>
       <c r="P274" t="s">
         <v>25</v>
@@ -10500,7 +10541,7 @@
         <v>35</v>
       </c>
       <c r="R274" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="275" spans="13:18">
@@ -10508,10 +10549,10 @@
         <v>17</v>
       </c>
       <c r="N275" t="s">
-        <v>756</v>
+        <v>762</v>
       </c>
       <c r="O275" t="s">
-        <v>757</v>
+        <v>763</v>
       </c>
       <c r="P275" t="s">
         <v>25</v>
@@ -10520,7 +10561,7 @@
         <v>35</v>
       </c>
       <c r="R275" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="276" spans="13:18">
@@ -10528,10 +10569,10 @@
         <v>17</v>
       </c>
       <c r="N276" t="s">
-        <v>758</v>
+        <v>764</v>
       </c>
       <c r="O276" t="s">
-        <v>759</v>
+        <v>765</v>
       </c>
       <c r="P276" t="s">
         <v>25</v>
@@ -10540,7 +10581,7 @@
         <v>35</v>
       </c>
       <c r="R276" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="277" spans="13:18">
@@ -10548,10 +10589,10 @@
         <v>17</v>
       </c>
       <c r="N277" t="s">
-        <v>760</v>
+        <v>766</v>
       </c>
       <c r="O277" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="P277" t="s">
         <v>25</v>
@@ -10560,7 +10601,7 @@
         <v>35</v>
       </c>
       <c r="R277" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="278" spans="13:18">
@@ -10568,10 +10609,10 @@
         <v>17</v>
       </c>
       <c r="N278" t="s">
-        <v>762</v>
+        <v>768</v>
       </c>
       <c r="O278" t="s">
-        <v>763</v>
+        <v>769</v>
       </c>
       <c r="P278" t="s">
         <v>25</v>
@@ -10580,7 +10621,7 @@
         <v>35</v>
       </c>
       <c r="R278" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="279" spans="13:18">
@@ -10588,10 +10629,10 @@
         <v>17</v>
       </c>
       <c r="N279" t="s">
-        <v>764</v>
+        <v>770</v>
       </c>
       <c r="O279" t="s">
-        <v>765</v>
+        <v>771</v>
       </c>
       <c r="P279" t="s">
         <v>25</v>
@@ -10600,7 +10641,7 @@
         <v>35</v>
       </c>
       <c r="R279" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="280" spans="13:18">
@@ -10608,10 +10649,10 @@
         <v>17</v>
       </c>
       <c r="N280" t="s">
-        <v>766</v>
+        <v>772</v>
       </c>
       <c r="O280" t="s">
-        <v>767</v>
+        <v>773</v>
       </c>
       <c r="P280" t="s">
         <v>25</v>
@@ -10620,7 +10661,7 @@
         <v>35</v>
       </c>
       <c r="R280" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="281" spans="13:18">
@@ -10628,10 +10669,10 @@
         <v>17</v>
       </c>
       <c r="N281" t="s">
-        <v>768</v>
+        <v>774</v>
       </c>
       <c r="O281" t="s">
-        <v>769</v>
+        <v>775</v>
       </c>
       <c r="P281" t="s">
         <v>25</v>
@@ -10640,7 +10681,7 @@
         <v>35</v>
       </c>
       <c r="R281" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="282" spans="13:18">
@@ -10648,10 +10689,10 @@
         <v>17</v>
       </c>
       <c r="N282" t="s">
-        <v>770</v>
+        <v>776</v>
       </c>
       <c r="O282" t="s">
-        <v>771</v>
+        <v>777</v>
       </c>
       <c r="P282" t="s">
         <v>25</v>
@@ -10660,7 +10701,7 @@
         <v>35</v>
       </c>
       <c r="R282" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="283" spans="13:18">
@@ -10668,10 +10709,10 @@
         <v>17</v>
       </c>
       <c r="N283" t="s">
-        <v>772</v>
+        <v>778</v>
       </c>
       <c r="O283" t="s">
-        <v>773</v>
+        <v>779</v>
       </c>
       <c r="P283" t="s">
         <v>25</v>
@@ -10680,7 +10721,7 @@
         <v>35</v>
       </c>
       <c r="R283" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="284" spans="13:18">
@@ -10688,10 +10729,10 @@
         <v>17</v>
       </c>
       <c r="N284" t="s">
-        <v>774</v>
+        <v>780</v>
       </c>
       <c r="O284" t="s">
-        <v>775</v>
+        <v>781</v>
       </c>
       <c r="P284" t="s">
         <v>25</v>
@@ -10700,7 +10741,7 @@
         <v>35</v>
       </c>
       <c r="R284" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="285" spans="13:18">
@@ -10708,10 +10749,10 @@
         <v>17</v>
       </c>
       <c r="N285" t="s">
-        <v>776</v>
+        <v>782</v>
       </c>
       <c r="O285" t="s">
-        <v>777</v>
+        <v>783</v>
       </c>
       <c r="P285" t="s">
         <v>25</v>
@@ -10720,7 +10761,7 @@
         <v>35</v>
       </c>
       <c r="R285" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="286" spans="13:18">
@@ -10728,10 +10769,10 @@
         <v>17</v>
       </c>
       <c r="N286" t="s">
-        <v>778</v>
+        <v>784</v>
       </c>
       <c r="O286" t="s">
-        <v>779</v>
+        <v>785</v>
       </c>
       <c r="P286" t="s">
         <v>25</v>
@@ -10740,7 +10781,7 @@
         <v>35</v>
       </c>
       <c r="R286" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="287" spans="13:18">
@@ -10748,10 +10789,10 @@
         <v>17</v>
       </c>
       <c r="N287" t="s">
-        <v>780</v>
+        <v>786</v>
       </c>
       <c r="O287" t="s">
-        <v>781</v>
+        <v>787</v>
       </c>
       <c r="P287" t="s">
         <v>25</v>
@@ -10760,7 +10801,7 @@
         <v>35</v>
       </c>
       <c r="R287" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="288" spans="13:18">
@@ -10768,10 +10809,10 @@
         <v>17</v>
       </c>
       <c r="N288" t="s">
-        <v>782</v>
+        <v>788</v>
       </c>
       <c r="O288" t="s">
-        <v>783</v>
+        <v>789</v>
       </c>
       <c r="P288" t="s">
         <v>25</v>
@@ -10780,7 +10821,7 @@
         <v>35</v>
       </c>
       <c r="R288" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
   </sheetData>
